--- a/Documents/Client-Shared/saturn_pdf/Saturn/Saturn_BOM_REVA.xlsx
+++ b/Documents/Client-Shared/saturn_pdf/Saturn/Saturn_BOM_REVA.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24931"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Saturn\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Melih-SoundSensor\Documents\Client-Shared\saturn_pdf\Saturn\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A99976D7-7560-4B33-BDC8-C7A60F700009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="9735"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -579,7 +580,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -1204,7 +1205,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="72">
+  <fills count="73">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1594,6 +1595,12 @@
       <patternFill patternType="solid">
         <fgColor indexed="26"/>
         <bgColor indexed="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -3196,7 +3203,7 @@
     <xf numFmtId="0" fontId="20" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3251,9 +3258,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3285,24 +3289,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3341,1034 +3327,1075 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="72" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="72" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="72" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="72" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="72" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1026">
     <cellStyle name="20% - Accent1" xfId="22" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent1 2" xfId="95"/>
-    <cellStyle name="20% - Accent1 2 2" xfId="294"/>
-    <cellStyle name="20% - Accent1 2 3" xfId="128"/>
-    <cellStyle name="20% - Accent1 2 3 2" xfId="990"/>
-    <cellStyle name="20% - Accent1 3" xfId="212"/>
-    <cellStyle name="20% - Accent1 3 2" xfId="848"/>
-    <cellStyle name="20% - Accent1 4" xfId="636"/>
-    <cellStyle name="20% - Accent1 4 2" xfId="898"/>
-    <cellStyle name="20% - Accent1 5" xfId="702"/>
-    <cellStyle name="20% - Accent1 6" xfId="1000"/>
+    <cellStyle name="20% - Accent1 2" xfId="95" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="20% - Accent1 2 2" xfId="294" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="20% - Accent1 2 3" xfId="128" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="20% - Accent1 2 3 2" xfId="990" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="20% - Accent1 3" xfId="212" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="20% - Accent1 3 2" xfId="848" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="20% - Accent1 4" xfId="636" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="20% - Accent1 4 2" xfId="898" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="20% - Accent1 5" xfId="702" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="20% - Accent1 6" xfId="1000" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
     <cellStyle name="20% - Accent2" xfId="26" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2 2" xfId="100"/>
-    <cellStyle name="20% - Accent2 2 2" xfId="297"/>
-    <cellStyle name="20% - Accent2 2 3" xfId="130"/>
-    <cellStyle name="20% - Accent2 2 3 2" xfId="968"/>
-    <cellStyle name="20% - Accent2 3" xfId="213"/>
-    <cellStyle name="20% - Accent2 3 2" xfId="847"/>
-    <cellStyle name="20% - Accent2 4" xfId="638"/>
-    <cellStyle name="20% - Accent2 4 2" xfId="900"/>
-    <cellStyle name="20% - Accent2 5" xfId="704"/>
-    <cellStyle name="20% - Accent2 6" xfId="999"/>
+    <cellStyle name="20% - Accent2 2" xfId="100" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="20% - Accent2 2 2" xfId="297" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="20% - Accent2 2 3" xfId="130" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="20% - Accent2 2 3 2" xfId="968" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="20% - Accent2 3" xfId="213" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="20% - Accent2 3 2" xfId="847" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="20% - Accent2 4" xfId="638" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
+    <cellStyle name="20% - Accent2 4 2" xfId="900" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="20% - Accent2 5" xfId="704" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="20% - Accent2 6" xfId="999" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
     <cellStyle name="20% - Accent3" xfId="30" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3 2" xfId="97"/>
-    <cellStyle name="20% - Accent3 2 2" xfId="290"/>
-    <cellStyle name="20% - Accent3 2 3" xfId="132"/>
-    <cellStyle name="20% - Accent3 2 3 2" xfId="108"/>
-    <cellStyle name="20% - Accent3 3" xfId="214"/>
-    <cellStyle name="20% - Accent3 3 2" xfId="846"/>
-    <cellStyle name="20% - Accent3 4" xfId="640"/>
-    <cellStyle name="20% - Accent3 4 2" xfId="902"/>
-    <cellStyle name="20% - Accent3 5" xfId="706"/>
-    <cellStyle name="20% - Accent3 6" xfId="1001"/>
+    <cellStyle name="20% - Accent3 2" xfId="97" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
+    <cellStyle name="20% - Accent3 2 2" xfId="290" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
+    <cellStyle name="20% - Accent3 2 3" xfId="132" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
+    <cellStyle name="20% - Accent3 2 3 2" xfId="108" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
+    <cellStyle name="20% - Accent3 3" xfId="214" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
+    <cellStyle name="20% - Accent3 3 2" xfId="846" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
+    <cellStyle name="20% - Accent3 4" xfId="640" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
+    <cellStyle name="20% - Accent3 4 2" xfId="902" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
+    <cellStyle name="20% - Accent3 5" xfId="706" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
+    <cellStyle name="20% - Accent3 6" xfId="1001" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
     <cellStyle name="20% - Accent4" xfId="34" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4 2" xfId="99"/>
-    <cellStyle name="20% - Accent4 2 2" xfId="298"/>
-    <cellStyle name="20% - Accent4 2 3" xfId="134"/>
-    <cellStyle name="20% - Accent4 2 3 2" xfId="994"/>
-    <cellStyle name="20% - Accent4 3" xfId="217"/>
-    <cellStyle name="20% - Accent4 3 2" xfId="845"/>
-    <cellStyle name="20% - Accent4 4" xfId="642"/>
-    <cellStyle name="20% - Accent4 4 2" xfId="904"/>
-    <cellStyle name="20% - Accent4 5" xfId="708"/>
-    <cellStyle name="20% - Accent4 6" xfId="1002"/>
+    <cellStyle name="20% - Accent4 2" xfId="99" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
+    <cellStyle name="20% - Accent4 2 2" xfId="298" xr:uid="{00000000-0005-0000-0000-000023000000}"/>
+    <cellStyle name="20% - Accent4 2 3" xfId="134" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
+    <cellStyle name="20% - Accent4 2 3 2" xfId="994" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
+    <cellStyle name="20% - Accent4 3" xfId="217" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
+    <cellStyle name="20% - Accent4 3 2" xfId="845" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
+    <cellStyle name="20% - Accent4 4" xfId="642" xr:uid="{00000000-0005-0000-0000-000028000000}"/>
+    <cellStyle name="20% - Accent4 4 2" xfId="904" xr:uid="{00000000-0005-0000-0000-000029000000}"/>
+    <cellStyle name="20% - Accent4 5" xfId="708" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
+    <cellStyle name="20% - Accent4 6" xfId="1002" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
     <cellStyle name="20% - Accent5" xfId="38" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5 2" xfId="98"/>
-    <cellStyle name="20% - Accent5 2 2" xfId="299"/>
-    <cellStyle name="20% - Accent5 2 3" xfId="136"/>
-    <cellStyle name="20% - Accent5 2 3 2" xfId="965"/>
-    <cellStyle name="20% - Accent5 3" xfId="583"/>
-    <cellStyle name="20% - Accent5 3 2" xfId="844"/>
-    <cellStyle name="20% - Accent5 4" xfId="644"/>
-    <cellStyle name="20% - Accent5 4 2" xfId="906"/>
-    <cellStyle name="20% - Accent5 5" xfId="710"/>
+    <cellStyle name="20% - Accent5 2" xfId="98" xr:uid="{00000000-0005-0000-0000-00002D000000}"/>
+    <cellStyle name="20% - Accent5 2 2" xfId="299" xr:uid="{00000000-0005-0000-0000-00002E000000}"/>
+    <cellStyle name="20% - Accent5 2 3" xfId="136" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
+    <cellStyle name="20% - Accent5 2 3 2" xfId="965" xr:uid="{00000000-0005-0000-0000-000030000000}"/>
+    <cellStyle name="20% - Accent5 3" xfId="583" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="20% - Accent5 3 2" xfId="844" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="20% - Accent5 4" xfId="644" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
+    <cellStyle name="20% - Accent5 4 2" xfId="906" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
+    <cellStyle name="20% - Accent5 5" xfId="710" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
     <cellStyle name="20% - Accent6" xfId="42" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6 2" xfId="94"/>
-    <cellStyle name="20% - Accent6 2 2" xfId="301"/>
-    <cellStyle name="20% - Accent6 2 3" xfId="138"/>
-    <cellStyle name="20% - Accent6 2 3 2" xfId="109"/>
-    <cellStyle name="20% - Accent6 3" xfId="582"/>
-    <cellStyle name="20% - Accent6 3 2" xfId="843"/>
-    <cellStyle name="20% - Accent6 4" xfId="646"/>
-    <cellStyle name="20% - Accent6 4 2" xfId="908"/>
-    <cellStyle name="20% - Accent6 5" xfId="712"/>
+    <cellStyle name="20% - Accent6 2" xfId="94" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
+    <cellStyle name="20% - Accent6 2 2" xfId="301" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
+    <cellStyle name="20% - Accent6 2 3" xfId="138" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
+    <cellStyle name="20% - Accent6 2 3 2" xfId="109" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
+    <cellStyle name="20% - Accent6 3" xfId="582" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
+    <cellStyle name="20% - Accent6 3 2" xfId="843" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
+    <cellStyle name="20% - Accent6 4" xfId="646" xr:uid="{00000000-0005-0000-0000-00003D000000}"/>
+    <cellStyle name="20% - Accent6 4 2" xfId="908" xr:uid="{00000000-0005-0000-0000-00003E000000}"/>
+    <cellStyle name="20% - Accent6 5" xfId="712" xr:uid="{00000000-0005-0000-0000-00003F000000}"/>
     <cellStyle name="40% - Accent1" xfId="23" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1 2" xfId="101"/>
-    <cellStyle name="40% - Accent1 2 2" xfId="289"/>
-    <cellStyle name="40% - Accent1 2 3" xfId="129"/>
-    <cellStyle name="40% - Accent1 2 3 2" xfId="107"/>
-    <cellStyle name="40% - Accent1 3" xfId="581"/>
-    <cellStyle name="40% - Accent1 3 2" xfId="842"/>
-    <cellStyle name="40% - Accent1 4" xfId="637"/>
-    <cellStyle name="40% - Accent1 4 2" xfId="899"/>
-    <cellStyle name="40% - Accent1 5" xfId="703"/>
-    <cellStyle name="40% - Accent1 6" xfId="1003"/>
+    <cellStyle name="40% - Accent1 2" xfId="101" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
+    <cellStyle name="40% - Accent1 2 2" xfId="289" xr:uid="{00000000-0005-0000-0000-000042000000}"/>
+    <cellStyle name="40% - Accent1 2 3" xfId="129" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
+    <cellStyle name="40% - Accent1 2 3 2" xfId="107" xr:uid="{00000000-0005-0000-0000-000044000000}"/>
+    <cellStyle name="40% - Accent1 3" xfId="581" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
+    <cellStyle name="40% - Accent1 3 2" xfId="842" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
+    <cellStyle name="40% - Accent1 4" xfId="637" xr:uid="{00000000-0005-0000-0000-000047000000}"/>
+    <cellStyle name="40% - Accent1 4 2" xfId="899" xr:uid="{00000000-0005-0000-0000-000048000000}"/>
+    <cellStyle name="40% - Accent1 5" xfId="703" xr:uid="{00000000-0005-0000-0000-000049000000}"/>
+    <cellStyle name="40% - Accent1 6" xfId="1003" xr:uid="{00000000-0005-0000-0000-00004A000000}"/>
     <cellStyle name="40% - Accent2" xfId="27" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2 2" xfId="59"/>
-    <cellStyle name="40% - Accent2 2 2" xfId="303"/>
-    <cellStyle name="40% - Accent2 2 3" xfId="131"/>
-    <cellStyle name="40% - Accent2 2 3 2" xfId="111"/>
-    <cellStyle name="40% - Accent2 3" xfId="580"/>
-    <cellStyle name="40% - Accent2 3 2" xfId="841"/>
-    <cellStyle name="40% - Accent2 4" xfId="639"/>
-    <cellStyle name="40% - Accent2 4 2" xfId="901"/>
-    <cellStyle name="40% - Accent2 5" xfId="705"/>
+    <cellStyle name="40% - Accent2 2" xfId="59" xr:uid="{00000000-0005-0000-0000-00004C000000}"/>
+    <cellStyle name="40% - Accent2 2 2" xfId="303" xr:uid="{00000000-0005-0000-0000-00004D000000}"/>
+    <cellStyle name="40% - Accent2 2 3" xfId="131" xr:uid="{00000000-0005-0000-0000-00004E000000}"/>
+    <cellStyle name="40% - Accent2 2 3 2" xfId="111" xr:uid="{00000000-0005-0000-0000-00004F000000}"/>
+    <cellStyle name="40% - Accent2 3" xfId="580" xr:uid="{00000000-0005-0000-0000-000050000000}"/>
+    <cellStyle name="40% - Accent2 3 2" xfId="841" xr:uid="{00000000-0005-0000-0000-000051000000}"/>
+    <cellStyle name="40% - Accent2 4" xfId="639" xr:uid="{00000000-0005-0000-0000-000052000000}"/>
+    <cellStyle name="40% - Accent2 4 2" xfId="901" xr:uid="{00000000-0005-0000-0000-000053000000}"/>
+    <cellStyle name="40% - Accent2 5" xfId="705" xr:uid="{00000000-0005-0000-0000-000054000000}"/>
     <cellStyle name="40% - Accent3" xfId="31" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3 2" xfId="66"/>
-    <cellStyle name="40% - Accent3 2 2" xfId="304"/>
-    <cellStyle name="40% - Accent3 2 3" xfId="133"/>
-    <cellStyle name="40% - Accent3 2 3 2" xfId="982"/>
-    <cellStyle name="40% - Accent3 3" xfId="215"/>
-    <cellStyle name="40% - Accent3 3 2" xfId="840"/>
-    <cellStyle name="40% - Accent3 4" xfId="641"/>
-    <cellStyle name="40% - Accent3 4 2" xfId="903"/>
-    <cellStyle name="40% - Accent3 5" xfId="707"/>
-    <cellStyle name="40% - Accent3 6" xfId="1004"/>
+    <cellStyle name="40% - Accent3 2" xfId="66" xr:uid="{00000000-0005-0000-0000-000056000000}"/>
+    <cellStyle name="40% - Accent3 2 2" xfId="304" xr:uid="{00000000-0005-0000-0000-000057000000}"/>
+    <cellStyle name="40% - Accent3 2 3" xfId="133" xr:uid="{00000000-0005-0000-0000-000058000000}"/>
+    <cellStyle name="40% - Accent3 2 3 2" xfId="982" xr:uid="{00000000-0005-0000-0000-000059000000}"/>
+    <cellStyle name="40% - Accent3 3" xfId="215" xr:uid="{00000000-0005-0000-0000-00005A000000}"/>
+    <cellStyle name="40% - Accent3 3 2" xfId="840" xr:uid="{00000000-0005-0000-0000-00005B000000}"/>
+    <cellStyle name="40% - Accent3 4" xfId="641" xr:uid="{00000000-0005-0000-0000-00005C000000}"/>
+    <cellStyle name="40% - Accent3 4 2" xfId="903" xr:uid="{00000000-0005-0000-0000-00005D000000}"/>
+    <cellStyle name="40% - Accent3 5" xfId="707" xr:uid="{00000000-0005-0000-0000-00005E000000}"/>
+    <cellStyle name="40% - Accent3 6" xfId="1004" xr:uid="{00000000-0005-0000-0000-00005F000000}"/>
     <cellStyle name="40% - Accent4" xfId="35" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4 2" xfId="69"/>
-    <cellStyle name="40% - Accent4 2 2" xfId="305"/>
-    <cellStyle name="40% - Accent4 2 3" xfId="135"/>
-    <cellStyle name="40% - Accent4 2 3 2" xfId="989"/>
-    <cellStyle name="40% - Accent4 3" xfId="579"/>
-    <cellStyle name="40% - Accent4 3 2" xfId="839"/>
-    <cellStyle name="40% - Accent4 4" xfId="643"/>
-    <cellStyle name="40% - Accent4 4 2" xfId="905"/>
-    <cellStyle name="40% - Accent4 5" xfId="709"/>
-    <cellStyle name="40% - Accent4 6" xfId="1005"/>
+    <cellStyle name="40% - Accent4 2" xfId="69" xr:uid="{00000000-0005-0000-0000-000061000000}"/>
+    <cellStyle name="40% - Accent4 2 2" xfId="305" xr:uid="{00000000-0005-0000-0000-000062000000}"/>
+    <cellStyle name="40% - Accent4 2 3" xfId="135" xr:uid="{00000000-0005-0000-0000-000063000000}"/>
+    <cellStyle name="40% - Accent4 2 3 2" xfId="989" xr:uid="{00000000-0005-0000-0000-000064000000}"/>
+    <cellStyle name="40% - Accent4 3" xfId="579" xr:uid="{00000000-0005-0000-0000-000065000000}"/>
+    <cellStyle name="40% - Accent4 3 2" xfId="839" xr:uid="{00000000-0005-0000-0000-000066000000}"/>
+    <cellStyle name="40% - Accent4 4" xfId="643" xr:uid="{00000000-0005-0000-0000-000067000000}"/>
+    <cellStyle name="40% - Accent4 4 2" xfId="905" xr:uid="{00000000-0005-0000-0000-000068000000}"/>
+    <cellStyle name="40% - Accent4 5" xfId="709" xr:uid="{00000000-0005-0000-0000-000069000000}"/>
+    <cellStyle name="40% - Accent4 6" xfId="1005" xr:uid="{00000000-0005-0000-0000-00006A000000}"/>
     <cellStyle name="40% - Accent5" xfId="39" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5 2" xfId="67"/>
-    <cellStyle name="40% - Accent5 2 2" xfId="306"/>
-    <cellStyle name="40% - Accent5 2 3" xfId="137"/>
-    <cellStyle name="40% - Accent5 2 3 2" xfId="976"/>
-    <cellStyle name="40% - Accent5 3" xfId="578"/>
-    <cellStyle name="40% - Accent5 3 2" xfId="838"/>
-    <cellStyle name="40% - Accent5 4" xfId="645"/>
-    <cellStyle name="40% - Accent5 4 2" xfId="907"/>
-    <cellStyle name="40% - Accent5 5" xfId="711"/>
+    <cellStyle name="40% - Accent5 2" xfId="67" xr:uid="{00000000-0005-0000-0000-00006C000000}"/>
+    <cellStyle name="40% - Accent5 2 2" xfId="306" xr:uid="{00000000-0005-0000-0000-00006D000000}"/>
+    <cellStyle name="40% - Accent5 2 3" xfId="137" xr:uid="{00000000-0005-0000-0000-00006E000000}"/>
+    <cellStyle name="40% - Accent5 2 3 2" xfId="976" xr:uid="{00000000-0005-0000-0000-00006F000000}"/>
+    <cellStyle name="40% - Accent5 3" xfId="578" xr:uid="{00000000-0005-0000-0000-000070000000}"/>
+    <cellStyle name="40% - Accent5 3 2" xfId="838" xr:uid="{00000000-0005-0000-0000-000071000000}"/>
+    <cellStyle name="40% - Accent5 4" xfId="645" xr:uid="{00000000-0005-0000-0000-000072000000}"/>
+    <cellStyle name="40% - Accent5 4 2" xfId="907" xr:uid="{00000000-0005-0000-0000-000073000000}"/>
+    <cellStyle name="40% - Accent5 5" xfId="711" xr:uid="{00000000-0005-0000-0000-000074000000}"/>
     <cellStyle name="40% - Accent6" xfId="43" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6 2" xfId="63"/>
-    <cellStyle name="40% - Accent6 2 2" xfId="309"/>
-    <cellStyle name="40% - Accent6 2 3" xfId="139"/>
-    <cellStyle name="40% - Accent6 2 3 2" xfId="987"/>
-    <cellStyle name="40% - Accent6 3" xfId="577"/>
-    <cellStyle name="40% - Accent6 3 2" xfId="837"/>
-    <cellStyle name="40% - Accent6 4" xfId="647"/>
-    <cellStyle name="40% - Accent6 4 2" xfId="909"/>
-    <cellStyle name="40% - Accent6 5" xfId="713"/>
-    <cellStyle name="40% - Accent6 6" xfId="1006"/>
+    <cellStyle name="40% - Accent6 2" xfId="63" xr:uid="{00000000-0005-0000-0000-000076000000}"/>
+    <cellStyle name="40% - Accent6 2 2" xfId="309" xr:uid="{00000000-0005-0000-0000-000077000000}"/>
+    <cellStyle name="40% - Accent6 2 3" xfId="139" xr:uid="{00000000-0005-0000-0000-000078000000}"/>
+    <cellStyle name="40% - Accent6 2 3 2" xfId="987" xr:uid="{00000000-0005-0000-0000-000079000000}"/>
+    <cellStyle name="40% - Accent6 3" xfId="577" xr:uid="{00000000-0005-0000-0000-00007A000000}"/>
+    <cellStyle name="40% - Accent6 3 2" xfId="837" xr:uid="{00000000-0005-0000-0000-00007B000000}"/>
+    <cellStyle name="40% - Accent6 4" xfId="647" xr:uid="{00000000-0005-0000-0000-00007C000000}"/>
+    <cellStyle name="40% - Accent6 4 2" xfId="909" xr:uid="{00000000-0005-0000-0000-00007D000000}"/>
+    <cellStyle name="40% - Accent6 5" xfId="713" xr:uid="{00000000-0005-0000-0000-00007E000000}"/>
+    <cellStyle name="40% - Accent6 6" xfId="1006" xr:uid="{00000000-0005-0000-0000-00007F000000}"/>
     <cellStyle name="60% - Accent1" xfId="24" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1 2" xfId="62"/>
-    <cellStyle name="60% - Accent1 2 2" xfId="300"/>
-    <cellStyle name="60% - Accent1 2 2 2" xfId="967"/>
-    <cellStyle name="60% - Accent1 3" xfId="1007"/>
+    <cellStyle name="60% - Accent1 2" xfId="62" xr:uid="{00000000-0005-0000-0000-000081000000}"/>
+    <cellStyle name="60% - Accent1 2 2" xfId="300" xr:uid="{00000000-0005-0000-0000-000082000000}"/>
+    <cellStyle name="60% - Accent1 2 2 2" xfId="967" xr:uid="{00000000-0005-0000-0000-000083000000}"/>
+    <cellStyle name="60% - Accent1 3" xfId="1007" xr:uid="{00000000-0005-0000-0000-000084000000}"/>
     <cellStyle name="60% - Accent2" xfId="28" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2 2" xfId="61"/>
-    <cellStyle name="60% - Accent2 2 2" xfId="302"/>
-    <cellStyle name="60% - Accent2 2 2 2" xfId="964"/>
+    <cellStyle name="60% - Accent2 2" xfId="61" xr:uid="{00000000-0005-0000-0000-000086000000}"/>
+    <cellStyle name="60% - Accent2 2 2" xfId="302" xr:uid="{00000000-0005-0000-0000-000087000000}"/>
+    <cellStyle name="60% - Accent2 2 2 2" xfId="964" xr:uid="{00000000-0005-0000-0000-000088000000}"/>
     <cellStyle name="60% - Accent3" xfId="32" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3 2" xfId="60"/>
-    <cellStyle name="60% - Accent3 2 2" xfId="311"/>
-    <cellStyle name="60% - Accent3 2 3" xfId="216"/>
-    <cellStyle name="60% - Accent3 2 3 2" xfId="979"/>
-    <cellStyle name="60% - Accent3 3" xfId="1008"/>
+    <cellStyle name="60% - Accent3 2" xfId="60" xr:uid="{00000000-0005-0000-0000-00008A000000}"/>
+    <cellStyle name="60% - Accent3 2 2" xfId="311" xr:uid="{00000000-0005-0000-0000-00008B000000}"/>
+    <cellStyle name="60% - Accent3 2 3" xfId="216" xr:uid="{00000000-0005-0000-0000-00008C000000}"/>
+    <cellStyle name="60% - Accent3 2 3 2" xfId="979" xr:uid="{00000000-0005-0000-0000-00008D000000}"/>
+    <cellStyle name="60% - Accent3 3" xfId="1008" xr:uid="{00000000-0005-0000-0000-00008E000000}"/>
     <cellStyle name="60% - Accent4" xfId="36" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4 2" xfId="64"/>
-    <cellStyle name="60% - Accent4 2 2" xfId="313"/>
-    <cellStyle name="60% - Accent4 2 3" xfId="218"/>
-    <cellStyle name="60% - Accent4 2 3 2" xfId="969"/>
-    <cellStyle name="60% - Accent4 3" xfId="1009"/>
+    <cellStyle name="60% - Accent4 2" xfId="64" xr:uid="{00000000-0005-0000-0000-000090000000}"/>
+    <cellStyle name="60% - Accent4 2 2" xfId="313" xr:uid="{00000000-0005-0000-0000-000091000000}"/>
+    <cellStyle name="60% - Accent4 2 3" xfId="218" xr:uid="{00000000-0005-0000-0000-000092000000}"/>
+    <cellStyle name="60% - Accent4 2 3 2" xfId="969" xr:uid="{00000000-0005-0000-0000-000093000000}"/>
+    <cellStyle name="60% - Accent4 3" xfId="1009" xr:uid="{00000000-0005-0000-0000-000094000000}"/>
     <cellStyle name="60% - Accent5" xfId="40" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5 2" xfId="71"/>
-    <cellStyle name="60% - Accent5 2 2" xfId="314"/>
-    <cellStyle name="60% - Accent5 2 2 2" xfId="971"/>
+    <cellStyle name="60% - Accent5 2" xfId="71" xr:uid="{00000000-0005-0000-0000-000096000000}"/>
+    <cellStyle name="60% - Accent5 2 2" xfId="314" xr:uid="{00000000-0005-0000-0000-000097000000}"/>
+    <cellStyle name="60% - Accent5 2 2 2" xfId="971" xr:uid="{00000000-0005-0000-0000-000098000000}"/>
     <cellStyle name="60% - Accent6" xfId="44" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6 2" xfId="70"/>
-    <cellStyle name="60% - Accent6 2 2" xfId="315"/>
-    <cellStyle name="60% - Accent6 2 3" xfId="219"/>
-    <cellStyle name="60% - Accent6 2 3 2" xfId="970"/>
-    <cellStyle name="60% - Accent6 3" xfId="1010"/>
+    <cellStyle name="60% - Accent6 2" xfId="70" xr:uid="{00000000-0005-0000-0000-00009A000000}"/>
+    <cellStyle name="60% - Accent6 2 2" xfId="315" xr:uid="{00000000-0005-0000-0000-00009B000000}"/>
+    <cellStyle name="60% - Accent6 2 3" xfId="219" xr:uid="{00000000-0005-0000-0000-00009C000000}"/>
+    <cellStyle name="60% - Accent6 2 3 2" xfId="970" xr:uid="{00000000-0005-0000-0000-00009D000000}"/>
+    <cellStyle name="60% - Accent6 3" xfId="1010" xr:uid="{00000000-0005-0000-0000-00009E000000}"/>
     <cellStyle name="Accent1" xfId="21" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent1 2" xfId="68"/>
-    <cellStyle name="Accent1 2 2" xfId="316"/>
-    <cellStyle name="Accent1 2 2 2" xfId="972"/>
-    <cellStyle name="Accent1 3" xfId="1011"/>
+    <cellStyle name="Accent1 2" xfId="68" xr:uid="{00000000-0005-0000-0000-0000A0000000}"/>
+    <cellStyle name="Accent1 2 2" xfId="316" xr:uid="{00000000-0005-0000-0000-0000A1000000}"/>
+    <cellStyle name="Accent1 2 2 2" xfId="972" xr:uid="{00000000-0005-0000-0000-0000A2000000}"/>
+    <cellStyle name="Accent1 3" xfId="1011" xr:uid="{00000000-0005-0000-0000-0000A3000000}"/>
     <cellStyle name="Accent2" xfId="25" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent2 2" xfId="65"/>
-    <cellStyle name="Accent2 2 2" xfId="317"/>
-    <cellStyle name="Accent2 2 2 2" xfId="978"/>
-    <cellStyle name="Accent2 3" xfId="1012"/>
+    <cellStyle name="Accent2 2" xfId="65" xr:uid="{00000000-0005-0000-0000-0000A5000000}"/>
+    <cellStyle name="Accent2 2 2" xfId="317" xr:uid="{00000000-0005-0000-0000-0000A6000000}"/>
+    <cellStyle name="Accent2 2 2 2" xfId="978" xr:uid="{00000000-0005-0000-0000-0000A7000000}"/>
+    <cellStyle name="Accent2 3" xfId="1012" xr:uid="{00000000-0005-0000-0000-0000A8000000}"/>
     <cellStyle name="Accent3" xfId="29" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent3 2" xfId="90"/>
-    <cellStyle name="Accent3 2 2" xfId="318"/>
-    <cellStyle name="Accent3 2 2 2" xfId="981"/>
-    <cellStyle name="Accent3 3" xfId="1013"/>
+    <cellStyle name="Accent3 2" xfId="90" xr:uid="{00000000-0005-0000-0000-0000AA000000}"/>
+    <cellStyle name="Accent3 2 2" xfId="318" xr:uid="{00000000-0005-0000-0000-0000AB000000}"/>
+    <cellStyle name="Accent3 2 2 2" xfId="981" xr:uid="{00000000-0005-0000-0000-0000AC000000}"/>
+    <cellStyle name="Accent3 3" xfId="1013" xr:uid="{00000000-0005-0000-0000-0000AD000000}"/>
     <cellStyle name="Accent4" xfId="33" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent4 2" xfId="86"/>
-    <cellStyle name="Accent4 2 2" xfId="319"/>
-    <cellStyle name="Accent4 2 2 2" xfId="993"/>
-    <cellStyle name="Accent4 3" xfId="1014"/>
+    <cellStyle name="Accent4 2" xfId="86" xr:uid="{00000000-0005-0000-0000-0000AF000000}"/>
+    <cellStyle name="Accent4 2 2" xfId="319" xr:uid="{00000000-0005-0000-0000-0000B0000000}"/>
+    <cellStyle name="Accent4 2 2 2" xfId="993" xr:uid="{00000000-0005-0000-0000-0000B1000000}"/>
+    <cellStyle name="Accent4 3" xfId="1014" xr:uid="{00000000-0005-0000-0000-0000B2000000}"/>
     <cellStyle name="Accent5" xfId="37" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent5 2" xfId="82"/>
-    <cellStyle name="Accent5 2 2" xfId="320"/>
-    <cellStyle name="Accent5 2 2 2" xfId="986"/>
+    <cellStyle name="Accent5 2" xfId="82" xr:uid="{00000000-0005-0000-0000-0000B4000000}"/>
+    <cellStyle name="Accent5 2 2" xfId="320" xr:uid="{00000000-0005-0000-0000-0000B5000000}"/>
+    <cellStyle name="Accent5 2 2 2" xfId="986" xr:uid="{00000000-0005-0000-0000-0000B6000000}"/>
     <cellStyle name="Accent6" xfId="41" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Accent6 2" xfId="78"/>
-    <cellStyle name="Accent6 2 2" xfId="321"/>
-    <cellStyle name="Accent6 2 2 2" xfId="992"/>
+    <cellStyle name="Accent6 2" xfId="78" xr:uid="{00000000-0005-0000-0000-0000B8000000}"/>
+    <cellStyle name="Accent6 2 2" xfId="321" xr:uid="{00000000-0005-0000-0000-0000B9000000}"/>
+    <cellStyle name="Accent6 2 2 2" xfId="992" xr:uid="{00000000-0005-0000-0000-0000BA000000}"/>
     <cellStyle name="Bad" xfId="10" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Bad 2" xfId="75"/>
-    <cellStyle name="Bad 2 2" xfId="322"/>
-    <cellStyle name="Bad 2 2 2" xfId="984"/>
-    <cellStyle name="Bad 3" xfId="1015"/>
+    <cellStyle name="Bad 2" xfId="75" xr:uid="{00000000-0005-0000-0000-0000BC000000}"/>
+    <cellStyle name="Bad 2 2" xfId="322" xr:uid="{00000000-0005-0000-0000-0000BD000000}"/>
+    <cellStyle name="Bad 2 2 2" xfId="984" xr:uid="{00000000-0005-0000-0000-0000BE000000}"/>
+    <cellStyle name="Bad 3" xfId="1015" xr:uid="{00000000-0005-0000-0000-0000BF000000}"/>
     <cellStyle name="Calculation" xfId="14" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Calculation 2" xfId="72"/>
-    <cellStyle name="Calculation 2 2" xfId="296"/>
-    <cellStyle name="Calculation 2 2 2" xfId="977"/>
-    <cellStyle name="Calculation 3" xfId="1016"/>
+    <cellStyle name="Calculation 2" xfId="72" xr:uid="{00000000-0005-0000-0000-0000C1000000}"/>
+    <cellStyle name="Calculation 2 2" xfId="296" xr:uid="{00000000-0005-0000-0000-0000C2000000}"/>
+    <cellStyle name="Calculation 2 2 2" xfId="977" xr:uid="{00000000-0005-0000-0000-0000C3000000}"/>
+    <cellStyle name="Calculation 3" xfId="1016" xr:uid="{00000000-0005-0000-0000-0000C4000000}"/>
     <cellStyle name="Check Cell" xfId="16" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Check Cell 2" xfId="93"/>
-    <cellStyle name="Check Cell 2 2" xfId="323"/>
-    <cellStyle name="Check Cell 2 2 2" xfId="966"/>
-    <cellStyle name="Comma 2" xfId="118"/>
-    <cellStyle name="Comma 2 10" xfId="731"/>
-    <cellStyle name="Comma 2 2" xfId="226"/>
-    <cellStyle name="Comma 2 2 2" xfId="307"/>
-    <cellStyle name="Comma 2 2 3" xfId="478"/>
-    <cellStyle name="Comma 2 3" xfId="225"/>
-    <cellStyle name="Comma 2 4" xfId="325"/>
-    <cellStyle name="Comma 2 5" xfId="441"/>
-    <cellStyle name="Comma 2 5 2" xfId="795"/>
-    <cellStyle name="Comma 2 6" xfId="477"/>
-    <cellStyle name="Comma 2 7" xfId="575"/>
-    <cellStyle name="Comma 2 7 2" xfId="836"/>
-    <cellStyle name="Comma 2 8" xfId="576"/>
-    <cellStyle name="Comma 2 9" xfId="665"/>
-    <cellStyle name="Comma 2 9 2" xfId="927"/>
-    <cellStyle name="Comma 3" xfId="476"/>
-    <cellStyle name="Comma 3 2" xfId="830"/>
-    <cellStyle name="Currency 2" xfId="79"/>
-    <cellStyle name="Currency 3" xfId="102"/>
-    <cellStyle name="Currency 3 2" xfId="105"/>
+    <cellStyle name="Check Cell 2" xfId="93" xr:uid="{00000000-0005-0000-0000-0000C6000000}"/>
+    <cellStyle name="Check Cell 2 2" xfId="323" xr:uid="{00000000-0005-0000-0000-0000C7000000}"/>
+    <cellStyle name="Check Cell 2 2 2" xfId="966" xr:uid="{00000000-0005-0000-0000-0000C8000000}"/>
+    <cellStyle name="Comma 2" xfId="118" xr:uid="{00000000-0005-0000-0000-0000C9000000}"/>
+    <cellStyle name="Comma 2 10" xfId="731" xr:uid="{00000000-0005-0000-0000-0000CA000000}"/>
+    <cellStyle name="Comma 2 2" xfId="226" xr:uid="{00000000-0005-0000-0000-0000CB000000}"/>
+    <cellStyle name="Comma 2 2 2" xfId="307" xr:uid="{00000000-0005-0000-0000-0000CC000000}"/>
+    <cellStyle name="Comma 2 2 3" xfId="478" xr:uid="{00000000-0005-0000-0000-0000CD000000}"/>
+    <cellStyle name="Comma 2 3" xfId="225" xr:uid="{00000000-0005-0000-0000-0000CE000000}"/>
+    <cellStyle name="Comma 2 4" xfId="325" xr:uid="{00000000-0005-0000-0000-0000CF000000}"/>
+    <cellStyle name="Comma 2 5" xfId="441" xr:uid="{00000000-0005-0000-0000-0000D0000000}"/>
+    <cellStyle name="Comma 2 5 2" xfId="795" xr:uid="{00000000-0005-0000-0000-0000D1000000}"/>
+    <cellStyle name="Comma 2 6" xfId="477" xr:uid="{00000000-0005-0000-0000-0000D2000000}"/>
+    <cellStyle name="Comma 2 7" xfId="575" xr:uid="{00000000-0005-0000-0000-0000D3000000}"/>
+    <cellStyle name="Comma 2 7 2" xfId="836" xr:uid="{00000000-0005-0000-0000-0000D4000000}"/>
+    <cellStyle name="Comma 2 8" xfId="576" xr:uid="{00000000-0005-0000-0000-0000D5000000}"/>
+    <cellStyle name="Comma 2 9" xfId="665" xr:uid="{00000000-0005-0000-0000-0000D6000000}"/>
+    <cellStyle name="Comma 2 9 2" xfId="927" xr:uid="{00000000-0005-0000-0000-0000D7000000}"/>
+    <cellStyle name="Comma 3" xfId="476" xr:uid="{00000000-0005-0000-0000-0000D8000000}"/>
+    <cellStyle name="Comma 3 2" xfId="830" xr:uid="{00000000-0005-0000-0000-0000D9000000}"/>
+    <cellStyle name="Currency 2" xfId="79" xr:uid="{00000000-0005-0000-0000-0000DA000000}"/>
+    <cellStyle name="Currency 3" xfId="102" xr:uid="{00000000-0005-0000-0000-0000DB000000}"/>
+    <cellStyle name="Currency 3 2" xfId="105" xr:uid="{00000000-0005-0000-0000-0000DC000000}"/>
     <cellStyle name="Explanatory Text" xfId="19" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text 2" xfId="89"/>
-    <cellStyle name="Explanatory Text 2 2" xfId="327"/>
-    <cellStyle name="Explanatory Text 2 2 2" xfId="112"/>
+    <cellStyle name="Explanatory Text 2" xfId="89" xr:uid="{00000000-0005-0000-0000-0000DE000000}"/>
+    <cellStyle name="Explanatory Text 2 2" xfId="327" xr:uid="{00000000-0005-0000-0000-0000DF000000}"/>
+    <cellStyle name="Explanatory Text 2 2 2" xfId="112" xr:uid="{00000000-0005-0000-0000-0000E0000000}"/>
     <cellStyle name="Good" xfId="9" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Good 2" xfId="85"/>
-    <cellStyle name="Good 2 2" xfId="312"/>
-    <cellStyle name="Good 2 2 2" xfId="985"/>
+    <cellStyle name="Good 2" xfId="85" xr:uid="{00000000-0005-0000-0000-0000E2000000}"/>
+    <cellStyle name="Good 2 2" xfId="312" xr:uid="{00000000-0005-0000-0000-0000E3000000}"/>
+    <cellStyle name="Good 2 2 2" xfId="985" xr:uid="{00000000-0005-0000-0000-0000E4000000}"/>
     <cellStyle name="Heading 1" xfId="5" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 1 2" xfId="81"/>
-    <cellStyle name="Heading 1 2 2" xfId="329"/>
-    <cellStyle name="Heading 1 2 2 2" xfId="988"/>
-    <cellStyle name="Heading 1 3" xfId="1017"/>
+    <cellStyle name="Heading 1 2" xfId="81" xr:uid="{00000000-0005-0000-0000-0000E6000000}"/>
+    <cellStyle name="Heading 1 2 2" xfId="329" xr:uid="{00000000-0005-0000-0000-0000E7000000}"/>
+    <cellStyle name="Heading 1 2 2 2" xfId="988" xr:uid="{00000000-0005-0000-0000-0000E8000000}"/>
+    <cellStyle name="Heading 1 3" xfId="1017" xr:uid="{00000000-0005-0000-0000-0000E9000000}"/>
     <cellStyle name="Heading 2" xfId="6" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 2 2" xfId="77"/>
-    <cellStyle name="Heading 2 2 2" xfId="324"/>
-    <cellStyle name="Heading 2 2 2 2" xfId="973"/>
-    <cellStyle name="Heading 2 3" xfId="1018"/>
+    <cellStyle name="Heading 2 2" xfId="77" xr:uid="{00000000-0005-0000-0000-0000EB000000}"/>
+    <cellStyle name="Heading 2 2 2" xfId="324" xr:uid="{00000000-0005-0000-0000-0000EC000000}"/>
+    <cellStyle name="Heading 2 2 2 2" xfId="973" xr:uid="{00000000-0005-0000-0000-0000ED000000}"/>
+    <cellStyle name="Heading 2 3" xfId="1018" xr:uid="{00000000-0005-0000-0000-0000EE000000}"/>
     <cellStyle name="Heading 3" xfId="7" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 3 2" xfId="74"/>
-    <cellStyle name="Heading 3 2 2" xfId="330"/>
-    <cellStyle name="Heading 3 2 2 2" xfId="963"/>
-    <cellStyle name="Heading 3 3" xfId="1019"/>
+    <cellStyle name="Heading 3 2" xfId="74" xr:uid="{00000000-0005-0000-0000-0000F0000000}"/>
+    <cellStyle name="Heading 3 2 2" xfId="330" xr:uid="{00000000-0005-0000-0000-0000F1000000}"/>
+    <cellStyle name="Heading 3 2 2 2" xfId="963" xr:uid="{00000000-0005-0000-0000-0000F2000000}"/>
+    <cellStyle name="Heading 3 3" xfId="1019" xr:uid="{00000000-0005-0000-0000-0000F3000000}"/>
     <cellStyle name="Heading 4" xfId="8" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Heading 4 2" xfId="92"/>
-    <cellStyle name="Heading 4 2 2" xfId="331"/>
-    <cellStyle name="Heading 4 2 2 2" xfId="110"/>
-    <cellStyle name="Heading 4 3" xfId="1020"/>
-    <cellStyle name="Hyperlink 2" xfId="168"/>
-    <cellStyle name="Hyperlink 2 2" xfId="335"/>
-    <cellStyle name="Hyperlink 2 3" xfId="479"/>
-    <cellStyle name="Hyperlink 3" xfId="208"/>
-    <cellStyle name="Hyperlink 3 2" xfId="291"/>
-    <cellStyle name="Hyperlink 3 3" xfId="480"/>
-    <cellStyle name="Hyperlink 4" xfId="151"/>
-    <cellStyle name="Hyperlink 4 2" xfId="336"/>
-    <cellStyle name="Hyperlink 4 3" xfId="481"/>
-    <cellStyle name="Hyperlink 5" xfId="123"/>
-    <cellStyle name="Hyperlink 5 2" xfId="338"/>
-    <cellStyle name="Hyperlink 5 3" xfId="482"/>
-    <cellStyle name="Hyperlink 6" xfId="182"/>
-    <cellStyle name="Hyperlink 7" xfId="113"/>
+    <cellStyle name="Heading 4 2" xfId="92" xr:uid="{00000000-0005-0000-0000-0000F5000000}"/>
+    <cellStyle name="Heading 4 2 2" xfId="331" xr:uid="{00000000-0005-0000-0000-0000F6000000}"/>
+    <cellStyle name="Heading 4 2 2 2" xfId="110" xr:uid="{00000000-0005-0000-0000-0000F7000000}"/>
+    <cellStyle name="Heading 4 3" xfId="1020" xr:uid="{00000000-0005-0000-0000-0000F8000000}"/>
+    <cellStyle name="Hyperlink 2" xfId="168" xr:uid="{00000000-0005-0000-0000-0000F9000000}"/>
+    <cellStyle name="Hyperlink 2 2" xfId="335" xr:uid="{00000000-0005-0000-0000-0000FA000000}"/>
+    <cellStyle name="Hyperlink 2 3" xfId="479" xr:uid="{00000000-0005-0000-0000-0000FB000000}"/>
+    <cellStyle name="Hyperlink 3" xfId="208" xr:uid="{00000000-0005-0000-0000-0000FC000000}"/>
+    <cellStyle name="Hyperlink 3 2" xfId="291" xr:uid="{00000000-0005-0000-0000-0000FD000000}"/>
+    <cellStyle name="Hyperlink 3 3" xfId="480" xr:uid="{00000000-0005-0000-0000-0000FE000000}"/>
+    <cellStyle name="Hyperlink 4" xfId="151" xr:uid="{00000000-0005-0000-0000-0000FF000000}"/>
+    <cellStyle name="Hyperlink 4 2" xfId="336" xr:uid="{00000000-0005-0000-0000-000000010000}"/>
+    <cellStyle name="Hyperlink 4 3" xfId="481" xr:uid="{00000000-0005-0000-0000-000001010000}"/>
+    <cellStyle name="Hyperlink 5" xfId="123" xr:uid="{00000000-0005-0000-0000-000002010000}"/>
+    <cellStyle name="Hyperlink 5 2" xfId="338" xr:uid="{00000000-0005-0000-0000-000003010000}"/>
+    <cellStyle name="Hyperlink 5 3" xfId="482" xr:uid="{00000000-0005-0000-0000-000004010000}"/>
+    <cellStyle name="Hyperlink 6" xfId="182" xr:uid="{00000000-0005-0000-0000-000005010000}"/>
+    <cellStyle name="Hyperlink 7" xfId="113" xr:uid="{00000000-0005-0000-0000-000006010000}"/>
     <cellStyle name="Input" xfId="12" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Input 2" xfId="88"/>
-    <cellStyle name="Input 2 2" xfId="339"/>
-    <cellStyle name="Input 2 2 2" xfId="991"/>
+    <cellStyle name="Input 2" xfId="88" xr:uid="{00000000-0005-0000-0000-000008010000}"/>
+    <cellStyle name="Input 2 2" xfId="339" xr:uid="{00000000-0005-0000-0000-000009010000}"/>
+    <cellStyle name="Input 2 2 2" xfId="991" xr:uid="{00000000-0005-0000-0000-00000A010000}"/>
     <cellStyle name="Linked Cell" xfId="15" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Linked Cell 2" xfId="84"/>
-    <cellStyle name="Linked Cell 2 2" xfId="341"/>
-    <cellStyle name="Linked Cell 2 2 2" xfId="974"/>
-    <cellStyle name="Microsoft Excel found an error in the formula you entered. Do you want to accept the correction proposed below?_x000a__x000a_|_x000a__x000a_• To accept the correction, click Yes._x000a_• To close this message and correct the formula yourself, click No. 2" xfId="114"/>
-    <cellStyle name="Microsoft Excel found an error in the formula you entered. Do you want to accept the correction proposed below?_x000a__x000a_|_x000a__x000a_• To accept the correction, click Yes._x000a_• To close this message and correct the formula yourself, click No. 2 2" xfId="332"/>
-    <cellStyle name="Microsoft Excel found an error in the formula you entered. Do you want to accept the correction proposed below?_x000a__x000a_|_x000a__x000a_• To accept the correction, click Yes._x000a_• To close this message and correct the formula yourself, click No. 2 3" xfId="483"/>
+    <cellStyle name="Linked Cell 2" xfId="84" xr:uid="{00000000-0005-0000-0000-00000C010000}"/>
+    <cellStyle name="Linked Cell 2 2" xfId="341" xr:uid="{00000000-0005-0000-0000-00000D010000}"/>
+    <cellStyle name="Linked Cell 2 2 2" xfId="974" xr:uid="{00000000-0005-0000-0000-00000E010000}"/>
+    <cellStyle name="Microsoft Excel found an error in the formula you entered. Do you want to accept the correction proposed below?_x000a__x000a_|_x000a__x000a_• To accept the correction, click Yes._x000a_• To close this message and correct the formula yourself, click No. 2" xfId="114" xr:uid="{00000000-0005-0000-0000-00000F010000}"/>
+    <cellStyle name="Microsoft Excel found an error in the formula you entered. Do you want to accept the correction proposed below?_x000a__x000a_|_x000a__x000a_• To accept the correction, click Yes._x000a_• To close this message and correct the formula yourself, click No. 2 2" xfId="332" xr:uid="{00000000-0005-0000-0000-000010010000}"/>
+    <cellStyle name="Microsoft Excel found an error in the formula you entered. Do you want to accept the correction proposed below?_x000a__x000a_|_x000a__x000a_• To accept the correction, click Yes._x000a_• To close this message and correct the formula yourself, click No. 2 3" xfId="483" xr:uid="{00000000-0005-0000-0000-000011010000}"/>
     <cellStyle name="Neutral" xfId="11" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Neutral 2" xfId="80"/>
-    <cellStyle name="Neutral 2 2" xfId="344"/>
-    <cellStyle name="Neutral 2 2 2" xfId="980"/>
+    <cellStyle name="Neutral 2" xfId="80" xr:uid="{00000000-0005-0000-0000-000013010000}"/>
+    <cellStyle name="Neutral 2 2" xfId="344" xr:uid="{00000000-0005-0000-0000-000014010000}"/>
+    <cellStyle name="Neutral 2 2 2" xfId="980" xr:uid="{00000000-0005-0000-0000-000015010000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10" xfId="153"/>
-    <cellStyle name="Normal 10 10" xfId="714"/>
-    <cellStyle name="Normal 10 2" xfId="174"/>
-    <cellStyle name="Normal 10 2 2" xfId="200"/>
-    <cellStyle name="Normal 10 2 2 2" xfId="229"/>
-    <cellStyle name="Normal 10 2 2 3" xfId="337"/>
-    <cellStyle name="Normal 10 2 2 4" xfId="467"/>
-    <cellStyle name="Normal 10 2 2 4 2" xfId="821"/>
-    <cellStyle name="Normal 10 2 2 5" xfId="486"/>
-    <cellStyle name="Normal 10 2 2 6" xfId="572"/>
-    <cellStyle name="Normal 10 2 2 6 2" xfId="833"/>
-    <cellStyle name="Normal 10 2 2 7" xfId="692"/>
-    <cellStyle name="Normal 10 2 2 7 2" xfId="954"/>
-    <cellStyle name="Normal 10 2 2 8" xfId="758"/>
-    <cellStyle name="Normal 10 2 3" xfId="228"/>
-    <cellStyle name="Normal 10 2 4" xfId="333"/>
-    <cellStyle name="Normal 10 2 5" xfId="438"/>
-    <cellStyle name="Normal 10 2 5 2" xfId="792"/>
-    <cellStyle name="Normal 10 2 6" xfId="485"/>
-    <cellStyle name="Normal 10 2 7" xfId="573"/>
-    <cellStyle name="Normal 10 2 7 2" xfId="834"/>
-    <cellStyle name="Normal 10 2 8" xfId="656"/>
-    <cellStyle name="Normal 10 2 8 2" xfId="918"/>
-    <cellStyle name="Normal 10 2 9" xfId="722"/>
-    <cellStyle name="Normal 10 3" xfId="189"/>
-    <cellStyle name="Normal 10 3 2" xfId="230"/>
-    <cellStyle name="Normal 10 3 3" xfId="292"/>
-    <cellStyle name="Normal 10 3 4" xfId="456"/>
-    <cellStyle name="Normal 10 3 4 2" xfId="810"/>
-    <cellStyle name="Normal 10 3 5" xfId="487"/>
-    <cellStyle name="Normal 10 3 6" xfId="571"/>
-    <cellStyle name="Normal 10 3 6 2" xfId="832"/>
-    <cellStyle name="Normal 10 3 7" xfId="681"/>
-    <cellStyle name="Normal 10 3 7 2" xfId="943"/>
-    <cellStyle name="Normal 10 3 8" xfId="747"/>
-    <cellStyle name="Normal 10 4" xfId="227"/>
-    <cellStyle name="Normal 10 5" xfId="351"/>
-    <cellStyle name="Normal 10 6" xfId="446"/>
-    <cellStyle name="Normal 10 6 2" xfId="800"/>
-    <cellStyle name="Normal 10 7" xfId="484"/>
-    <cellStyle name="Normal 10 8" xfId="574"/>
-    <cellStyle name="Normal 10 8 2" xfId="835"/>
-    <cellStyle name="Normal 10 9" xfId="648"/>
-    <cellStyle name="Normal 10 9 2" xfId="910"/>
-    <cellStyle name="Normal 11" xfId="150"/>
-    <cellStyle name="Normal 11 10" xfId="570"/>
-    <cellStyle name="Normal 11 10 2" xfId="831"/>
-    <cellStyle name="Normal 11 11" xfId="649"/>
-    <cellStyle name="Normal 11 11 2" xfId="911"/>
-    <cellStyle name="Normal 11 12" xfId="715"/>
-    <cellStyle name="Normal 11 2" xfId="154"/>
-    <cellStyle name="Normal 11 2 10" xfId="723"/>
-    <cellStyle name="Normal 11 2 2" xfId="175"/>
-    <cellStyle name="Normal 11 2 2 2" xfId="201"/>
-    <cellStyle name="Normal 11 2 2 2 2" xfId="234"/>
-    <cellStyle name="Normal 11 2 2 2 3" xfId="345"/>
-    <cellStyle name="Normal 11 2 2 2 4" xfId="468"/>
-    <cellStyle name="Normal 11 2 2 2 4 2" xfId="822"/>
-    <cellStyle name="Normal 11 2 2 2 5" xfId="491"/>
-    <cellStyle name="Normal 11 2 2 2 6" xfId="586"/>
-    <cellStyle name="Normal 11 2 2 2 6 2" xfId="851"/>
-    <cellStyle name="Normal 11 2 2 2 7" xfId="693"/>
-    <cellStyle name="Normal 11 2 2 2 7 2" xfId="955"/>
-    <cellStyle name="Normal 11 2 2 2 8" xfId="759"/>
-    <cellStyle name="Normal 11 2 2 3" xfId="233"/>
-    <cellStyle name="Normal 11 2 2 4" xfId="293"/>
-    <cellStyle name="Normal 11 2 2 5" xfId="443"/>
-    <cellStyle name="Normal 11 2 2 5 2" xfId="797"/>
-    <cellStyle name="Normal 11 2 2 6" xfId="490"/>
-    <cellStyle name="Normal 11 2 2 7" xfId="585"/>
-    <cellStyle name="Normal 11 2 2 7 2" xfId="850"/>
-    <cellStyle name="Normal 11 2 2 8" xfId="673"/>
-    <cellStyle name="Normal 11 2 2 8 2" xfId="935"/>
-    <cellStyle name="Normal 11 2 2 9" xfId="739"/>
-    <cellStyle name="Normal 11 2 3" xfId="190"/>
-    <cellStyle name="Normal 11 2 3 2" xfId="235"/>
-    <cellStyle name="Normal 11 2 3 3" xfId="340"/>
-    <cellStyle name="Normal 11 2 3 4" xfId="457"/>
-    <cellStyle name="Normal 11 2 3 4 2" xfId="811"/>
-    <cellStyle name="Normal 11 2 3 5" xfId="492"/>
-    <cellStyle name="Normal 11 2 3 6" xfId="587"/>
-    <cellStyle name="Normal 11 2 3 6 2" xfId="852"/>
-    <cellStyle name="Normal 11 2 3 7" xfId="682"/>
-    <cellStyle name="Normal 11 2 3 7 2" xfId="944"/>
-    <cellStyle name="Normal 11 2 3 8" xfId="748"/>
-    <cellStyle name="Normal 11 2 4" xfId="232"/>
-    <cellStyle name="Normal 11 2 5" xfId="308"/>
-    <cellStyle name="Normal 11 2 6" xfId="447"/>
-    <cellStyle name="Normal 11 2 6 2" xfId="801"/>
-    <cellStyle name="Normal 11 2 7" xfId="489"/>
-    <cellStyle name="Normal 11 2 8" xfId="592"/>
-    <cellStyle name="Normal 11 2 8 2" xfId="857"/>
-    <cellStyle name="Normal 11 2 9" xfId="657"/>
-    <cellStyle name="Normal 11 2 9 2" xfId="919"/>
-    <cellStyle name="Normal 11 3" xfId="173"/>
-    <cellStyle name="Normal 11 3 2" xfId="199"/>
-    <cellStyle name="Normal 11 3 2 2" xfId="237"/>
-    <cellStyle name="Normal 11 3 2 3" xfId="346"/>
-    <cellStyle name="Normal 11 3 2 4" xfId="466"/>
-    <cellStyle name="Normal 11 3 2 4 2" xfId="820"/>
-    <cellStyle name="Normal 11 3 2 5" xfId="494"/>
-    <cellStyle name="Normal 11 3 2 6" xfId="589"/>
-    <cellStyle name="Normal 11 3 2 6 2" xfId="854"/>
-    <cellStyle name="Normal 11 3 2 7" xfId="691"/>
-    <cellStyle name="Normal 11 3 2 7 2" xfId="953"/>
-    <cellStyle name="Normal 11 3 2 8" xfId="757"/>
-    <cellStyle name="Normal 11 3 3" xfId="236"/>
-    <cellStyle name="Normal 11 3 4" xfId="310"/>
-    <cellStyle name="Normal 11 3 5" xfId="451"/>
-    <cellStyle name="Normal 11 3 5 2" xfId="805"/>
-    <cellStyle name="Normal 11 3 6" xfId="493"/>
-    <cellStyle name="Normal 11 3 7" xfId="588"/>
-    <cellStyle name="Normal 11 3 7 2" xfId="853"/>
-    <cellStyle name="Normal 11 3 8" xfId="672"/>
-    <cellStyle name="Normal 11 3 8 2" xfId="934"/>
-    <cellStyle name="Normal 11 3 9" xfId="738"/>
-    <cellStyle name="Normal 11 4" xfId="188"/>
-    <cellStyle name="Normal 11 4 2" xfId="238"/>
-    <cellStyle name="Normal 11 4 3" xfId="343"/>
-    <cellStyle name="Normal 11 4 4" xfId="455"/>
-    <cellStyle name="Normal 11 4 4 2" xfId="809"/>
-    <cellStyle name="Normal 11 4 5" xfId="495"/>
-    <cellStyle name="Normal 11 4 6" xfId="590"/>
-    <cellStyle name="Normal 11 4 6 2" xfId="855"/>
-    <cellStyle name="Normal 11 4 7" xfId="680"/>
-    <cellStyle name="Normal 11 4 7 2" xfId="942"/>
-    <cellStyle name="Normal 11 4 8" xfId="746"/>
-    <cellStyle name="Normal 11 5" xfId="239"/>
-    <cellStyle name="Normal 11 5 2" xfId="353"/>
-    <cellStyle name="Normal 11 5 3" xfId="424"/>
-    <cellStyle name="Normal 11 5 3 2" xfId="778"/>
-    <cellStyle name="Normal 11 5 4" xfId="496"/>
-    <cellStyle name="Normal 11 5 5" xfId="591"/>
-    <cellStyle name="Normal 11 5 5 2" xfId="856"/>
-    <cellStyle name="Normal 11 5 6" xfId="669"/>
-    <cellStyle name="Normal 11 5 6 2" xfId="931"/>
-    <cellStyle name="Normal 11 5 7" xfId="768"/>
-    <cellStyle name="Normal 11 5 8" xfId="735"/>
-    <cellStyle name="Normal 11 6" xfId="231"/>
-    <cellStyle name="Normal 11 7" xfId="326"/>
-    <cellStyle name="Normal 11 8" xfId="448"/>
-    <cellStyle name="Normal 11 8 2" xfId="802"/>
-    <cellStyle name="Normal 11 9" xfId="488"/>
-    <cellStyle name="Normal 12" xfId="155"/>
-    <cellStyle name="Normal 12 10" xfId="716"/>
-    <cellStyle name="Normal 12 2" xfId="176"/>
-    <cellStyle name="Normal 12 2 2" xfId="202"/>
-    <cellStyle name="Normal 12 2 2 2" xfId="242"/>
-    <cellStyle name="Normal 12 2 2 3" xfId="348"/>
-    <cellStyle name="Normal 12 2 2 4" xfId="469"/>
-    <cellStyle name="Normal 12 2 2 4 2" xfId="823"/>
-    <cellStyle name="Normal 12 2 2 5" xfId="499"/>
-    <cellStyle name="Normal 12 2 2 6" xfId="595"/>
-    <cellStyle name="Normal 12 2 2 6 2" xfId="860"/>
-    <cellStyle name="Normal 12 2 2 7" xfId="694"/>
-    <cellStyle name="Normal 12 2 2 7 2" xfId="956"/>
-    <cellStyle name="Normal 12 2 2 8" xfId="760"/>
-    <cellStyle name="Normal 12 2 3" xfId="241"/>
-    <cellStyle name="Normal 12 2 4" xfId="347"/>
-    <cellStyle name="Normal 12 2 5" xfId="442"/>
-    <cellStyle name="Normal 12 2 5 2" xfId="796"/>
-    <cellStyle name="Normal 12 2 6" xfId="498"/>
-    <cellStyle name="Normal 12 2 7" xfId="594"/>
-    <cellStyle name="Normal 12 2 7 2" xfId="859"/>
-    <cellStyle name="Normal 12 2 8" xfId="658"/>
-    <cellStyle name="Normal 12 2 8 2" xfId="920"/>
-    <cellStyle name="Normal 12 2 9" xfId="724"/>
-    <cellStyle name="Normal 12 3" xfId="191"/>
-    <cellStyle name="Normal 12 3 2" xfId="243"/>
-    <cellStyle name="Normal 12 3 3" xfId="295"/>
-    <cellStyle name="Normal 12 3 4" xfId="458"/>
-    <cellStyle name="Normal 12 3 4 2" xfId="812"/>
-    <cellStyle name="Normal 12 3 5" xfId="500"/>
-    <cellStyle name="Normal 12 3 6" xfId="596"/>
-    <cellStyle name="Normal 12 3 6 2" xfId="861"/>
-    <cellStyle name="Normal 12 3 7" xfId="683"/>
-    <cellStyle name="Normal 12 3 7 2" xfId="945"/>
-    <cellStyle name="Normal 12 3 8" xfId="749"/>
-    <cellStyle name="Normal 12 4" xfId="240"/>
-    <cellStyle name="Normal 12 5" xfId="352"/>
-    <cellStyle name="Normal 12 6" xfId="436"/>
-    <cellStyle name="Normal 12 6 2" xfId="790"/>
-    <cellStyle name="Normal 12 7" xfId="497"/>
-    <cellStyle name="Normal 12 8" xfId="593"/>
-    <cellStyle name="Normal 12 8 2" xfId="858"/>
-    <cellStyle name="Normal 12 9" xfId="650"/>
-    <cellStyle name="Normal 12 9 2" xfId="912"/>
-    <cellStyle name="Normal 13" xfId="156"/>
-    <cellStyle name="Normal 13 10" xfId="717"/>
-    <cellStyle name="Normal 13 2" xfId="177"/>
-    <cellStyle name="Normal 13 2 2" xfId="203"/>
-    <cellStyle name="Normal 13 2 2 2" xfId="246"/>
-    <cellStyle name="Normal 13 2 2 3" xfId="355"/>
-    <cellStyle name="Normal 13 2 2 4" xfId="470"/>
-    <cellStyle name="Normal 13 2 2 4 2" xfId="824"/>
-    <cellStyle name="Normal 13 2 2 5" xfId="503"/>
-    <cellStyle name="Normal 13 2 2 6" xfId="599"/>
-    <cellStyle name="Normal 13 2 2 6 2" xfId="864"/>
-    <cellStyle name="Normal 13 2 2 7" xfId="695"/>
-    <cellStyle name="Normal 13 2 2 7 2" xfId="957"/>
-    <cellStyle name="Normal 13 2 2 8" xfId="761"/>
-    <cellStyle name="Normal 13 2 3" xfId="245"/>
-    <cellStyle name="Normal 13 2 4" xfId="350"/>
-    <cellStyle name="Normal 13 2 5" xfId="453"/>
-    <cellStyle name="Normal 13 2 5 2" xfId="807"/>
-    <cellStyle name="Normal 13 2 6" xfId="502"/>
-    <cellStyle name="Normal 13 2 7" xfId="598"/>
-    <cellStyle name="Normal 13 2 7 2" xfId="863"/>
-    <cellStyle name="Normal 13 2 8" xfId="659"/>
-    <cellStyle name="Normal 13 2 8 2" xfId="921"/>
-    <cellStyle name="Normal 13 2 9" xfId="725"/>
-    <cellStyle name="Normal 13 3" xfId="192"/>
-    <cellStyle name="Normal 13 3 2" xfId="247"/>
-    <cellStyle name="Normal 13 3 3" xfId="356"/>
-    <cellStyle name="Normal 13 3 4" xfId="459"/>
-    <cellStyle name="Normal 13 3 4 2" xfId="813"/>
-    <cellStyle name="Normal 13 3 5" xfId="504"/>
-    <cellStyle name="Normal 13 3 6" xfId="600"/>
-    <cellStyle name="Normal 13 3 6 2" xfId="865"/>
-    <cellStyle name="Normal 13 3 7" xfId="684"/>
-    <cellStyle name="Normal 13 3 7 2" xfId="946"/>
-    <cellStyle name="Normal 13 3 8" xfId="750"/>
-    <cellStyle name="Normal 13 4" xfId="244"/>
-    <cellStyle name="Normal 13 5" xfId="349"/>
-    <cellStyle name="Normal 13 6" xfId="444"/>
-    <cellStyle name="Normal 13 6 2" xfId="798"/>
-    <cellStyle name="Normal 13 7" xfId="501"/>
-    <cellStyle name="Normal 13 8" xfId="597"/>
-    <cellStyle name="Normal 13 8 2" xfId="862"/>
-    <cellStyle name="Normal 13 9" xfId="651"/>
-    <cellStyle name="Normal 13 9 2" xfId="913"/>
-    <cellStyle name="Normal 14" xfId="157"/>
-    <cellStyle name="Normal 14 10" xfId="718"/>
-    <cellStyle name="Normal 14 2" xfId="178"/>
-    <cellStyle name="Normal 14 2 2" xfId="204"/>
-    <cellStyle name="Normal 14 2 2 2" xfId="250"/>
-    <cellStyle name="Normal 14 2 2 3" xfId="359"/>
-    <cellStyle name="Normal 14 2 2 4" xfId="471"/>
-    <cellStyle name="Normal 14 2 2 4 2" xfId="825"/>
-    <cellStyle name="Normal 14 2 2 5" xfId="507"/>
-    <cellStyle name="Normal 14 2 2 6" xfId="603"/>
-    <cellStyle name="Normal 14 2 2 6 2" xfId="868"/>
-    <cellStyle name="Normal 14 2 2 7" xfId="696"/>
-    <cellStyle name="Normal 14 2 2 7 2" xfId="958"/>
-    <cellStyle name="Normal 14 2 2 8" xfId="762"/>
-    <cellStyle name="Normal 14 2 3" xfId="249"/>
-    <cellStyle name="Normal 14 2 4" xfId="358"/>
-    <cellStyle name="Normal 14 2 5" xfId="452"/>
-    <cellStyle name="Normal 14 2 5 2" xfId="806"/>
-    <cellStyle name="Normal 14 2 6" xfId="506"/>
-    <cellStyle name="Normal 14 2 7" xfId="602"/>
-    <cellStyle name="Normal 14 2 7 2" xfId="867"/>
-    <cellStyle name="Normal 14 2 8" xfId="660"/>
-    <cellStyle name="Normal 14 2 8 2" xfId="922"/>
-    <cellStyle name="Normal 14 2 9" xfId="726"/>
-    <cellStyle name="Normal 14 3" xfId="193"/>
-    <cellStyle name="Normal 14 3 2" xfId="251"/>
-    <cellStyle name="Normal 14 3 3" xfId="362"/>
-    <cellStyle name="Normal 14 3 4" xfId="460"/>
-    <cellStyle name="Normal 14 3 4 2" xfId="814"/>
-    <cellStyle name="Normal 14 3 5" xfId="508"/>
-    <cellStyle name="Normal 14 3 6" xfId="604"/>
-    <cellStyle name="Normal 14 3 6 2" xfId="869"/>
-    <cellStyle name="Normal 14 3 7" xfId="685"/>
-    <cellStyle name="Normal 14 3 7 2" xfId="947"/>
-    <cellStyle name="Normal 14 3 8" xfId="751"/>
-    <cellStyle name="Normal 14 4" xfId="248"/>
-    <cellStyle name="Normal 14 5" xfId="357"/>
-    <cellStyle name="Normal 14 6" xfId="431"/>
-    <cellStyle name="Normal 14 6 2" xfId="785"/>
-    <cellStyle name="Normal 14 7" xfId="505"/>
-    <cellStyle name="Normal 14 8" xfId="601"/>
-    <cellStyle name="Normal 14 8 2" xfId="866"/>
-    <cellStyle name="Normal 14 9" xfId="652"/>
-    <cellStyle name="Normal 14 9 2" xfId="914"/>
-    <cellStyle name="Normal 15" xfId="152"/>
-    <cellStyle name="Normal 15 10" xfId="730"/>
-    <cellStyle name="Normal 15 2" xfId="58"/>
-    <cellStyle name="Normal 15 2 2" xfId="364"/>
-    <cellStyle name="Normal 15 2 3" xfId="510"/>
-    <cellStyle name="Normal 15 3" xfId="253"/>
-    <cellStyle name="Normal 15 3 2" xfId="365"/>
-    <cellStyle name="Normal 15 3 3" xfId="511"/>
-    <cellStyle name="Normal 15 4" xfId="252"/>
-    <cellStyle name="Normal 15 5" xfId="363"/>
-    <cellStyle name="Normal 15 6" xfId="430"/>
-    <cellStyle name="Normal 15 6 2" xfId="784"/>
-    <cellStyle name="Normal 15 7" xfId="509"/>
-    <cellStyle name="Normal 15 8" xfId="605"/>
-    <cellStyle name="Normal 15 8 2" xfId="870"/>
-    <cellStyle name="Normal 15 9" xfId="664"/>
-    <cellStyle name="Normal 15 9 2" xfId="926"/>
-    <cellStyle name="Normal 16" xfId="142"/>
-    <cellStyle name="Normal 16 2" xfId="209"/>
-    <cellStyle name="Normal 16 2 2" xfId="367"/>
-    <cellStyle name="Normal 16 2 3" xfId="475"/>
-    <cellStyle name="Normal 16 2 3 2" xfId="829"/>
-    <cellStyle name="Normal 16 2 4" xfId="513"/>
-    <cellStyle name="Normal 16 2 5" xfId="606"/>
-    <cellStyle name="Normal 16 2 5 2" xfId="871"/>
-    <cellStyle name="Normal 16 2 6" xfId="700"/>
-    <cellStyle name="Normal 16 2 6 2" xfId="962"/>
-    <cellStyle name="Normal 16 2 7" xfId="769"/>
-    <cellStyle name="Normal 16 2 8" xfId="766"/>
-    <cellStyle name="Normal 16 2 9" xfId="255"/>
-    <cellStyle name="Normal 16 3" xfId="256"/>
-    <cellStyle name="Normal 16 3 2" xfId="368"/>
-    <cellStyle name="Normal 16 3 3" xfId="514"/>
-    <cellStyle name="Normal 16 4" xfId="254"/>
-    <cellStyle name="Normal 16 5" xfId="366"/>
-    <cellStyle name="Normal 16 6" xfId="512"/>
-    <cellStyle name="Normal 17" xfId="257"/>
-    <cellStyle name="Normal 17 2" xfId="369"/>
-    <cellStyle name="Normal 17 3" xfId="515"/>
-    <cellStyle name="Normal 17 4" xfId="770"/>
-    <cellStyle name="Normal 18" xfId="258"/>
-    <cellStyle name="Normal 18 2" xfId="370"/>
-    <cellStyle name="Normal 18 3" xfId="516"/>
-    <cellStyle name="Normal 18 4" xfId="771"/>
-    <cellStyle name="Normal 19" xfId="259"/>
-    <cellStyle name="Normal 19 2" xfId="372"/>
-    <cellStyle name="Normal 19 3" xfId="517"/>
-    <cellStyle name="Normal 19 4" xfId="772"/>
-    <cellStyle name="Normal 2" xfId="2"/>
-    <cellStyle name="Normal 2 10" xfId="518"/>
-    <cellStyle name="Normal 2 11" xfId="607"/>
-    <cellStyle name="Normal 2 11 2" xfId="872"/>
-    <cellStyle name="Normal 2 12" xfId="653"/>
-    <cellStyle name="Normal 2 12 2" xfId="915"/>
-    <cellStyle name="Normal 2 13" xfId="719"/>
-    <cellStyle name="Normal 2 14" xfId="983"/>
-    <cellStyle name="Normal 2 2" xfId="52"/>
-    <cellStyle name="Normal 2 2 10" xfId="429"/>
-    <cellStyle name="Normal 2 2 10 2" xfId="783"/>
-    <cellStyle name="Normal 2 2 11" xfId="519"/>
-    <cellStyle name="Normal 2 2 12" xfId="608"/>
-    <cellStyle name="Normal 2 2 12 2" xfId="873"/>
-    <cellStyle name="Normal 2 2 13" xfId="654"/>
-    <cellStyle name="Normal 2 2 13 2" xfId="916"/>
-    <cellStyle name="Normal 2 2 14" xfId="720"/>
-    <cellStyle name="Normal 2 2 15" xfId="119"/>
-    <cellStyle name="Normal 2 2 2" xfId="160"/>
-    <cellStyle name="Normal 2 2 2 2" xfId="342"/>
-    <cellStyle name="Normal 2 2 2 3" xfId="520"/>
-    <cellStyle name="Normal 2 2 3" xfId="159"/>
-    <cellStyle name="Normal 2 2 3 10" xfId="728"/>
-    <cellStyle name="Normal 2 2 3 2" xfId="180"/>
-    <cellStyle name="Normal 2 2 3 2 2" xfId="206"/>
-    <cellStyle name="Normal 2 2 3 2 2 2" xfId="264"/>
-    <cellStyle name="Normal 2 2 3 2 2 3" xfId="376"/>
-    <cellStyle name="Normal 2 2 3 2 2 4" xfId="473"/>
-    <cellStyle name="Normal 2 2 3 2 2 4 2" xfId="827"/>
-    <cellStyle name="Normal 2 2 3 2 2 5" xfId="523"/>
-    <cellStyle name="Normal 2 2 3 2 2 6" xfId="611"/>
-    <cellStyle name="Normal 2 2 3 2 2 6 2" xfId="876"/>
-    <cellStyle name="Normal 2 2 3 2 2 7" xfId="698"/>
-    <cellStyle name="Normal 2 2 3 2 2 7 2" xfId="960"/>
-    <cellStyle name="Normal 2 2 3 2 2 8" xfId="764"/>
-    <cellStyle name="Normal 2 2 3 2 3" xfId="263"/>
-    <cellStyle name="Normal 2 2 3 2 4" xfId="375"/>
-    <cellStyle name="Normal 2 2 3 2 5" xfId="433"/>
-    <cellStyle name="Normal 2 2 3 2 5 2" xfId="787"/>
-    <cellStyle name="Normal 2 2 3 2 6" xfId="522"/>
-    <cellStyle name="Normal 2 2 3 2 7" xfId="610"/>
-    <cellStyle name="Normal 2 2 3 2 7 2" xfId="875"/>
-    <cellStyle name="Normal 2 2 3 2 8" xfId="675"/>
-    <cellStyle name="Normal 2 2 3 2 8 2" xfId="937"/>
-    <cellStyle name="Normal 2 2 3 2 9" xfId="741"/>
-    <cellStyle name="Normal 2 2 3 3" xfId="195"/>
-    <cellStyle name="Normal 2 2 3 3 2" xfId="265"/>
-    <cellStyle name="Normal 2 2 3 3 3" xfId="377"/>
-    <cellStyle name="Normal 2 2 3 3 4" xfId="462"/>
-    <cellStyle name="Normal 2 2 3 3 4 2" xfId="816"/>
-    <cellStyle name="Normal 2 2 3 3 5" xfId="524"/>
-    <cellStyle name="Normal 2 2 3 3 6" xfId="612"/>
-    <cellStyle name="Normal 2 2 3 3 6 2" xfId="877"/>
-    <cellStyle name="Normal 2 2 3 3 7" xfId="687"/>
-    <cellStyle name="Normal 2 2 3 3 7 2" xfId="949"/>
-    <cellStyle name="Normal 2 2 3 3 8" xfId="753"/>
-    <cellStyle name="Normal 2 2 3 4" xfId="262"/>
-    <cellStyle name="Normal 2 2 3 5" xfId="354"/>
-    <cellStyle name="Normal 2 2 3 6" xfId="450"/>
-    <cellStyle name="Normal 2 2 3 6 2" xfId="804"/>
-    <cellStyle name="Normal 2 2 3 7" xfId="521"/>
-    <cellStyle name="Normal 2 2 3 8" xfId="609"/>
-    <cellStyle name="Normal 2 2 3 8 2" xfId="874"/>
-    <cellStyle name="Normal 2 2 3 9" xfId="662"/>
-    <cellStyle name="Normal 2 2 3 9 2" xfId="924"/>
-    <cellStyle name="Normal 2 2 4" xfId="170"/>
-    <cellStyle name="Normal 2 2 4 2" xfId="378"/>
-    <cellStyle name="Normal 2 2 4 3" xfId="525"/>
-    <cellStyle name="Normal 2 2 5" xfId="186"/>
-    <cellStyle name="Normal 2 2 5 2" xfId="379"/>
-    <cellStyle name="Normal 2 2 5 3" xfId="526"/>
-    <cellStyle name="Normal 2 2 6" xfId="183"/>
-    <cellStyle name="Normal 2 2 6 2" xfId="380"/>
-    <cellStyle name="Normal 2 2 6 3" xfId="527"/>
-    <cellStyle name="Normal 2 2 7" xfId="144"/>
-    <cellStyle name="Normal 2 2 7 2" xfId="381"/>
-    <cellStyle name="Normal 2 2 7 3" xfId="528"/>
-    <cellStyle name="Normal 2 2 8" xfId="261"/>
-    <cellStyle name="Normal 2 2 9" xfId="374"/>
-    <cellStyle name="Normal 2 3" xfId="55"/>
-    <cellStyle name="Normal 2 3 10" xfId="727"/>
-    <cellStyle name="Normal 2 3 11" xfId="158"/>
-    <cellStyle name="Normal 2 3 2" xfId="179"/>
-    <cellStyle name="Normal 2 3 2 2" xfId="205"/>
-    <cellStyle name="Normal 2 3 2 2 2" xfId="268"/>
-    <cellStyle name="Normal 2 3 2 2 3" xfId="371"/>
-    <cellStyle name="Normal 2 3 2 2 4" xfId="472"/>
-    <cellStyle name="Normal 2 3 2 2 4 2" xfId="826"/>
-    <cellStyle name="Normal 2 3 2 2 5" xfId="531"/>
-    <cellStyle name="Normal 2 3 2 2 6" xfId="615"/>
-    <cellStyle name="Normal 2 3 2 2 6 2" xfId="880"/>
-    <cellStyle name="Normal 2 3 2 2 7" xfId="697"/>
-    <cellStyle name="Normal 2 3 2 2 7 2" xfId="959"/>
-    <cellStyle name="Normal 2 3 2 2 8" xfId="763"/>
-    <cellStyle name="Normal 2 3 2 3" xfId="267"/>
-    <cellStyle name="Normal 2 3 2 4" xfId="384"/>
-    <cellStyle name="Normal 2 3 2 5" xfId="445"/>
-    <cellStyle name="Normal 2 3 2 5 2" xfId="799"/>
-    <cellStyle name="Normal 2 3 2 6" xfId="530"/>
-    <cellStyle name="Normal 2 3 2 7" xfId="614"/>
-    <cellStyle name="Normal 2 3 2 7 2" xfId="879"/>
-    <cellStyle name="Normal 2 3 2 8" xfId="674"/>
-    <cellStyle name="Normal 2 3 2 8 2" xfId="936"/>
-    <cellStyle name="Normal 2 3 2 9" xfId="740"/>
-    <cellStyle name="Normal 2 3 3" xfId="194"/>
-    <cellStyle name="Normal 2 3 3 2" xfId="269"/>
-    <cellStyle name="Normal 2 3 3 3" xfId="385"/>
-    <cellStyle name="Normal 2 3 3 4" xfId="461"/>
-    <cellStyle name="Normal 2 3 3 4 2" xfId="815"/>
-    <cellStyle name="Normal 2 3 3 5" xfId="532"/>
-    <cellStyle name="Normal 2 3 3 6" xfId="616"/>
-    <cellStyle name="Normal 2 3 3 6 2" xfId="881"/>
-    <cellStyle name="Normal 2 3 3 7" xfId="686"/>
-    <cellStyle name="Normal 2 3 3 7 2" xfId="948"/>
-    <cellStyle name="Normal 2 3 3 8" xfId="752"/>
-    <cellStyle name="Normal 2 3 4" xfId="266"/>
-    <cellStyle name="Normal 2 3 5" xfId="383"/>
-    <cellStyle name="Normal 2 3 6" xfId="427"/>
-    <cellStyle name="Normal 2 3 6 2" xfId="781"/>
-    <cellStyle name="Normal 2 3 7" xfId="529"/>
-    <cellStyle name="Normal 2 3 8" xfId="613"/>
-    <cellStyle name="Normal 2 3 8 2" xfId="878"/>
-    <cellStyle name="Normal 2 3 9" xfId="661"/>
-    <cellStyle name="Normal 2 3 9 2" xfId="923"/>
-    <cellStyle name="Normal 2 4" xfId="51"/>
-    <cellStyle name="Normal 2 4 10" xfId="169"/>
-    <cellStyle name="Normal 2 4 11" xfId="96"/>
-    <cellStyle name="Normal 2 4 2" xfId="197"/>
-    <cellStyle name="Normal 2 4 2 2" xfId="271"/>
-    <cellStyle name="Normal 2 4 2 3" xfId="387"/>
-    <cellStyle name="Normal 2 4 2 4" xfId="464"/>
-    <cellStyle name="Normal 2 4 2 4 2" xfId="818"/>
-    <cellStyle name="Normal 2 4 2 5" xfId="534"/>
-    <cellStyle name="Normal 2 4 2 6" xfId="618"/>
-    <cellStyle name="Normal 2 4 2 6 2" xfId="883"/>
-    <cellStyle name="Normal 2 4 2 7" xfId="689"/>
-    <cellStyle name="Normal 2 4 2 7 2" xfId="951"/>
-    <cellStyle name="Normal 2 4 2 8" xfId="755"/>
-    <cellStyle name="Normal 2 4 3" xfId="270"/>
-    <cellStyle name="Normal 2 4 4" xfId="386"/>
-    <cellStyle name="Normal 2 4 5" xfId="423"/>
-    <cellStyle name="Normal 2 4 5 2" xfId="777"/>
-    <cellStyle name="Normal 2 4 6" xfId="533"/>
-    <cellStyle name="Normal 2 4 7" xfId="617"/>
-    <cellStyle name="Normal 2 4 7 2" xfId="882"/>
-    <cellStyle name="Normal 2 4 8" xfId="670"/>
-    <cellStyle name="Normal 2 4 8 2" xfId="932"/>
-    <cellStyle name="Normal 2 4 9" xfId="736"/>
-    <cellStyle name="Normal 2 5" xfId="57"/>
-    <cellStyle name="Normal 2 5 2" xfId="272"/>
-    <cellStyle name="Normal 2 5 3" xfId="388"/>
-    <cellStyle name="Normal 2 5 4" xfId="434"/>
-    <cellStyle name="Normal 2 5 4 2" xfId="788"/>
-    <cellStyle name="Normal 2 5 5" xfId="535"/>
-    <cellStyle name="Normal 2 5 6" xfId="619"/>
-    <cellStyle name="Normal 2 5 6 2" xfId="884"/>
-    <cellStyle name="Normal 2 5 7" xfId="678"/>
-    <cellStyle name="Normal 2 5 7 2" xfId="940"/>
-    <cellStyle name="Normal 2 5 8" xfId="744"/>
-    <cellStyle name="Normal 2 5 9" xfId="185"/>
-    <cellStyle name="Normal 2 6" xfId="143"/>
-    <cellStyle name="Normal 2 6 2" xfId="389"/>
-    <cellStyle name="Normal 2 6 3" xfId="422"/>
-    <cellStyle name="Normal 2 6 3 2" xfId="776"/>
-    <cellStyle name="Normal 2 6 4" xfId="536"/>
-    <cellStyle name="Normal 2 6 5" xfId="620"/>
-    <cellStyle name="Normal 2 6 5 2" xfId="885"/>
-    <cellStyle name="Normal 2 6 6" xfId="667"/>
-    <cellStyle name="Normal 2 6 6 2" xfId="929"/>
-    <cellStyle name="Normal 2 6 7" xfId="773"/>
-    <cellStyle name="Normal 2 6 8" xfId="733"/>
-    <cellStyle name="Normal 2 6 9" xfId="273"/>
-    <cellStyle name="Normal 2 7" xfId="260"/>
-    <cellStyle name="Normal 2 8" xfId="373"/>
-    <cellStyle name="Normal 2 9" xfId="439"/>
-    <cellStyle name="Normal 2 9 2" xfId="793"/>
-    <cellStyle name="Normal 20" xfId="224"/>
-    <cellStyle name="Normal 21" xfId="288"/>
-    <cellStyle name="Normal 22" xfId="428"/>
-    <cellStyle name="Normal 22 2" xfId="782"/>
-    <cellStyle name="Normal 23" xfId="584"/>
-    <cellStyle name="Normal 23 2" xfId="849"/>
-    <cellStyle name="Normal 24" xfId="635"/>
-    <cellStyle name="Normal 24 2" xfId="897"/>
-    <cellStyle name="Normal 25" xfId="767"/>
-    <cellStyle name="Normal 26" xfId="701"/>
-    <cellStyle name="Normal 27" xfId="120"/>
-    <cellStyle name="Normal 27 2" xfId="390"/>
-    <cellStyle name="Normal 27 3" xfId="537"/>
-    <cellStyle name="Normal 28" xfId="121"/>
-    <cellStyle name="Normal 28 2" xfId="391"/>
-    <cellStyle name="Normal 28 3" xfId="538"/>
-    <cellStyle name="Normal 29" xfId="1021"/>
-    <cellStyle name="Normal 3" xfId="3"/>
-    <cellStyle name="Normal 3 2" xfId="48"/>
-    <cellStyle name="Normal 3 2 2" xfId="161"/>
-    <cellStyle name="Normal 3 2 2 2" xfId="393"/>
-    <cellStyle name="Normal 3 2 3" xfId="223"/>
-    <cellStyle name="Normal 3 2 3 2" xfId="540"/>
-    <cellStyle name="Normal 3 2 4" xfId="140"/>
-    <cellStyle name="Normal 3 3" xfId="53"/>
-    <cellStyle name="Normal 3 3 2" xfId="394"/>
-    <cellStyle name="Normal 3 3 3" xfId="541"/>
-    <cellStyle name="Normal 3 3 4" xfId="171"/>
-    <cellStyle name="Normal 3 4" xfId="56"/>
-    <cellStyle name="Normal 3 4 2" xfId="395"/>
-    <cellStyle name="Normal 3 4 3" xfId="542"/>
-    <cellStyle name="Normal 3 5" xfId="184"/>
-    <cellStyle name="Normal 3 5 2" xfId="274"/>
-    <cellStyle name="Normal 3 5 3" xfId="396"/>
-    <cellStyle name="Normal 3 5 4" xfId="440"/>
-    <cellStyle name="Normal 3 5 4 2" xfId="794"/>
-    <cellStyle name="Normal 3 5 5" xfId="543"/>
-    <cellStyle name="Normal 3 5 6" xfId="621"/>
-    <cellStyle name="Normal 3 5 6 2" xfId="886"/>
-    <cellStyle name="Normal 3 5 7" xfId="677"/>
-    <cellStyle name="Normal 3 5 7 2" xfId="939"/>
-    <cellStyle name="Normal 3 5 8" xfId="743"/>
-    <cellStyle name="Normal 3 6" xfId="145"/>
-    <cellStyle name="Normal 3 6 2" xfId="397"/>
-    <cellStyle name="Normal 3 6 3" xfId="544"/>
-    <cellStyle name="Normal 3 7" xfId="392"/>
-    <cellStyle name="Normal 3 8" xfId="539"/>
-    <cellStyle name="Normal 3 9" xfId="1022"/>
-    <cellStyle name="Normal 4" xfId="1"/>
-    <cellStyle name="Normal 4 2" xfId="47"/>
-    <cellStyle name="Normal 4 2 2" xfId="49"/>
-    <cellStyle name="Normal 4 2 2 2" xfId="399"/>
-    <cellStyle name="Normal 4 2 3" xfId="546"/>
-    <cellStyle name="Normal 4 2 4" xfId="162"/>
-    <cellStyle name="Normal 4 2 5" xfId="103"/>
-    <cellStyle name="Normal 4 3" xfId="45"/>
-    <cellStyle name="Normal 4 3 2" xfId="400"/>
-    <cellStyle name="Normal 4 3 3" xfId="547"/>
-    <cellStyle name="Normal 4 4" xfId="398"/>
-    <cellStyle name="Normal 4 5" xfId="545"/>
-    <cellStyle name="Normal 4 6" xfId="1023"/>
-    <cellStyle name="Normal 5" xfId="54"/>
-    <cellStyle name="Normal 5 2" xfId="127"/>
-    <cellStyle name="Normal 5 2 2" xfId="163"/>
-    <cellStyle name="Normal 5 2 2 2" xfId="401"/>
-    <cellStyle name="Normal 5 2 3" xfId="222"/>
-    <cellStyle name="Normal 5 2 3 2" xfId="548"/>
-    <cellStyle name="Normal 5 3" xfId="124"/>
-    <cellStyle name="Normal 5 3 2" xfId="220"/>
-    <cellStyle name="Normal 5 3 2 2" xfId="328"/>
-    <cellStyle name="Normal 5 3 3" xfId="210"/>
-    <cellStyle name="Normal 5 3 3 2" xfId="549"/>
-    <cellStyle name="Normal 5 4" xfId="146"/>
-    <cellStyle name="Normal 5 4 2" xfId="275"/>
-    <cellStyle name="Normal 5 5" xfId="632"/>
-    <cellStyle name="Normal 5 6" xfId="115"/>
-    <cellStyle name="Normal 6" xfId="50"/>
-    <cellStyle name="Normal 6 2" xfId="164"/>
-    <cellStyle name="Normal 6 2 2" xfId="403"/>
-    <cellStyle name="Normal 6 2 3" xfId="551"/>
-    <cellStyle name="Normal 6 3" xfId="147"/>
-    <cellStyle name="Normal 6 3 2" xfId="360"/>
-    <cellStyle name="Normal 6 3 3" xfId="552"/>
-    <cellStyle name="Normal 6 4" xfId="221"/>
-    <cellStyle name="Normal 6 4 2" xfId="402"/>
-    <cellStyle name="Normal 6 5" xfId="550"/>
-    <cellStyle name="Normal 6 6" xfId="126"/>
-    <cellStyle name="Normal 7" xfId="117"/>
-    <cellStyle name="Normal 7 2" xfId="165"/>
-    <cellStyle name="Normal 7 2 2" xfId="334"/>
-    <cellStyle name="Normal 7 2 3" xfId="554"/>
-    <cellStyle name="Normal 7 3" xfId="276"/>
-    <cellStyle name="Normal 7 3 2" xfId="405"/>
-    <cellStyle name="Normal 7 3 3" xfId="555"/>
-    <cellStyle name="Normal 7 4" xfId="404"/>
-    <cellStyle name="Normal 7 5" xfId="553"/>
-    <cellStyle name="Normal 8" xfId="148"/>
-    <cellStyle name="Normal 8 2" xfId="166"/>
-    <cellStyle name="Normal 8 2 2" xfId="407"/>
-    <cellStyle name="Normal 8 2 3" xfId="557"/>
-    <cellStyle name="Normal 8 3" xfId="277"/>
-    <cellStyle name="Normal 8 3 2" xfId="408"/>
-    <cellStyle name="Normal 8 3 3" xfId="558"/>
-    <cellStyle name="Normal 8 4" xfId="406"/>
-    <cellStyle name="Normal 8 5" xfId="556"/>
-    <cellStyle name="Normal 9" xfId="149"/>
-    <cellStyle name="Normal 9 10" xfId="622"/>
-    <cellStyle name="Normal 9 10 2" xfId="887"/>
-    <cellStyle name="Normal 9 11" xfId="655"/>
-    <cellStyle name="Normal 9 11 2" xfId="917"/>
-    <cellStyle name="Normal 9 12" xfId="721"/>
-    <cellStyle name="Normal 9 2" xfId="167"/>
-    <cellStyle name="Normal 9 2 10" xfId="729"/>
-    <cellStyle name="Normal 9 2 2" xfId="181"/>
-    <cellStyle name="Normal 9 2 2 2" xfId="207"/>
-    <cellStyle name="Normal 9 2 2 2 2" xfId="281"/>
-    <cellStyle name="Normal 9 2 2 2 3" xfId="411"/>
-    <cellStyle name="Normal 9 2 2 2 4" xfId="474"/>
-    <cellStyle name="Normal 9 2 2 2 4 2" xfId="828"/>
-    <cellStyle name="Normal 9 2 2 2 5" xfId="562"/>
-    <cellStyle name="Normal 9 2 2 2 6" xfId="625"/>
-    <cellStyle name="Normal 9 2 2 2 6 2" xfId="890"/>
-    <cellStyle name="Normal 9 2 2 2 7" xfId="699"/>
-    <cellStyle name="Normal 9 2 2 2 7 2" xfId="961"/>
-    <cellStyle name="Normal 9 2 2 2 8" xfId="765"/>
-    <cellStyle name="Normal 9 2 2 3" xfId="280"/>
-    <cellStyle name="Normal 9 2 2 4" xfId="410"/>
-    <cellStyle name="Normal 9 2 2 5" xfId="437"/>
-    <cellStyle name="Normal 9 2 2 5 2" xfId="791"/>
-    <cellStyle name="Normal 9 2 2 6" xfId="561"/>
-    <cellStyle name="Normal 9 2 2 7" xfId="624"/>
-    <cellStyle name="Normal 9 2 2 7 2" xfId="889"/>
-    <cellStyle name="Normal 9 2 2 8" xfId="676"/>
-    <cellStyle name="Normal 9 2 2 8 2" xfId="938"/>
-    <cellStyle name="Normal 9 2 2 9" xfId="742"/>
-    <cellStyle name="Normal 9 2 3" xfId="196"/>
-    <cellStyle name="Normal 9 2 3 2" xfId="282"/>
-    <cellStyle name="Normal 9 2 3 3" xfId="412"/>
-    <cellStyle name="Normal 9 2 3 4" xfId="463"/>
-    <cellStyle name="Normal 9 2 3 4 2" xfId="817"/>
-    <cellStyle name="Normal 9 2 3 5" xfId="563"/>
-    <cellStyle name="Normal 9 2 3 6" xfId="626"/>
-    <cellStyle name="Normal 9 2 3 6 2" xfId="891"/>
-    <cellStyle name="Normal 9 2 3 7" xfId="688"/>
-    <cellStyle name="Normal 9 2 3 7 2" xfId="950"/>
-    <cellStyle name="Normal 9 2 3 8" xfId="754"/>
-    <cellStyle name="Normal 9 2 4" xfId="279"/>
-    <cellStyle name="Normal 9 2 5" xfId="382"/>
-    <cellStyle name="Normal 9 2 6" xfId="449"/>
-    <cellStyle name="Normal 9 2 6 2" xfId="803"/>
-    <cellStyle name="Normal 9 2 7" xfId="560"/>
-    <cellStyle name="Normal 9 2 8" xfId="623"/>
-    <cellStyle name="Normal 9 2 8 2" xfId="888"/>
-    <cellStyle name="Normal 9 2 9" xfId="663"/>
-    <cellStyle name="Normal 9 2 9 2" xfId="925"/>
-    <cellStyle name="Normal 9 3" xfId="172"/>
-    <cellStyle name="Normal 9 3 2" xfId="198"/>
-    <cellStyle name="Normal 9 3 2 2" xfId="284"/>
-    <cellStyle name="Normal 9 3 2 3" xfId="414"/>
-    <cellStyle name="Normal 9 3 2 4" xfId="465"/>
-    <cellStyle name="Normal 9 3 2 4 2" xfId="819"/>
-    <cellStyle name="Normal 9 3 2 5" xfId="565"/>
-    <cellStyle name="Normal 9 3 2 6" xfId="628"/>
-    <cellStyle name="Normal 9 3 2 6 2" xfId="893"/>
-    <cellStyle name="Normal 9 3 2 7" xfId="690"/>
-    <cellStyle name="Normal 9 3 2 7 2" xfId="952"/>
-    <cellStyle name="Normal 9 3 2 8" xfId="756"/>
-    <cellStyle name="Normal 9 3 3" xfId="283"/>
-    <cellStyle name="Normal 9 3 4" xfId="413"/>
-    <cellStyle name="Normal 9 3 5" xfId="425"/>
-    <cellStyle name="Normal 9 3 5 2" xfId="779"/>
-    <cellStyle name="Normal 9 3 6" xfId="564"/>
-    <cellStyle name="Normal 9 3 7" xfId="627"/>
-    <cellStyle name="Normal 9 3 7 2" xfId="892"/>
-    <cellStyle name="Normal 9 3 8" xfId="671"/>
-    <cellStyle name="Normal 9 3 8 2" xfId="933"/>
-    <cellStyle name="Normal 9 3 9" xfId="737"/>
-    <cellStyle name="Normal 9 4" xfId="187"/>
-    <cellStyle name="Normal 9 4 2" xfId="285"/>
-    <cellStyle name="Normal 9 4 3" xfId="415"/>
-    <cellStyle name="Normal 9 4 4" xfId="454"/>
-    <cellStyle name="Normal 9 4 4 2" xfId="808"/>
-    <cellStyle name="Normal 9 4 5" xfId="566"/>
-    <cellStyle name="Normal 9 4 6" xfId="629"/>
-    <cellStyle name="Normal 9 4 6 2" xfId="894"/>
-    <cellStyle name="Normal 9 4 7" xfId="679"/>
-    <cellStyle name="Normal 9 4 7 2" xfId="941"/>
-    <cellStyle name="Normal 9 4 8" xfId="745"/>
-    <cellStyle name="Normal 9 5" xfId="286"/>
-    <cellStyle name="Normal 9 5 2" xfId="416"/>
-    <cellStyle name="Normal 9 5 3" xfId="435"/>
-    <cellStyle name="Normal 9 5 3 2" xfId="789"/>
-    <cellStyle name="Normal 9 5 4" xfId="567"/>
-    <cellStyle name="Normal 9 5 5" xfId="630"/>
-    <cellStyle name="Normal 9 5 5 2" xfId="895"/>
-    <cellStyle name="Normal 9 5 6" xfId="668"/>
-    <cellStyle name="Normal 9 5 6 2" xfId="930"/>
-    <cellStyle name="Normal 9 5 7" xfId="774"/>
-    <cellStyle name="Normal 9 5 8" xfId="734"/>
-    <cellStyle name="Normal 9 6" xfId="278"/>
-    <cellStyle name="Normal 9 7" xfId="409"/>
-    <cellStyle name="Normal 9 8" xfId="426"/>
-    <cellStyle name="Normal 9 8 2" xfId="780"/>
-    <cellStyle name="Normal 9 9" xfId="559"/>
+    <cellStyle name="Normal 10" xfId="153" xr:uid="{00000000-0005-0000-0000-000017010000}"/>
+    <cellStyle name="Normal 10 10" xfId="714" xr:uid="{00000000-0005-0000-0000-000018010000}"/>
+    <cellStyle name="Normal 10 2" xfId="174" xr:uid="{00000000-0005-0000-0000-000019010000}"/>
+    <cellStyle name="Normal 10 2 2" xfId="200" xr:uid="{00000000-0005-0000-0000-00001A010000}"/>
+    <cellStyle name="Normal 10 2 2 2" xfId="229" xr:uid="{00000000-0005-0000-0000-00001B010000}"/>
+    <cellStyle name="Normal 10 2 2 3" xfId="337" xr:uid="{00000000-0005-0000-0000-00001C010000}"/>
+    <cellStyle name="Normal 10 2 2 4" xfId="467" xr:uid="{00000000-0005-0000-0000-00001D010000}"/>
+    <cellStyle name="Normal 10 2 2 4 2" xfId="821" xr:uid="{00000000-0005-0000-0000-00001E010000}"/>
+    <cellStyle name="Normal 10 2 2 5" xfId="486" xr:uid="{00000000-0005-0000-0000-00001F010000}"/>
+    <cellStyle name="Normal 10 2 2 6" xfId="572" xr:uid="{00000000-0005-0000-0000-000020010000}"/>
+    <cellStyle name="Normal 10 2 2 6 2" xfId="833" xr:uid="{00000000-0005-0000-0000-000021010000}"/>
+    <cellStyle name="Normal 10 2 2 7" xfId="692" xr:uid="{00000000-0005-0000-0000-000022010000}"/>
+    <cellStyle name="Normal 10 2 2 7 2" xfId="954" xr:uid="{00000000-0005-0000-0000-000023010000}"/>
+    <cellStyle name="Normal 10 2 2 8" xfId="758" xr:uid="{00000000-0005-0000-0000-000024010000}"/>
+    <cellStyle name="Normal 10 2 3" xfId="228" xr:uid="{00000000-0005-0000-0000-000025010000}"/>
+    <cellStyle name="Normal 10 2 4" xfId="333" xr:uid="{00000000-0005-0000-0000-000026010000}"/>
+    <cellStyle name="Normal 10 2 5" xfId="438" xr:uid="{00000000-0005-0000-0000-000027010000}"/>
+    <cellStyle name="Normal 10 2 5 2" xfId="792" xr:uid="{00000000-0005-0000-0000-000028010000}"/>
+    <cellStyle name="Normal 10 2 6" xfId="485" xr:uid="{00000000-0005-0000-0000-000029010000}"/>
+    <cellStyle name="Normal 10 2 7" xfId="573" xr:uid="{00000000-0005-0000-0000-00002A010000}"/>
+    <cellStyle name="Normal 10 2 7 2" xfId="834" xr:uid="{00000000-0005-0000-0000-00002B010000}"/>
+    <cellStyle name="Normal 10 2 8" xfId="656" xr:uid="{00000000-0005-0000-0000-00002C010000}"/>
+    <cellStyle name="Normal 10 2 8 2" xfId="918" xr:uid="{00000000-0005-0000-0000-00002D010000}"/>
+    <cellStyle name="Normal 10 2 9" xfId="722" xr:uid="{00000000-0005-0000-0000-00002E010000}"/>
+    <cellStyle name="Normal 10 3" xfId="189" xr:uid="{00000000-0005-0000-0000-00002F010000}"/>
+    <cellStyle name="Normal 10 3 2" xfId="230" xr:uid="{00000000-0005-0000-0000-000030010000}"/>
+    <cellStyle name="Normal 10 3 3" xfId="292" xr:uid="{00000000-0005-0000-0000-000031010000}"/>
+    <cellStyle name="Normal 10 3 4" xfId="456" xr:uid="{00000000-0005-0000-0000-000032010000}"/>
+    <cellStyle name="Normal 10 3 4 2" xfId="810" xr:uid="{00000000-0005-0000-0000-000033010000}"/>
+    <cellStyle name="Normal 10 3 5" xfId="487" xr:uid="{00000000-0005-0000-0000-000034010000}"/>
+    <cellStyle name="Normal 10 3 6" xfId="571" xr:uid="{00000000-0005-0000-0000-000035010000}"/>
+    <cellStyle name="Normal 10 3 6 2" xfId="832" xr:uid="{00000000-0005-0000-0000-000036010000}"/>
+    <cellStyle name="Normal 10 3 7" xfId="681" xr:uid="{00000000-0005-0000-0000-000037010000}"/>
+    <cellStyle name="Normal 10 3 7 2" xfId="943" xr:uid="{00000000-0005-0000-0000-000038010000}"/>
+    <cellStyle name="Normal 10 3 8" xfId="747" xr:uid="{00000000-0005-0000-0000-000039010000}"/>
+    <cellStyle name="Normal 10 4" xfId="227" xr:uid="{00000000-0005-0000-0000-00003A010000}"/>
+    <cellStyle name="Normal 10 5" xfId="351" xr:uid="{00000000-0005-0000-0000-00003B010000}"/>
+    <cellStyle name="Normal 10 6" xfId="446" xr:uid="{00000000-0005-0000-0000-00003C010000}"/>
+    <cellStyle name="Normal 10 6 2" xfId="800" xr:uid="{00000000-0005-0000-0000-00003D010000}"/>
+    <cellStyle name="Normal 10 7" xfId="484" xr:uid="{00000000-0005-0000-0000-00003E010000}"/>
+    <cellStyle name="Normal 10 8" xfId="574" xr:uid="{00000000-0005-0000-0000-00003F010000}"/>
+    <cellStyle name="Normal 10 8 2" xfId="835" xr:uid="{00000000-0005-0000-0000-000040010000}"/>
+    <cellStyle name="Normal 10 9" xfId="648" xr:uid="{00000000-0005-0000-0000-000041010000}"/>
+    <cellStyle name="Normal 10 9 2" xfId="910" xr:uid="{00000000-0005-0000-0000-000042010000}"/>
+    <cellStyle name="Normal 11" xfId="150" xr:uid="{00000000-0005-0000-0000-000043010000}"/>
+    <cellStyle name="Normal 11 10" xfId="570" xr:uid="{00000000-0005-0000-0000-000044010000}"/>
+    <cellStyle name="Normal 11 10 2" xfId="831" xr:uid="{00000000-0005-0000-0000-000045010000}"/>
+    <cellStyle name="Normal 11 11" xfId="649" xr:uid="{00000000-0005-0000-0000-000046010000}"/>
+    <cellStyle name="Normal 11 11 2" xfId="911" xr:uid="{00000000-0005-0000-0000-000047010000}"/>
+    <cellStyle name="Normal 11 12" xfId="715" xr:uid="{00000000-0005-0000-0000-000048010000}"/>
+    <cellStyle name="Normal 11 2" xfId="154" xr:uid="{00000000-0005-0000-0000-000049010000}"/>
+    <cellStyle name="Normal 11 2 10" xfId="723" xr:uid="{00000000-0005-0000-0000-00004A010000}"/>
+    <cellStyle name="Normal 11 2 2" xfId="175" xr:uid="{00000000-0005-0000-0000-00004B010000}"/>
+    <cellStyle name="Normal 11 2 2 2" xfId="201" xr:uid="{00000000-0005-0000-0000-00004C010000}"/>
+    <cellStyle name="Normal 11 2 2 2 2" xfId="234" xr:uid="{00000000-0005-0000-0000-00004D010000}"/>
+    <cellStyle name="Normal 11 2 2 2 3" xfId="345" xr:uid="{00000000-0005-0000-0000-00004E010000}"/>
+    <cellStyle name="Normal 11 2 2 2 4" xfId="468" xr:uid="{00000000-0005-0000-0000-00004F010000}"/>
+    <cellStyle name="Normal 11 2 2 2 4 2" xfId="822" xr:uid="{00000000-0005-0000-0000-000050010000}"/>
+    <cellStyle name="Normal 11 2 2 2 5" xfId="491" xr:uid="{00000000-0005-0000-0000-000051010000}"/>
+    <cellStyle name="Normal 11 2 2 2 6" xfId="586" xr:uid="{00000000-0005-0000-0000-000052010000}"/>
+    <cellStyle name="Normal 11 2 2 2 6 2" xfId="851" xr:uid="{00000000-0005-0000-0000-000053010000}"/>
+    <cellStyle name="Normal 11 2 2 2 7" xfId="693" xr:uid="{00000000-0005-0000-0000-000054010000}"/>
+    <cellStyle name="Normal 11 2 2 2 7 2" xfId="955" xr:uid="{00000000-0005-0000-0000-000055010000}"/>
+    <cellStyle name="Normal 11 2 2 2 8" xfId="759" xr:uid="{00000000-0005-0000-0000-000056010000}"/>
+    <cellStyle name="Normal 11 2 2 3" xfId="233" xr:uid="{00000000-0005-0000-0000-000057010000}"/>
+    <cellStyle name="Normal 11 2 2 4" xfId="293" xr:uid="{00000000-0005-0000-0000-000058010000}"/>
+    <cellStyle name="Normal 11 2 2 5" xfId="443" xr:uid="{00000000-0005-0000-0000-000059010000}"/>
+    <cellStyle name="Normal 11 2 2 5 2" xfId="797" xr:uid="{00000000-0005-0000-0000-00005A010000}"/>
+    <cellStyle name="Normal 11 2 2 6" xfId="490" xr:uid="{00000000-0005-0000-0000-00005B010000}"/>
+    <cellStyle name="Normal 11 2 2 7" xfId="585" xr:uid="{00000000-0005-0000-0000-00005C010000}"/>
+    <cellStyle name="Normal 11 2 2 7 2" xfId="850" xr:uid="{00000000-0005-0000-0000-00005D010000}"/>
+    <cellStyle name="Normal 11 2 2 8" xfId="673" xr:uid="{00000000-0005-0000-0000-00005E010000}"/>
+    <cellStyle name="Normal 11 2 2 8 2" xfId="935" xr:uid="{00000000-0005-0000-0000-00005F010000}"/>
+    <cellStyle name="Normal 11 2 2 9" xfId="739" xr:uid="{00000000-0005-0000-0000-000060010000}"/>
+    <cellStyle name="Normal 11 2 3" xfId="190" xr:uid="{00000000-0005-0000-0000-000061010000}"/>
+    <cellStyle name="Normal 11 2 3 2" xfId="235" xr:uid="{00000000-0005-0000-0000-000062010000}"/>
+    <cellStyle name="Normal 11 2 3 3" xfId="340" xr:uid="{00000000-0005-0000-0000-000063010000}"/>
+    <cellStyle name="Normal 11 2 3 4" xfId="457" xr:uid="{00000000-0005-0000-0000-000064010000}"/>
+    <cellStyle name="Normal 11 2 3 4 2" xfId="811" xr:uid="{00000000-0005-0000-0000-000065010000}"/>
+    <cellStyle name="Normal 11 2 3 5" xfId="492" xr:uid="{00000000-0005-0000-0000-000066010000}"/>
+    <cellStyle name="Normal 11 2 3 6" xfId="587" xr:uid="{00000000-0005-0000-0000-000067010000}"/>
+    <cellStyle name="Normal 11 2 3 6 2" xfId="852" xr:uid="{00000000-0005-0000-0000-000068010000}"/>
+    <cellStyle name="Normal 11 2 3 7" xfId="682" xr:uid="{00000000-0005-0000-0000-000069010000}"/>
+    <cellStyle name="Normal 11 2 3 7 2" xfId="944" xr:uid="{00000000-0005-0000-0000-00006A010000}"/>
+    <cellStyle name="Normal 11 2 3 8" xfId="748" xr:uid="{00000000-0005-0000-0000-00006B010000}"/>
+    <cellStyle name="Normal 11 2 4" xfId="232" xr:uid="{00000000-0005-0000-0000-00006C010000}"/>
+    <cellStyle name="Normal 11 2 5" xfId="308" xr:uid="{00000000-0005-0000-0000-00006D010000}"/>
+    <cellStyle name="Normal 11 2 6" xfId="447" xr:uid="{00000000-0005-0000-0000-00006E010000}"/>
+    <cellStyle name="Normal 11 2 6 2" xfId="801" xr:uid="{00000000-0005-0000-0000-00006F010000}"/>
+    <cellStyle name="Normal 11 2 7" xfId="489" xr:uid="{00000000-0005-0000-0000-000070010000}"/>
+    <cellStyle name="Normal 11 2 8" xfId="592" xr:uid="{00000000-0005-0000-0000-000071010000}"/>
+    <cellStyle name="Normal 11 2 8 2" xfId="857" xr:uid="{00000000-0005-0000-0000-000072010000}"/>
+    <cellStyle name="Normal 11 2 9" xfId="657" xr:uid="{00000000-0005-0000-0000-000073010000}"/>
+    <cellStyle name="Normal 11 2 9 2" xfId="919" xr:uid="{00000000-0005-0000-0000-000074010000}"/>
+    <cellStyle name="Normal 11 3" xfId="173" xr:uid="{00000000-0005-0000-0000-000075010000}"/>
+    <cellStyle name="Normal 11 3 2" xfId="199" xr:uid="{00000000-0005-0000-0000-000076010000}"/>
+    <cellStyle name="Normal 11 3 2 2" xfId="237" xr:uid="{00000000-0005-0000-0000-000077010000}"/>
+    <cellStyle name="Normal 11 3 2 3" xfId="346" xr:uid="{00000000-0005-0000-0000-000078010000}"/>
+    <cellStyle name="Normal 11 3 2 4" xfId="466" xr:uid="{00000000-0005-0000-0000-000079010000}"/>
+    <cellStyle name="Normal 11 3 2 4 2" xfId="820" xr:uid="{00000000-0005-0000-0000-00007A010000}"/>
+    <cellStyle name="Normal 11 3 2 5" xfId="494" xr:uid="{00000000-0005-0000-0000-00007B010000}"/>
+    <cellStyle name="Normal 11 3 2 6" xfId="589" xr:uid="{00000000-0005-0000-0000-00007C010000}"/>
+    <cellStyle name="Normal 11 3 2 6 2" xfId="854" xr:uid="{00000000-0005-0000-0000-00007D010000}"/>
+    <cellStyle name="Normal 11 3 2 7" xfId="691" xr:uid="{00000000-0005-0000-0000-00007E010000}"/>
+    <cellStyle name="Normal 11 3 2 7 2" xfId="953" xr:uid="{00000000-0005-0000-0000-00007F010000}"/>
+    <cellStyle name="Normal 11 3 2 8" xfId="757" xr:uid="{00000000-0005-0000-0000-000080010000}"/>
+    <cellStyle name="Normal 11 3 3" xfId="236" xr:uid="{00000000-0005-0000-0000-000081010000}"/>
+    <cellStyle name="Normal 11 3 4" xfId="310" xr:uid="{00000000-0005-0000-0000-000082010000}"/>
+    <cellStyle name="Normal 11 3 5" xfId="451" xr:uid="{00000000-0005-0000-0000-000083010000}"/>
+    <cellStyle name="Normal 11 3 5 2" xfId="805" xr:uid="{00000000-0005-0000-0000-000084010000}"/>
+    <cellStyle name="Normal 11 3 6" xfId="493" xr:uid="{00000000-0005-0000-0000-000085010000}"/>
+    <cellStyle name="Normal 11 3 7" xfId="588" xr:uid="{00000000-0005-0000-0000-000086010000}"/>
+    <cellStyle name="Normal 11 3 7 2" xfId="853" xr:uid="{00000000-0005-0000-0000-000087010000}"/>
+    <cellStyle name="Normal 11 3 8" xfId="672" xr:uid="{00000000-0005-0000-0000-000088010000}"/>
+    <cellStyle name="Normal 11 3 8 2" xfId="934" xr:uid="{00000000-0005-0000-0000-000089010000}"/>
+    <cellStyle name="Normal 11 3 9" xfId="738" xr:uid="{00000000-0005-0000-0000-00008A010000}"/>
+    <cellStyle name="Normal 11 4" xfId="188" xr:uid="{00000000-0005-0000-0000-00008B010000}"/>
+    <cellStyle name="Normal 11 4 2" xfId="238" xr:uid="{00000000-0005-0000-0000-00008C010000}"/>
+    <cellStyle name="Normal 11 4 3" xfId="343" xr:uid="{00000000-0005-0000-0000-00008D010000}"/>
+    <cellStyle name="Normal 11 4 4" xfId="455" xr:uid="{00000000-0005-0000-0000-00008E010000}"/>
+    <cellStyle name="Normal 11 4 4 2" xfId="809" xr:uid="{00000000-0005-0000-0000-00008F010000}"/>
+    <cellStyle name="Normal 11 4 5" xfId="495" xr:uid="{00000000-0005-0000-0000-000090010000}"/>
+    <cellStyle name="Normal 11 4 6" xfId="590" xr:uid="{00000000-0005-0000-0000-000091010000}"/>
+    <cellStyle name="Normal 11 4 6 2" xfId="855" xr:uid="{00000000-0005-0000-0000-000092010000}"/>
+    <cellStyle name="Normal 11 4 7" xfId="680" xr:uid="{00000000-0005-0000-0000-000093010000}"/>
+    <cellStyle name="Normal 11 4 7 2" xfId="942" xr:uid="{00000000-0005-0000-0000-000094010000}"/>
+    <cellStyle name="Normal 11 4 8" xfId="746" xr:uid="{00000000-0005-0000-0000-000095010000}"/>
+    <cellStyle name="Normal 11 5" xfId="239" xr:uid="{00000000-0005-0000-0000-000096010000}"/>
+    <cellStyle name="Normal 11 5 2" xfId="353" xr:uid="{00000000-0005-0000-0000-000097010000}"/>
+    <cellStyle name="Normal 11 5 3" xfId="424" xr:uid="{00000000-0005-0000-0000-000098010000}"/>
+    <cellStyle name="Normal 11 5 3 2" xfId="778" xr:uid="{00000000-0005-0000-0000-000099010000}"/>
+    <cellStyle name="Normal 11 5 4" xfId="496" xr:uid="{00000000-0005-0000-0000-00009A010000}"/>
+    <cellStyle name="Normal 11 5 5" xfId="591" xr:uid="{00000000-0005-0000-0000-00009B010000}"/>
+    <cellStyle name="Normal 11 5 5 2" xfId="856" xr:uid="{00000000-0005-0000-0000-00009C010000}"/>
+    <cellStyle name="Normal 11 5 6" xfId="669" xr:uid="{00000000-0005-0000-0000-00009D010000}"/>
+    <cellStyle name="Normal 11 5 6 2" xfId="931" xr:uid="{00000000-0005-0000-0000-00009E010000}"/>
+    <cellStyle name="Normal 11 5 7" xfId="768" xr:uid="{00000000-0005-0000-0000-00009F010000}"/>
+    <cellStyle name="Normal 11 5 8" xfId="735" xr:uid="{00000000-0005-0000-0000-0000A0010000}"/>
+    <cellStyle name="Normal 11 6" xfId="231" xr:uid="{00000000-0005-0000-0000-0000A1010000}"/>
+    <cellStyle name="Normal 11 7" xfId="326" xr:uid="{00000000-0005-0000-0000-0000A2010000}"/>
+    <cellStyle name="Normal 11 8" xfId="448" xr:uid="{00000000-0005-0000-0000-0000A3010000}"/>
+    <cellStyle name="Normal 11 8 2" xfId="802" xr:uid="{00000000-0005-0000-0000-0000A4010000}"/>
+    <cellStyle name="Normal 11 9" xfId="488" xr:uid="{00000000-0005-0000-0000-0000A5010000}"/>
+    <cellStyle name="Normal 12" xfId="155" xr:uid="{00000000-0005-0000-0000-0000A6010000}"/>
+    <cellStyle name="Normal 12 10" xfId="716" xr:uid="{00000000-0005-0000-0000-0000A7010000}"/>
+    <cellStyle name="Normal 12 2" xfId="176" xr:uid="{00000000-0005-0000-0000-0000A8010000}"/>
+    <cellStyle name="Normal 12 2 2" xfId="202" xr:uid="{00000000-0005-0000-0000-0000A9010000}"/>
+    <cellStyle name="Normal 12 2 2 2" xfId="242" xr:uid="{00000000-0005-0000-0000-0000AA010000}"/>
+    <cellStyle name="Normal 12 2 2 3" xfId="348" xr:uid="{00000000-0005-0000-0000-0000AB010000}"/>
+    <cellStyle name="Normal 12 2 2 4" xfId="469" xr:uid="{00000000-0005-0000-0000-0000AC010000}"/>
+    <cellStyle name="Normal 12 2 2 4 2" xfId="823" xr:uid="{00000000-0005-0000-0000-0000AD010000}"/>
+    <cellStyle name="Normal 12 2 2 5" xfId="499" xr:uid="{00000000-0005-0000-0000-0000AE010000}"/>
+    <cellStyle name="Normal 12 2 2 6" xfId="595" xr:uid="{00000000-0005-0000-0000-0000AF010000}"/>
+    <cellStyle name="Normal 12 2 2 6 2" xfId="860" xr:uid="{00000000-0005-0000-0000-0000B0010000}"/>
+    <cellStyle name="Normal 12 2 2 7" xfId="694" xr:uid="{00000000-0005-0000-0000-0000B1010000}"/>
+    <cellStyle name="Normal 12 2 2 7 2" xfId="956" xr:uid="{00000000-0005-0000-0000-0000B2010000}"/>
+    <cellStyle name="Normal 12 2 2 8" xfId="760" xr:uid="{00000000-0005-0000-0000-0000B3010000}"/>
+    <cellStyle name="Normal 12 2 3" xfId="241" xr:uid="{00000000-0005-0000-0000-0000B4010000}"/>
+    <cellStyle name="Normal 12 2 4" xfId="347" xr:uid="{00000000-0005-0000-0000-0000B5010000}"/>
+    <cellStyle name="Normal 12 2 5" xfId="442" xr:uid="{00000000-0005-0000-0000-0000B6010000}"/>
+    <cellStyle name="Normal 12 2 5 2" xfId="796" xr:uid="{00000000-0005-0000-0000-0000B7010000}"/>
+    <cellStyle name="Normal 12 2 6" xfId="498" xr:uid="{00000000-0005-0000-0000-0000B8010000}"/>
+    <cellStyle name="Normal 12 2 7" xfId="594" xr:uid="{00000000-0005-0000-0000-0000B9010000}"/>
+    <cellStyle name="Normal 12 2 7 2" xfId="859" xr:uid="{00000000-0005-0000-0000-0000BA010000}"/>
+    <cellStyle name="Normal 12 2 8" xfId="658" xr:uid="{00000000-0005-0000-0000-0000BB010000}"/>
+    <cellStyle name="Normal 12 2 8 2" xfId="920" xr:uid="{00000000-0005-0000-0000-0000BC010000}"/>
+    <cellStyle name="Normal 12 2 9" xfId="724" xr:uid="{00000000-0005-0000-0000-0000BD010000}"/>
+    <cellStyle name="Normal 12 3" xfId="191" xr:uid="{00000000-0005-0000-0000-0000BE010000}"/>
+    <cellStyle name="Normal 12 3 2" xfId="243" xr:uid="{00000000-0005-0000-0000-0000BF010000}"/>
+    <cellStyle name="Normal 12 3 3" xfId="295" xr:uid="{00000000-0005-0000-0000-0000C0010000}"/>
+    <cellStyle name="Normal 12 3 4" xfId="458" xr:uid="{00000000-0005-0000-0000-0000C1010000}"/>
+    <cellStyle name="Normal 12 3 4 2" xfId="812" xr:uid="{00000000-0005-0000-0000-0000C2010000}"/>
+    <cellStyle name="Normal 12 3 5" xfId="500" xr:uid="{00000000-0005-0000-0000-0000C3010000}"/>
+    <cellStyle name="Normal 12 3 6" xfId="596" xr:uid="{00000000-0005-0000-0000-0000C4010000}"/>
+    <cellStyle name="Normal 12 3 6 2" xfId="861" xr:uid="{00000000-0005-0000-0000-0000C5010000}"/>
+    <cellStyle name="Normal 12 3 7" xfId="683" xr:uid="{00000000-0005-0000-0000-0000C6010000}"/>
+    <cellStyle name="Normal 12 3 7 2" xfId="945" xr:uid="{00000000-0005-0000-0000-0000C7010000}"/>
+    <cellStyle name="Normal 12 3 8" xfId="749" xr:uid="{00000000-0005-0000-0000-0000C8010000}"/>
+    <cellStyle name="Normal 12 4" xfId="240" xr:uid="{00000000-0005-0000-0000-0000C9010000}"/>
+    <cellStyle name="Normal 12 5" xfId="352" xr:uid="{00000000-0005-0000-0000-0000CA010000}"/>
+    <cellStyle name="Normal 12 6" xfId="436" xr:uid="{00000000-0005-0000-0000-0000CB010000}"/>
+    <cellStyle name="Normal 12 6 2" xfId="790" xr:uid="{00000000-0005-0000-0000-0000CC010000}"/>
+    <cellStyle name="Normal 12 7" xfId="497" xr:uid="{00000000-0005-0000-0000-0000CD010000}"/>
+    <cellStyle name="Normal 12 8" xfId="593" xr:uid="{00000000-0005-0000-0000-0000CE010000}"/>
+    <cellStyle name="Normal 12 8 2" xfId="858" xr:uid="{00000000-0005-0000-0000-0000CF010000}"/>
+    <cellStyle name="Normal 12 9" xfId="650" xr:uid="{00000000-0005-0000-0000-0000D0010000}"/>
+    <cellStyle name="Normal 12 9 2" xfId="912" xr:uid="{00000000-0005-0000-0000-0000D1010000}"/>
+    <cellStyle name="Normal 13" xfId="156" xr:uid="{00000000-0005-0000-0000-0000D2010000}"/>
+    <cellStyle name="Normal 13 10" xfId="717" xr:uid="{00000000-0005-0000-0000-0000D3010000}"/>
+    <cellStyle name="Normal 13 2" xfId="177" xr:uid="{00000000-0005-0000-0000-0000D4010000}"/>
+    <cellStyle name="Normal 13 2 2" xfId="203" xr:uid="{00000000-0005-0000-0000-0000D5010000}"/>
+    <cellStyle name="Normal 13 2 2 2" xfId="246" xr:uid="{00000000-0005-0000-0000-0000D6010000}"/>
+    <cellStyle name="Normal 13 2 2 3" xfId="355" xr:uid="{00000000-0005-0000-0000-0000D7010000}"/>
+    <cellStyle name="Normal 13 2 2 4" xfId="470" xr:uid="{00000000-0005-0000-0000-0000D8010000}"/>
+    <cellStyle name="Normal 13 2 2 4 2" xfId="824" xr:uid="{00000000-0005-0000-0000-0000D9010000}"/>
+    <cellStyle name="Normal 13 2 2 5" xfId="503" xr:uid="{00000000-0005-0000-0000-0000DA010000}"/>
+    <cellStyle name="Normal 13 2 2 6" xfId="599" xr:uid="{00000000-0005-0000-0000-0000DB010000}"/>
+    <cellStyle name="Normal 13 2 2 6 2" xfId="864" xr:uid="{00000000-0005-0000-0000-0000DC010000}"/>
+    <cellStyle name="Normal 13 2 2 7" xfId="695" xr:uid="{00000000-0005-0000-0000-0000DD010000}"/>
+    <cellStyle name="Normal 13 2 2 7 2" xfId="957" xr:uid="{00000000-0005-0000-0000-0000DE010000}"/>
+    <cellStyle name="Normal 13 2 2 8" xfId="761" xr:uid="{00000000-0005-0000-0000-0000DF010000}"/>
+    <cellStyle name="Normal 13 2 3" xfId="245" xr:uid="{00000000-0005-0000-0000-0000E0010000}"/>
+    <cellStyle name="Normal 13 2 4" xfId="350" xr:uid="{00000000-0005-0000-0000-0000E1010000}"/>
+    <cellStyle name="Normal 13 2 5" xfId="453" xr:uid="{00000000-0005-0000-0000-0000E2010000}"/>
+    <cellStyle name="Normal 13 2 5 2" xfId="807" xr:uid="{00000000-0005-0000-0000-0000E3010000}"/>
+    <cellStyle name="Normal 13 2 6" xfId="502" xr:uid="{00000000-0005-0000-0000-0000E4010000}"/>
+    <cellStyle name="Normal 13 2 7" xfId="598" xr:uid="{00000000-0005-0000-0000-0000E5010000}"/>
+    <cellStyle name="Normal 13 2 7 2" xfId="863" xr:uid="{00000000-0005-0000-0000-0000E6010000}"/>
+    <cellStyle name="Normal 13 2 8" xfId="659" xr:uid="{00000000-0005-0000-0000-0000E7010000}"/>
+    <cellStyle name="Normal 13 2 8 2" xfId="921" xr:uid="{00000000-0005-0000-0000-0000E8010000}"/>
+    <cellStyle name="Normal 13 2 9" xfId="725" xr:uid="{00000000-0005-0000-0000-0000E9010000}"/>
+    <cellStyle name="Normal 13 3" xfId="192" xr:uid="{00000000-0005-0000-0000-0000EA010000}"/>
+    <cellStyle name="Normal 13 3 2" xfId="247" xr:uid="{00000000-0005-0000-0000-0000EB010000}"/>
+    <cellStyle name="Normal 13 3 3" xfId="356" xr:uid="{00000000-0005-0000-0000-0000EC010000}"/>
+    <cellStyle name="Normal 13 3 4" xfId="459" xr:uid="{00000000-0005-0000-0000-0000ED010000}"/>
+    <cellStyle name="Normal 13 3 4 2" xfId="813" xr:uid="{00000000-0005-0000-0000-0000EE010000}"/>
+    <cellStyle name="Normal 13 3 5" xfId="504" xr:uid="{00000000-0005-0000-0000-0000EF010000}"/>
+    <cellStyle name="Normal 13 3 6" xfId="600" xr:uid="{00000000-0005-0000-0000-0000F0010000}"/>
+    <cellStyle name="Normal 13 3 6 2" xfId="865" xr:uid="{00000000-0005-0000-0000-0000F1010000}"/>
+    <cellStyle name="Normal 13 3 7" xfId="684" xr:uid="{00000000-0005-0000-0000-0000F2010000}"/>
+    <cellStyle name="Normal 13 3 7 2" xfId="946" xr:uid="{00000000-0005-0000-0000-0000F3010000}"/>
+    <cellStyle name="Normal 13 3 8" xfId="750" xr:uid="{00000000-0005-0000-0000-0000F4010000}"/>
+    <cellStyle name="Normal 13 4" xfId="244" xr:uid="{00000000-0005-0000-0000-0000F5010000}"/>
+    <cellStyle name="Normal 13 5" xfId="349" xr:uid="{00000000-0005-0000-0000-0000F6010000}"/>
+    <cellStyle name="Normal 13 6" xfId="444" xr:uid="{00000000-0005-0000-0000-0000F7010000}"/>
+    <cellStyle name="Normal 13 6 2" xfId="798" xr:uid="{00000000-0005-0000-0000-0000F8010000}"/>
+    <cellStyle name="Normal 13 7" xfId="501" xr:uid="{00000000-0005-0000-0000-0000F9010000}"/>
+    <cellStyle name="Normal 13 8" xfId="597" xr:uid="{00000000-0005-0000-0000-0000FA010000}"/>
+    <cellStyle name="Normal 13 8 2" xfId="862" xr:uid="{00000000-0005-0000-0000-0000FB010000}"/>
+    <cellStyle name="Normal 13 9" xfId="651" xr:uid="{00000000-0005-0000-0000-0000FC010000}"/>
+    <cellStyle name="Normal 13 9 2" xfId="913" xr:uid="{00000000-0005-0000-0000-0000FD010000}"/>
+    <cellStyle name="Normal 14" xfId="157" xr:uid="{00000000-0005-0000-0000-0000FE010000}"/>
+    <cellStyle name="Normal 14 10" xfId="718" xr:uid="{00000000-0005-0000-0000-0000FF010000}"/>
+    <cellStyle name="Normal 14 2" xfId="178" xr:uid="{00000000-0005-0000-0000-000000020000}"/>
+    <cellStyle name="Normal 14 2 2" xfId="204" xr:uid="{00000000-0005-0000-0000-000001020000}"/>
+    <cellStyle name="Normal 14 2 2 2" xfId="250" xr:uid="{00000000-0005-0000-0000-000002020000}"/>
+    <cellStyle name="Normal 14 2 2 3" xfId="359" xr:uid="{00000000-0005-0000-0000-000003020000}"/>
+    <cellStyle name="Normal 14 2 2 4" xfId="471" xr:uid="{00000000-0005-0000-0000-000004020000}"/>
+    <cellStyle name="Normal 14 2 2 4 2" xfId="825" xr:uid="{00000000-0005-0000-0000-000005020000}"/>
+    <cellStyle name="Normal 14 2 2 5" xfId="507" xr:uid="{00000000-0005-0000-0000-000006020000}"/>
+    <cellStyle name="Normal 14 2 2 6" xfId="603" xr:uid="{00000000-0005-0000-0000-000007020000}"/>
+    <cellStyle name="Normal 14 2 2 6 2" xfId="868" xr:uid="{00000000-0005-0000-0000-000008020000}"/>
+    <cellStyle name="Normal 14 2 2 7" xfId="696" xr:uid="{00000000-0005-0000-0000-000009020000}"/>
+    <cellStyle name="Normal 14 2 2 7 2" xfId="958" xr:uid="{00000000-0005-0000-0000-00000A020000}"/>
+    <cellStyle name="Normal 14 2 2 8" xfId="762" xr:uid="{00000000-0005-0000-0000-00000B020000}"/>
+    <cellStyle name="Normal 14 2 3" xfId="249" xr:uid="{00000000-0005-0000-0000-00000C020000}"/>
+    <cellStyle name="Normal 14 2 4" xfId="358" xr:uid="{00000000-0005-0000-0000-00000D020000}"/>
+    <cellStyle name="Normal 14 2 5" xfId="452" xr:uid="{00000000-0005-0000-0000-00000E020000}"/>
+    <cellStyle name="Normal 14 2 5 2" xfId="806" xr:uid="{00000000-0005-0000-0000-00000F020000}"/>
+    <cellStyle name="Normal 14 2 6" xfId="506" xr:uid="{00000000-0005-0000-0000-000010020000}"/>
+    <cellStyle name="Normal 14 2 7" xfId="602" xr:uid="{00000000-0005-0000-0000-000011020000}"/>
+    <cellStyle name="Normal 14 2 7 2" xfId="867" xr:uid="{00000000-0005-0000-0000-000012020000}"/>
+    <cellStyle name="Normal 14 2 8" xfId="660" xr:uid="{00000000-0005-0000-0000-000013020000}"/>
+    <cellStyle name="Normal 14 2 8 2" xfId="922" xr:uid="{00000000-0005-0000-0000-000014020000}"/>
+    <cellStyle name="Normal 14 2 9" xfId="726" xr:uid="{00000000-0005-0000-0000-000015020000}"/>
+    <cellStyle name="Normal 14 3" xfId="193" xr:uid="{00000000-0005-0000-0000-000016020000}"/>
+    <cellStyle name="Normal 14 3 2" xfId="251" xr:uid="{00000000-0005-0000-0000-000017020000}"/>
+    <cellStyle name="Normal 14 3 3" xfId="362" xr:uid="{00000000-0005-0000-0000-000018020000}"/>
+    <cellStyle name="Normal 14 3 4" xfId="460" xr:uid="{00000000-0005-0000-0000-000019020000}"/>
+    <cellStyle name="Normal 14 3 4 2" xfId="814" xr:uid="{00000000-0005-0000-0000-00001A020000}"/>
+    <cellStyle name="Normal 14 3 5" xfId="508" xr:uid="{00000000-0005-0000-0000-00001B020000}"/>
+    <cellStyle name="Normal 14 3 6" xfId="604" xr:uid="{00000000-0005-0000-0000-00001C020000}"/>
+    <cellStyle name="Normal 14 3 6 2" xfId="869" xr:uid="{00000000-0005-0000-0000-00001D020000}"/>
+    <cellStyle name="Normal 14 3 7" xfId="685" xr:uid="{00000000-0005-0000-0000-00001E020000}"/>
+    <cellStyle name="Normal 14 3 7 2" xfId="947" xr:uid="{00000000-0005-0000-0000-00001F020000}"/>
+    <cellStyle name="Normal 14 3 8" xfId="751" xr:uid="{00000000-0005-0000-0000-000020020000}"/>
+    <cellStyle name="Normal 14 4" xfId="248" xr:uid="{00000000-0005-0000-0000-000021020000}"/>
+    <cellStyle name="Normal 14 5" xfId="357" xr:uid="{00000000-0005-0000-0000-000022020000}"/>
+    <cellStyle name="Normal 14 6" xfId="431" xr:uid="{00000000-0005-0000-0000-000023020000}"/>
+    <cellStyle name="Normal 14 6 2" xfId="785" xr:uid="{00000000-0005-0000-0000-000024020000}"/>
+    <cellStyle name="Normal 14 7" xfId="505" xr:uid="{00000000-0005-0000-0000-000025020000}"/>
+    <cellStyle name="Normal 14 8" xfId="601" xr:uid="{00000000-0005-0000-0000-000026020000}"/>
+    <cellStyle name="Normal 14 8 2" xfId="866" xr:uid="{00000000-0005-0000-0000-000027020000}"/>
+    <cellStyle name="Normal 14 9" xfId="652" xr:uid="{00000000-0005-0000-0000-000028020000}"/>
+    <cellStyle name="Normal 14 9 2" xfId="914" xr:uid="{00000000-0005-0000-0000-000029020000}"/>
+    <cellStyle name="Normal 15" xfId="152" xr:uid="{00000000-0005-0000-0000-00002A020000}"/>
+    <cellStyle name="Normal 15 10" xfId="730" xr:uid="{00000000-0005-0000-0000-00002B020000}"/>
+    <cellStyle name="Normal 15 2" xfId="58" xr:uid="{00000000-0005-0000-0000-00002C020000}"/>
+    <cellStyle name="Normal 15 2 2" xfId="364" xr:uid="{00000000-0005-0000-0000-00002D020000}"/>
+    <cellStyle name="Normal 15 2 3" xfId="510" xr:uid="{00000000-0005-0000-0000-00002E020000}"/>
+    <cellStyle name="Normal 15 3" xfId="253" xr:uid="{00000000-0005-0000-0000-00002F020000}"/>
+    <cellStyle name="Normal 15 3 2" xfId="365" xr:uid="{00000000-0005-0000-0000-000030020000}"/>
+    <cellStyle name="Normal 15 3 3" xfId="511" xr:uid="{00000000-0005-0000-0000-000031020000}"/>
+    <cellStyle name="Normal 15 4" xfId="252" xr:uid="{00000000-0005-0000-0000-000032020000}"/>
+    <cellStyle name="Normal 15 5" xfId="363" xr:uid="{00000000-0005-0000-0000-000033020000}"/>
+    <cellStyle name="Normal 15 6" xfId="430" xr:uid="{00000000-0005-0000-0000-000034020000}"/>
+    <cellStyle name="Normal 15 6 2" xfId="784" xr:uid="{00000000-0005-0000-0000-000035020000}"/>
+    <cellStyle name="Normal 15 7" xfId="509" xr:uid="{00000000-0005-0000-0000-000036020000}"/>
+    <cellStyle name="Normal 15 8" xfId="605" xr:uid="{00000000-0005-0000-0000-000037020000}"/>
+    <cellStyle name="Normal 15 8 2" xfId="870" xr:uid="{00000000-0005-0000-0000-000038020000}"/>
+    <cellStyle name="Normal 15 9" xfId="664" xr:uid="{00000000-0005-0000-0000-000039020000}"/>
+    <cellStyle name="Normal 15 9 2" xfId="926" xr:uid="{00000000-0005-0000-0000-00003A020000}"/>
+    <cellStyle name="Normal 16" xfId="142" xr:uid="{00000000-0005-0000-0000-00003B020000}"/>
+    <cellStyle name="Normal 16 2" xfId="209" xr:uid="{00000000-0005-0000-0000-00003C020000}"/>
+    <cellStyle name="Normal 16 2 2" xfId="367" xr:uid="{00000000-0005-0000-0000-00003D020000}"/>
+    <cellStyle name="Normal 16 2 3" xfId="475" xr:uid="{00000000-0005-0000-0000-00003E020000}"/>
+    <cellStyle name="Normal 16 2 3 2" xfId="829" xr:uid="{00000000-0005-0000-0000-00003F020000}"/>
+    <cellStyle name="Normal 16 2 4" xfId="513" xr:uid="{00000000-0005-0000-0000-000040020000}"/>
+    <cellStyle name="Normal 16 2 5" xfId="606" xr:uid="{00000000-0005-0000-0000-000041020000}"/>
+    <cellStyle name="Normal 16 2 5 2" xfId="871" xr:uid="{00000000-0005-0000-0000-000042020000}"/>
+    <cellStyle name="Normal 16 2 6" xfId="700" xr:uid="{00000000-0005-0000-0000-000043020000}"/>
+    <cellStyle name="Normal 16 2 6 2" xfId="962" xr:uid="{00000000-0005-0000-0000-000044020000}"/>
+    <cellStyle name="Normal 16 2 7" xfId="769" xr:uid="{00000000-0005-0000-0000-000045020000}"/>
+    <cellStyle name="Normal 16 2 8" xfId="766" xr:uid="{00000000-0005-0000-0000-000046020000}"/>
+    <cellStyle name="Normal 16 2 9" xfId="255" xr:uid="{00000000-0005-0000-0000-000047020000}"/>
+    <cellStyle name="Normal 16 3" xfId="256" xr:uid="{00000000-0005-0000-0000-000048020000}"/>
+    <cellStyle name="Normal 16 3 2" xfId="368" xr:uid="{00000000-0005-0000-0000-000049020000}"/>
+    <cellStyle name="Normal 16 3 3" xfId="514" xr:uid="{00000000-0005-0000-0000-00004A020000}"/>
+    <cellStyle name="Normal 16 4" xfId="254" xr:uid="{00000000-0005-0000-0000-00004B020000}"/>
+    <cellStyle name="Normal 16 5" xfId="366" xr:uid="{00000000-0005-0000-0000-00004C020000}"/>
+    <cellStyle name="Normal 16 6" xfId="512" xr:uid="{00000000-0005-0000-0000-00004D020000}"/>
+    <cellStyle name="Normal 17" xfId="257" xr:uid="{00000000-0005-0000-0000-00004E020000}"/>
+    <cellStyle name="Normal 17 2" xfId="369" xr:uid="{00000000-0005-0000-0000-00004F020000}"/>
+    <cellStyle name="Normal 17 3" xfId="515" xr:uid="{00000000-0005-0000-0000-000050020000}"/>
+    <cellStyle name="Normal 17 4" xfId="770" xr:uid="{00000000-0005-0000-0000-000051020000}"/>
+    <cellStyle name="Normal 18" xfId="258" xr:uid="{00000000-0005-0000-0000-000052020000}"/>
+    <cellStyle name="Normal 18 2" xfId="370" xr:uid="{00000000-0005-0000-0000-000053020000}"/>
+    <cellStyle name="Normal 18 3" xfId="516" xr:uid="{00000000-0005-0000-0000-000054020000}"/>
+    <cellStyle name="Normal 18 4" xfId="771" xr:uid="{00000000-0005-0000-0000-000055020000}"/>
+    <cellStyle name="Normal 19" xfId="259" xr:uid="{00000000-0005-0000-0000-000056020000}"/>
+    <cellStyle name="Normal 19 2" xfId="372" xr:uid="{00000000-0005-0000-0000-000057020000}"/>
+    <cellStyle name="Normal 19 3" xfId="517" xr:uid="{00000000-0005-0000-0000-000058020000}"/>
+    <cellStyle name="Normal 19 4" xfId="772" xr:uid="{00000000-0005-0000-0000-000059020000}"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-00005A020000}"/>
+    <cellStyle name="Normal 2 10" xfId="518" xr:uid="{00000000-0005-0000-0000-00005B020000}"/>
+    <cellStyle name="Normal 2 11" xfId="607" xr:uid="{00000000-0005-0000-0000-00005C020000}"/>
+    <cellStyle name="Normal 2 11 2" xfId="872" xr:uid="{00000000-0005-0000-0000-00005D020000}"/>
+    <cellStyle name="Normal 2 12" xfId="653" xr:uid="{00000000-0005-0000-0000-00005E020000}"/>
+    <cellStyle name="Normal 2 12 2" xfId="915" xr:uid="{00000000-0005-0000-0000-00005F020000}"/>
+    <cellStyle name="Normal 2 13" xfId="719" xr:uid="{00000000-0005-0000-0000-000060020000}"/>
+    <cellStyle name="Normal 2 14" xfId="983" xr:uid="{00000000-0005-0000-0000-000061020000}"/>
+    <cellStyle name="Normal 2 2" xfId="52" xr:uid="{00000000-0005-0000-0000-000062020000}"/>
+    <cellStyle name="Normal 2 2 10" xfId="429" xr:uid="{00000000-0005-0000-0000-000063020000}"/>
+    <cellStyle name="Normal 2 2 10 2" xfId="783" xr:uid="{00000000-0005-0000-0000-000064020000}"/>
+    <cellStyle name="Normal 2 2 11" xfId="519" xr:uid="{00000000-0005-0000-0000-000065020000}"/>
+    <cellStyle name="Normal 2 2 12" xfId="608" xr:uid="{00000000-0005-0000-0000-000066020000}"/>
+    <cellStyle name="Normal 2 2 12 2" xfId="873" xr:uid="{00000000-0005-0000-0000-000067020000}"/>
+    <cellStyle name="Normal 2 2 13" xfId="654" xr:uid="{00000000-0005-0000-0000-000068020000}"/>
+    <cellStyle name="Normal 2 2 13 2" xfId="916" xr:uid="{00000000-0005-0000-0000-000069020000}"/>
+    <cellStyle name="Normal 2 2 14" xfId="720" xr:uid="{00000000-0005-0000-0000-00006A020000}"/>
+    <cellStyle name="Normal 2 2 15" xfId="119" xr:uid="{00000000-0005-0000-0000-00006B020000}"/>
+    <cellStyle name="Normal 2 2 2" xfId="160" xr:uid="{00000000-0005-0000-0000-00006C020000}"/>
+    <cellStyle name="Normal 2 2 2 2" xfId="342" xr:uid="{00000000-0005-0000-0000-00006D020000}"/>
+    <cellStyle name="Normal 2 2 2 3" xfId="520" xr:uid="{00000000-0005-0000-0000-00006E020000}"/>
+    <cellStyle name="Normal 2 2 3" xfId="159" xr:uid="{00000000-0005-0000-0000-00006F020000}"/>
+    <cellStyle name="Normal 2 2 3 10" xfId="728" xr:uid="{00000000-0005-0000-0000-000070020000}"/>
+    <cellStyle name="Normal 2 2 3 2" xfId="180" xr:uid="{00000000-0005-0000-0000-000071020000}"/>
+    <cellStyle name="Normal 2 2 3 2 2" xfId="206" xr:uid="{00000000-0005-0000-0000-000072020000}"/>
+    <cellStyle name="Normal 2 2 3 2 2 2" xfId="264" xr:uid="{00000000-0005-0000-0000-000073020000}"/>
+    <cellStyle name="Normal 2 2 3 2 2 3" xfId="376" xr:uid="{00000000-0005-0000-0000-000074020000}"/>
+    <cellStyle name="Normal 2 2 3 2 2 4" xfId="473" xr:uid="{00000000-0005-0000-0000-000075020000}"/>
+    <cellStyle name="Normal 2 2 3 2 2 4 2" xfId="827" xr:uid="{00000000-0005-0000-0000-000076020000}"/>
+    <cellStyle name="Normal 2 2 3 2 2 5" xfId="523" xr:uid="{00000000-0005-0000-0000-000077020000}"/>
+    <cellStyle name="Normal 2 2 3 2 2 6" xfId="611" xr:uid="{00000000-0005-0000-0000-000078020000}"/>
+    <cellStyle name="Normal 2 2 3 2 2 6 2" xfId="876" xr:uid="{00000000-0005-0000-0000-000079020000}"/>
+    <cellStyle name="Normal 2 2 3 2 2 7" xfId="698" xr:uid="{00000000-0005-0000-0000-00007A020000}"/>
+    <cellStyle name="Normal 2 2 3 2 2 7 2" xfId="960" xr:uid="{00000000-0005-0000-0000-00007B020000}"/>
+    <cellStyle name="Normal 2 2 3 2 2 8" xfId="764" xr:uid="{00000000-0005-0000-0000-00007C020000}"/>
+    <cellStyle name="Normal 2 2 3 2 3" xfId="263" xr:uid="{00000000-0005-0000-0000-00007D020000}"/>
+    <cellStyle name="Normal 2 2 3 2 4" xfId="375" xr:uid="{00000000-0005-0000-0000-00007E020000}"/>
+    <cellStyle name="Normal 2 2 3 2 5" xfId="433" xr:uid="{00000000-0005-0000-0000-00007F020000}"/>
+    <cellStyle name="Normal 2 2 3 2 5 2" xfId="787" xr:uid="{00000000-0005-0000-0000-000080020000}"/>
+    <cellStyle name="Normal 2 2 3 2 6" xfId="522" xr:uid="{00000000-0005-0000-0000-000081020000}"/>
+    <cellStyle name="Normal 2 2 3 2 7" xfId="610" xr:uid="{00000000-0005-0000-0000-000082020000}"/>
+    <cellStyle name="Normal 2 2 3 2 7 2" xfId="875" xr:uid="{00000000-0005-0000-0000-000083020000}"/>
+    <cellStyle name="Normal 2 2 3 2 8" xfId="675" xr:uid="{00000000-0005-0000-0000-000084020000}"/>
+    <cellStyle name="Normal 2 2 3 2 8 2" xfId="937" xr:uid="{00000000-0005-0000-0000-000085020000}"/>
+    <cellStyle name="Normal 2 2 3 2 9" xfId="741" xr:uid="{00000000-0005-0000-0000-000086020000}"/>
+    <cellStyle name="Normal 2 2 3 3" xfId="195" xr:uid="{00000000-0005-0000-0000-000087020000}"/>
+    <cellStyle name="Normal 2 2 3 3 2" xfId="265" xr:uid="{00000000-0005-0000-0000-000088020000}"/>
+    <cellStyle name="Normal 2 2 3 3 3" xfId="377" xr:uid="{00000000-0005-0000-0000-000089020000}"/>
+    <cellStyle name="Normal 2 2 3 3 4" xfId="462" xr:uid="{00000000-0005-0000-0000-00008A020000}"/>
+    <cellStyle name="Normal 2 2 3 3 4 2" xfId="816" xr:uid="{00000000-0005-0000-0000-00008B020000}"/>
+    <cellStyle name="Normal 2 2 3 3 5" xfId="524" xr:uid="{00000000-0005-0000-0000-00008C020000}"/>
+    <cellStyle name="Normal 2 2 3 3 6" xfId="612" xr:uid="{00000000-0005-0000-0000-00008D020000}"/>
+    <cellStyle name="Normal 2 2 3 3 6 2" xfId="877" xr:uid="{00000000-0005-0000-0000-00008E020000}"/>
+    <cellStyle name="Normal 2 2 3 3 7" xfId="687" xr:uid="{00000000-0005-0000-0000-00008F020000}"/>
+    <cellStyle name="Normal 2 2 3 3 7 2" xfId="949" xr:uid="{00000000-0005-0000-0000-000090020000}"/>
+    <cellStyle name="Normal 2 2 3 3 8" xfId="753" xr:uid="{00000000-0005-0000-0000-000091020000}"/>
+    <cellStyle name="Normal 2 2 3 4" xfId="262" xr:uid="{00000000-0005-0000-0000-000092020000}"/>
+    <cellStyle name="Normal 2 2 3 5" xfId="354" xr:uid="{00000000-0005-0000-0000-000093020000}"/>
+    <cellStyle name="Normal 2 2 3 6" xfId="450" xr:uid="{00000000-0005-0000-0000-000094020000}"/>
+    <cellStyle name="Normal 2 2 3 6 2" xfId="804" xr:uid="{00000000-0005-0000-0000-000095020000}"/>
+    <cellStyle name="Normal 2 2 3 7" xfId="521" xr:uid="{00000000-0005-0000-0000-000096020000}"/>
+    <cellStyle name="Normal 2 2 3 8" xfId="609" xr:uid="{00000000-0005-0000-0000-000097020000}"/>
+    <cellStyle name="Normal 2 2 3 8 2" xfId="874" xr:uid="{00000000-0005-0000-0000-000098020000}"/>
+    <cellStyle name="Normal 2 2 3 9" xfId="662" xr:uid="{00000000-0005-0000-0000-000099020000}"/>
+    <cellStyle name="Normal 2 2 3 9 2" xfId="924" xr:uid="{00000000-0005-0000-0000-00009A020000}"/>
+    <cellStyle name="Normal 2 2 4" xfId="170" xr:uid="{00000000-0005-0000-0000-00009B020000}"/>
+    <cellStyle name="Normal 2 2 4 2" xfId="378" xr:uid="{00000000-0005-0000-0000-00009C020000}"/>
+    <cellStyle name="Normal 2 2 4 3" xfId="525" xr:uid="{00000000-0005-0000-0000-00009D020000}"/>
+    <cellStyle name="Normal 2 2 5" xfId="186" xr:uid="{00000000-0005-0000-0000-00009E020000}"/>
+    <cellStyle name="Normal 2 2 5 2" xfId="379" xr:uid="{00000000-0005-0000-0000-00009F020000}"/>
+    <cellStyle name="Normal 2 2 5 3" xfId="526" xr:uid="{00000000-0005-0000-0000-0000A0020000}"/>
+    <cellStyle name="Normal 2 2 6" xfId="183" xr:uid="{00000000-0005-0000-0000-0000A1020000}"/>
+    <cellStyle name="Normal 2 2 6 2" xfId="380" xr:uid="{00000000-0005-0000-0000-0000A2020000}"/>
+    <cellStyle name="Normal 2 2 6 3" xfId="527" xr:uid="{00000000-0005-0000-0000-0000A3020000}"/>
+    <cellStyle name="Normal 2 2 7" xfId="144" xr:uid="{00000000-0005-0000-0000-0000A4020000}"/>
+    <cellStyle name="Normal 2 2 7 2" xfId="381" xr:uid="{00000000-0005-0000-0000-0000A5020000}"/>
+    <cellStyle name="Normal 2 2 7 3" xfId="528" xr:uid="{00000000-0005-0000-0000-0000A6020000}"/>
+    <cellStyle name="Normal 2 2 8" xfId="261" xr:uid="{00000000-0005-0000-0000-0000A7020000}"/>
+    <cellStyle name="Normal 2 2 9" xfId="374" xr:uid="{00000000-0005-0000-0000-0000A8020000}"/>
+    <cellStyle name="Normal 2 3" xfId="55" xr:uid="{00000000-0005-0000-0000-0000A9020000}"/>
+    <cellStyle name="Normal 2 3 10" xfId="727" xr:uid="{00000000-0005-0000-0000-0000AA020000}"/>
+    <cellStyle name="Normal 2 3 11" xfId="158" xr:uid="{00000000-0005-0000-0000-0000AB020000}"/>
+    <cellStyle name="Normal 2 3 2" xfId="179" xr:uid="{00000000-0005-0000-0000-0000AC020000}"/>
+    <cellStyle name="Normal 2 3 2 2" xfId="205" xr:uid="{00000000-0005-0000-0000-0000AD020000}"/>
+    <cellStyle name="Normal 2 3 2 2 2" xfId="268" xr:uid="{00000000-0005-0000-0000-0000AE020000}"/>
+    <cellStyle name="Normal 2 3 2 2 3" xfId="371" xr:uid="{00000000-0005-0000-0000-0000AF020000}"/>
+    <cellStyle name="Normal 2 3 2 2 4" xfId="472" xr:uid="{00000000-0005-0000-0000-0000B0020000}"/>
+    <cellStyle name="Normal 2 3 2 2 4 2" xfId="826" xr:uid="{00000000-0005-0000-0000-0000B1020000}"/>
+    <cellStyle name="Normal 2 3 2 2 5" xfId="531" xr:uid="{00000000-0005-0000-0000-0000B2020000}"/>
+    <cellStyle name="Normal 2 3 2 2 6" xfId="615" xr:uid="{00000000-0005-0000-0000-0000B3020000}"/>
+    <cellStyle name="Normal 2 3 2 2 6 2" xfId="880" xr:uid="{00000000-0005-0000-0000-0000B4020000}"/>
+    <cellStyle name="Normal 2 3 2 2 7" xfId="697" xr:uid="{00000000-0005-0000-0000-0000B5020000}"/>
+    <cellStyle name="Normal 2 3 2 2 7 2" xfId="959" xr:uid="{00000000-0005-0000-0000-0000B6020000}"/>
+    <cellStyle name="Normal 2 3 2 2 8" xfId="763" xr:uid="{00000000-0005-0000-0000-0000B7020000}"/>
+    <cellStyle name="Normal 2 3 2 3" xfId="267" xr:uid="{00000000-0005-0000-0000-0000B8020000}"/>
+    <cellStyle name="Normal 2 3 2 4" xfId="384" xr:uid="{00000000-0005-0000-0000-0000B9020000}"/>
+    <cellStyle name="Normal 2 3 2 5" xfId="445" xr:uid="{00000000-0005-0000-0000-0000BA020000}"/>
+    <cellStyle name="Normal 2 3 2 5 2" xfId="799" xr:uid="{00000000-0005-0000-0000-0000BB020000}"/>
+    <cellStyle name="Normal 2 3 2 6" xfId="530" xr:uid="{00000000-0005-0000-0000-0000BC020000}"/>
+    <cellStyle name="Normal 2 3 2 7" xfId="614" xr:uid="{00000000-0005-0000-0000-0000BD020000}"/>
+    <cellStyle name="Normal 2 3 2 7 2" xfId="879" xr:uid="{00000000-0005-0000-0000-0000BE020000}"/>
+    <cellStyle name="Normal 2 3 2 8" xfId="674" xr:uid="{00000000-0005-0000-0000-0000BF020000}"/>
+    <cellStyle name="Normal 2 3 2 8 2" xfId="936" xr:uid="{00000000-0005-0000-0000-0000C0020000}"/>
+    <cellStyle name="Normal 2 3 2 9" xfId="740" xr:uid="{00000000-0005-0000-0000-0000C1020000}"/>
+    <cellStyle name="Normal 2 3 3" xfId="194" xr:uid="{00000000-0005-0000-0000-0000C2020000}"/>
+    <cellStyle name="Normal 2 3 3 2" xfId="269" xr:uid="{00000000-0005-0000-0000-0000C3020000}"/>
+    <cellStyle name="Normal 2 3 3 3" xfId="385" xr:uid="{00000000-0005-0000-0000-0000C4020000}"/>
+    <cellStyle name="Normal 2 3 3 4" xfId="461" xr:uid="{00000000-0005-0000-0000-0000C5020000}"/>
+    <cellStyle name="Normal 2 3 3 4 2" xfId="815" xr:uid="{00000000-0005-0000-0000-0000C6020000}"/>
+    <cellStyle name="Normal 2 3 3 5" xfId="532" xr:uid="{00000000-0005-0000-0000-0000C7020000}"/>
+    <cellStyle name="Normal 2 3 3 6" xfId="616" xr:uid="{00000000-0005-0000-0000-0000C8020000}"/>
+    <cellStyle name="Normal 2 3 3 6 2" xfId="881" xr:uid="{00000000-0005-0000-0000-0000C9020000}"/>
+    <cellStyle name="Normal 2 3 3 7" xfId="686" xr:uid="{00000000-0005-0000-0000-0000CA020000}"/>
+    <cellStyle name="Normal 2 3 3 7 2" xfId="948" xr:uid="{00000000-0005-0000-0000-0000CB020000}"/>
+    <cellStyle name="Normal 2 3 3 8" xfId="752" xr:uid="{00000000-0005-0000-0000-0000CC020000}"/>
+    <cellStyle name="Normal 2 3 4" xfId="266" xr:uid="{00000000-0005-0000-0000-0000CD020000}"/>
+    <cellStyle name="Normal 2 3 5" xfId="383" xr:uid="{00000000-0005-0000-0000-0000CE020000}"/>
+    <cellStyle name="Normal 2 3 6" xfId="427" xr:uid="{00000000-0005-0000-0000-0000CF020000}"/>
+    <cellStyle name="Normal 2 3 6 2" xfId="781" xr:uid="{00000000-0005-0000-0000-0000D0020000}"/>
+    <cellStyle name="Normal 2 3 7" xfId="529" xr:uid="{00000000-0005-0000-0000-0000D1020000}"/>
+    <cellStyle name="Normal 2 3 8" xfId="613" xr:uid="{00000000-0005-0000-0000-0000D2020000}"/>
+    <cellStyle name="Normal 2 3 8 2" xfId="878" xr:uid="{00000000-0005-0000-0000-0000D3020000}"/>
+    <cellStyle name="Normal 2 3 9" xfId="661" xr:uid="{00000000-0005-0000-0000-0000D4020000}"/>
+    <cellStyle name="Normal 2 3 9 2" xfId="923" xr:uid="{00000000-0005-0000-0000-0000D5020000}"/>
+    <cellStyle name="Normal 2 4" xfId="51" xr:uid="{00000000-0005-0000-0000-0000D6020000}"/>
+    <cellStyle name="Normal 2 4 10" xfId="169" xr:uid="{00000000-0005-0000-0000-0000D7020000}"/>
+    <cellStyle name="Normal 2 4 11" xfId="96" xr:uid="{00000000-0005-0000-0000-0000D8020000}"/>
+    <cellStyle name="Normal 2 4 2" xfId="197" xr:uid="{00000000-0005-0000-0000-0000D9020000}"/>
+    <cellStyle name="Normal 2 4 2 2" xfId="271" xr:uid="{00000000-0005-0000-0000-0000DA020000}"/>
+    <cellStyle name="Normal 2 4 2 3" xfId="387" xr:uid="{00000000-0005-0000-0000-0000DB020000}"/>
+    <cellStyle name="Normal 2 4 2 4" xfId="464" xr:uid="{00000000-0005-0000-0000-0000DC020000}"/>
+    <cellStyle name="Normal 2 4 2 4 2" xfId="818" xr:uid="{00000000-0005-0000-0000-0000DD020000}"/>
+    <cellStyle name="Normal 2 4 2 5" xfId="534" xr:uid="{00000000-0005-0000-0000-0000DE020000}"/>
+    <cellStyle name="Normal 2 4 2 6" xfId="618" xr:uid="{00000000-0005-0000-0000-0000DF020000}"/>
+    <cellStyle name="Normal 2 4 2 6 2" xfId="883" xr:uid="{00000000-0005-0000-0000-0000E0020000}"/>
+    <cellStyle name="Normal 2 4 2 7" xfId="689" xr:uid="{00000000-0005-0000-0000-0000E1020000}"/>
+    <cellStyle name="Normal 2 4 2 7 2" xfId="951" xr:uid="{00000000-0005-0000-0000-0000E2020000}"/>
+    <cellStyle name="Normal 2 4 2 8" xfId="755" xr:uid="{00000000-0005-0000-0000-0000E3020000}"/>
+    <cellStyle name="Normal 2 4 3" xfId="270" xr:uid="{00000000-0005-0000-0000-0000E4020000}"/>
+    <cellStyle name="Normal 2 4 4" xfId="386" xr:uid="{00000000-0005-0000-0000-0000E5020000}"/>
+    <cellStyle name="Normal 2 4 5" xfId="423" xr:uid="{00000000-0005-0000-0000-0000E6020000}"/>
+    <cellStyle name="Normal 2 4 5 2" xfId="777" xr:uid="{00000000-0005-0000-0000-0000E7020000}"/>
+    <cellStyle name="Normal 2 4 6" xfId="533" xr:uid="{00000000-0005-0000-0000-0000E8020000}"/>
+    <cellStyle name="Normal 2 4 7" xfId="617" xr:uid="{00000000-0005-0000-0000-0000E9020000}"/>
+    <cellStyle name="Normal 2 4 7 2" xfId="882" xr:uid="{00000000-0005-0000-0000-0000EA020000}"/>
+    <cellStyle name="Normal 2 4 8" xfId="670" xr:uid="{00000000-0005-0000-0000-0000EB020000}"/>
+    <cellStyle name="Normal 2 4 8 2" xfId="932" xr:uid="{00000000-0005-0000-0000-0000EC020000}"/>
+    <cellStyle name="Normal 2 4 9" xfId="736" xr:uid="{00000000-0005-0000-0000-0000ED020000}"/>
+    <cellStyle name="Normal 2 5" xfId="57" xr:uid="{00000000-0005-0000-0000-0000EE020000}"/>
+    <cellStyle name="Normal 2 5 2" xfId="272" xr:uid="{00000000-0005-0000-0000-0000EF020000}"/>
+    <cellStyle name="Normal 2 5 3" xfId="388" xr:uid="{00000000-0005-0000-0000-0000F0020000}"/>
+    <cellStyle name="Normal 2 5 4" xfId="434" xr:uid="{00000000-0005-0000-0000-0000F1020000}"/>
+    <cellStyle name="Normal 2 5 4 2" xfId="788" xr:uid="{00000000-0005-0000-0000-0000F2020000}"/>
+    <cellStyle name="Normal 2 5 5" xfId="535" xr:uid="{00000000-0005-0000-0000-0000F3020000}"/>
+    <cellStyle name="Normal 2 5 6" xfId="619" xr:uid="{00000000-0005-0000-0000-0000F4020000}"/>
+    <cellStyle name="Normal 2 5 6 2" xfId="884" xr:uid="{00000000-0005-0000-0000-0000F5020000}"/>
+    <cellStyle name="Normal 2 5 7" xfId="678" xr:uid="{00000000-0005-0000-0000-0000F6020000}"/>
+    <cellStyle name="Normal 2 5 7 2" xfId="940" xr:uid="{00000000-0005-0000-0000-0000F7020000}"/>
+    <cellStyle name="Normal 2 5 8" xfId="744" xr:uid="{00000000-0005-0000-0000-0000F8020000}"/>
+    <cellStyle name="Normal 2 5 9" xfId="185" xr:uid="{00000000-0005-0000-0000-0000F9020000}"/>
+    <cellStyle name="Normal 2 6" xfId="143" xr:uid="{00000000-0005-0000-0000-0000FA020000}"/>
+    <cellStyle name="Normal 2 6 2" xfId="389" xr:uid="{00000000-0005-0000-0000-0000FB020000}"/>
+    <cellStyle name="Normal 2 6 3" xfId="422" xr:uid="{00000000-0005-0000-0000-0000FC020000}"/>
+    <cellStyle name="Normal 2 6 3 2" xfId="776" xr:uid="{00000000-0005-0000-0000-0000FD020000}"/>
+    <cellStyle name="Normal 2 6 4" xfId="536" xr:uid="{00000000-0005-0000-0000-0000FE020000}"/>
+    <cellStyle name="Normal 2 6 5" xfId="620" xr:uid="{00000000-0005-0000-0000-0000FF020000}"/>
+    <cellStyle name="Normal 2 6 5 2" xfId="885" xr:uid="{00000000-0005-0000-0000-000000030000}"/>
+    <cellStyle name="Normal 2 6 6" xfId="667" xr:uid="{00000000-0005-0000-0000-000001030000}"/>
+    <cellStyle name="Normal 2 6 6 2" xfId="929" xr:uid="{00000000-0005-0000-0000-000002030000}"/>
+    <cellStyle name="Normal 2 6 7" xfId="773" xr:uid="{00000000-0005-0000-0000-000003030000}"/>
+    <cellStyle name="Normal 2 6 8" xfId="733" xr:uid="{00000000-0005-0000-0000-000004030000}"/>
+    <cellStyle name="Normal 2 6 9" xfId="273" xr:uid="{00000000-0005-0000-0000-000005030000}"/>
+    <cellStyle name="Normal 2 7" xfId="260" xr:uid="{00000000-0005-0000-0000-000006030000}"/>
+    <cellStyle name="Normal 2 8" xfId="373" xr:uid="{00000000-0005-0000-0000-000007030000}"/>
+    <cellStyle name="Normal 2 9" xfId="439" xr:uid="{00000000-0005-0000-0000-000008030000}"/>
+    <cellStyle name="Normal 2 9 2" xfId="793" xr:uid="{00000000-0005-0000-0000-000009030000}"/>
+    <cellStyle name="Normal 20" xfId="224" xr:uid="{00000000-0005-0000-0000-00000A030000}"/>
+    <cellStyle name="Normal 21" xfId="288" xr:uid="{00000000-0005-0000-0000-00000B030000}"/>
+    <cellStyle name="Normal 22" xfId="428" xr:uid="{00000000-0005-0000-0000-00000C030000}"/>
+    <cellStyle name="Normal 22 2" xfId="782" xr:uid="{00000000-0005-0000-0000-00000D030000}"/>
+    <cellStyle name="Normal 23" xfId="584" xr:uid="{00000000-0005-0000-0000-00000E030000}"/>
+    <cellStyle name="Normal 23 2" xfId="849" xr:uid="{00000000-0005-0000-0000-00000F030000}"/>
+    <cellStyle name="Normal 24" xfId="635" xr:uid="{00000000-0005-0000-0000-000010030000}"/>
+    <cellStyle name="Normal 24 2" xfId="897" xr:uid="{00000000-0005-0000-0000-000011030000}"/>
+    <cellStyle name="Normal 25" xfId="767" xr:uid="{00000000-0005-0000-0000-000012030000}"/>
+    <cellStyle name="Normal 26" xfId="701" xr:uid="{00000000-0005-0000-0000-000013030000}"/>
+    <cellStyle name="Normal 27" xfId="120" xr:uid="{00000000-0005-0000-0000-000014030000}"/>
+    <cellStyle name="Normal 27 2" xfId="390" xr:uid="{00000000-0005-0000-0000-000015030000}"/>
+    <cellStyle name="Normal 27 3" xfId="537" xr:uid="{00000000-0005-0000-0000-000016030000}"/>
+    <cellStyle name="Normal 28" xfId="121" xr:uid="{00000000-0005-0000-0000-000017030000}"/>
+    <cellStyle name="Normal 28 2" xfId="391" xr:uid="{00000000-0005-0000-0000-000018030000}"/>
+    <cellStyle name="Normal 28 3" xfId="538" xr:uid="{00000000-0005-0000-0000-000019030000}"/>
+    <cellStyle name="Normal 29" xfId="1021" xr:uid="{00000000-0005-0000-0000-00001A030000}"/>
+    <cellStyle name="Normal 3" xfId="3" xr:uid="{00000000-0005-0000-0000-00001B030000}"/>
+    <cellStyle name="Normal 3 2" xfId="48" xr:uid="{00000000-0005-0000-0000-00001C030000}"/>
+    <cellStyle name="Normal 3 2 2" xfId="161" xr:uid="{00000000-0005-0000-0000-00001D030000}"/>
+    <cellStyle name="Normal 3 2 2 2" xfId="393" xr:uid="{00000000-0005-0000-0000-00001E030000}"/>
+    <cellStyle name="Normal 3 2 3" xfId="223" xr:uid="{00000000-0005-0000-0000-00001F030000}"/>
+    <cellStyle name="Normal 3 2 3 2" xfId="540" xr:uid="{00000000-0005-0000-0000-000020030000}"/>
+    <cellStyle name="Normal 3 2 4" xfId="140" xr:uid="{00000000-0005-0000-0000-000021030000}"/>
+    <cellStyle name="Normal 3 3" xfId="53" xr:uid="{00000000-0005-0000-0000-000022030000}"/>
+    <cellStyle name="Normal 3 3 2" xfId="394" xr:uid="{00000000-0005-0000-0000-000023030000}"/>
+    <cellStyle name="Normal 3 3 3" xfId="541" xr:uid="{00000000-0005-0000-0000-000024030000}"/>
+    <cellStyle name="Normal 3 3 4" xfId="171" xr:uid="{00000000-0005-0000-0000-000025030000}"/>
+    <cellStyle name="Normal 3 4" xfId="56" xr:uid="{00000000-0005-0000-0000-000026030000}"/>
+    <cellStyle name="Normal 3 4 2" xfId="395" xr:uid="{00000000-0005-0000-0000-000027030000}"/>
+    <cellStyle name="Normal 3 4 3" xfId="542" xr:uid="{00000000-0005-0000-0000-000028030000}"/>
+    <cellStyle name="Normal 3 5" xfId="184" xr:uid="{00000000-0005-0000-0000-000029030000}"/>
+    <cellStyle name="Normal 3 5 2" xfId="274" xr:uid="{00000000-0005-0000-0000-00002A030000}"/>
+    <cellStyle name="Normal 3 5 3" xfId="396" xr:uid="{00000000-0005-0000-0000-00002B030000}"/>
+    <cellStyle name="Normal 3 5 4" xfId="440" xr:uid="{00000000-0005-0000-0000-00002C030000}"/>
+    <cellStyle name="Normal 3 5 4 2" xfId="794" xr:uid="{00000000-0005-0000-0000-00002D030000}"/>
+    <cellStyle name="Normal 3 5 5" xfId="543" xr:uid="{00000000-0005-0000-0000-00002E030000}"/>
+    <cellStyle name="Normal 3 5 6" xfId="621" xr:uid="{00000000-0005-0000-0000-00002F030000}"/>
+    <cellStyle name="Normal 3 5 6 2" xfId="886" xr:uid="{00000000-0005-0000-0000-000030030000}"/>
+    <cellStyle name="Normal 3 5 7" xfId="677" xr:uid="{00000000-0005-0000-0000-000031030000}"/>
+    <cellStyle name="Normal 3 5 7 2" xfId="939" xr:uid="{00000000-0005-0000-0000-000032030000}"/>
+    <cellStyle name="Normal 3 5 8" xfId="743" xr:uid="{00000000-0005-0000-0000-000033030000}"/>
+    <cellStyle name="Normal 3 6" xfId="145" xr:uid="{00000000-0005-0000-0000-000034030000}"/>
+    <cellStyle name="Normal 3 6 2" xfId="397" xr:uid="{00000000-0005-0000-0000-000035030000}"/>
+    <cellStyle name="Normal 3 6 3" xfId="544" xr:uid="{00000000-0005-0000-0000-000036030000}"/>
+    <cellStyle name="Normal 3 7" xfId="392" xr:uid="{00000000-0005-0000-0000-000037030000}"/>
+    <cellStyle name="Normal 3 8" xfId="539" xr:uid="{00000000-0005-0000-0000-000038030000}"/>
+    <cellStyle name="Normal 3 9" xfId="1022" xr:uid="{00000000-0005-0000-0000-000039030000}"/>
+    <cellStyle name="Normal 4" xfId="1" xr:uid="{00000000-0005-0000-0000-00003A030000}"/>
+    <cellStyle name="Normal 4 2" xfId="47" xr:uid="{00000000-0005-0000-0000-00003B030000}"/>
+    <cellStyle name="Normal 4 2 2" xfId="49" xr:uid="{00000000-0005-0000-0000-00003C030000}"/>
+    <cellStyle name="Normal 4 2 2 2" xfId="399" xr:uid="{00000000-0005-0000-0000-00003D030000}"/>
+    <cellStyle name="Normal 4 2 3" xfId="546" xr:uid="{00000000-0005-0000-0000-00003E030000}"/>
+    <cellStyle name="Normal 4 2 4" xfId="162" xr:uid="{00000000-0005-0000-0000-00003F030000}"/>
+    <cellStyle name="Normal 4 2 5" xfId="103" xr:uid="{00000000-0005-0000-0000-000040030000}"/>
+    <cellStyle name="Normal 4 3" xfId="45" xr:uid="{00000000-0005-0000-0000-000041030000}"/>
+    <cellStyle name="Normal 4 3 2" xfId="400" xr:uid="{00000000-0005-0000-0000-000042030000}"/>
+    <cellStyle name="Normal 4 3 3" xfId="547" xr:uid="{00000000-0005-0000-0000-000043030000}"/>
+    <cellStyle name="Normal 4 4" xfId="398" xr:uid="{00000000-0005-0000-0000-000044030000}"/>
+    <cellStyle name="Normal 4 5" xfId="545" xr:uid="{00000000-0005-0000-0000-000045030000}"/>
+    <cellStyle name="Normal 4 6" xfId="1023" xr:uid="{00000000-0005-0000-0000-000046030000}"/>
+    <cellStyle name="Normal 5" xfId="54" xr:uid="{00000000-0005-0000-0000-000047030000}"/>
+    <cellStyle name="Normal 5 2" xfId="127" xr:uid="{00000000-0005-0000-0000-000048030000}"/>
+    <cellStyle name="Normal 5 2 2" xfId="163" xr:uid="{00000000-0005-0000-0000-000049030000}"/>
+    <cellStyle name="Normal 5 2 2 2" xfId="401" xr:uid="{00000000-0005-0000-0000-00004A030000}"/>
+    <cellStyle name="Normal 5 2 3" xfId="222" xr:uid="{00000000-0005-0000-0000-00004B030000}"/>
+    <cellStyle name="Normal 5 2 3 2" xfId="548" xr:uid="{00000000-0005-0000-0000-00004C030000}"/>
+    <cellStyle name="Normal 5 3" xfId="124" xr:uid="{00000000-0005-0000-0000-00004D030000}"/>
+    <cellStyle name="Normal 5 3 2" xfId="220" xr:uid="{00000000-0005-0000-0000-00004E030000}"/>
+    <cellStyle name="Normal 5 3 2 2" xfId="328" xr:uid="{00000000-0005-0000-0000-00004F030000}"/>
+    <cellStyle name="Normal 5 3 3" xfId="210" xr:uid="{00000000-0005-0000-0000-000050030000}"/>
+    <cellStyle name="Normal 5 3 3 2" xfId="549" xr:uid="{00000000-0005-0000-0000-000051030000}"/>
+    <cellStyle name="Normal 5 4" xfId="146" xr:uid="{00000000-0005-0000-0000-000052030000}"/>
+    <cellStyle name="Normal 5 4 2" xfId="275" xr:uid="{00000000-0005-0000-0000-000053030000}"/>
+    <cellStyle name="Normal 5 5" xfId="632" xr:uid="{00000000-0005-0000-0000-000054030000}"/>
+    <cellStyle name="Normal 5 6" xfId="115" xr:uid="{00000000-0005-0000-0000-000055030000}"/>
+    <cellStyle name="Normal 6" xfId="50" xr:uid="{00000000-0005-0000-0000-000056030000}"/>
+    <cellStyle name="Normal 6 2" xfId="164" xr:uid="{00000000-0005-0000-0000-000057030000}"/>
+    <cellStyle name="Normal 6 2 2" xfId="403" xr:uid="{00000000-0005-0000-0000-000058030000}"/>
+    <cellStyle name="Normal 6 2 3" xfId="551" xr:uid="{00000000-0005-0000-0000-000059030000}"/>
+    <cellStyle name="Normal 6 3" xfId="147" xr:uid="{00000000-0005-0000-0000-00005A030000}"/>
+    <cellStyle name="Normal 6 3 2" xfId="360" xr:uid="{00000000-0005-0000-0000-00005B030000}"/>
+    <cellStyle name="Normal 6 3 3" xfId="552" xr:uid="{00000000-0005-0000-0000-00005C030000}"/>
+    <cellStyle name="Normal 6 4" xfId="221" xr:uid="{00000000-0005-0000-0000-00005D030000}"/>
+    <cellStyle name="Normal 6 4 2" xfId="402" xr:uid="{00000000-0005-0000-0000-00005E030000}"/>
+    <cellStyle name="Normal 6 5" xfId="550" xr:uid="{00000000-0005-0000-0000-00005F030000}"/>
+    <cellStyle name="Normal 6 6" xfId="126" xr:uid="{00000000-0005-0000-0000-000060030000}"/>
+    <cellStyle name="Normal 7" xfId="117" xr:uid="{00000000-0005-0000-0000-000061030000}"/>
+    <cellStyle name="Normal 7 2" xfId="165" xr:uid="{00000000-0005-0000-0000-000062030000}"/>
+    <cellStyle name="Normal 7 2 2" xfId="334" xr:uid="{00000000-0005-0000-0000-000063030000}"/>
+    <cellStyle name="Normal 7 2 3" xfId="554" xr:uid="{00000000-0005-0000-0000-000064030000}"/>
+    <cellStyle name="Normal 7 3" xfId="276" xr:uid="{00000000-0005-0000-0000-000065030000}"/>
+    <cellStyle name="Normal 7 3 2" xfId="405" xr:uid="{00000000-0005-0000-0000-000066030000}"/>
+    <cellStyle name="Normal 7 3 3" xfId="555" xr:uid="{00000000-0005-0000-0000-000067030000}"/>
+    <cellStyle name="Normal 7 4" xfId="404" xr:uid="{00000000-0005-0000-0000-000068030000}"/>
+    <cellStyle name="Normal 7 5" xfId="553" xr:uid="{00000000-0005-0000-0000-000069030000}"/>
+    <cellStyle name="Normal 8" xfId="148" xr:uid="{00000000-0005-0000-0000-00006A030000}"/>
+    <cellStyle name="Normal 8 2" xfId="166" xr:uid="{00000000-0005-0000-0000-00006B030000}"/>
+    <cellStyle name="Normal 8 2 2" xfId="407" xr:uid="{00000000-0005-0000-0000-00006C030000}"/>
+    <cellStyle name="Normal 8 2 3" xfId="557" xr:uid="{00000000-0005-0000-0000-00006D030000}"/>
+    <cellStyle name="Normal 8 3" xfId="277" xr:uid="{00000000-0005-0000-0000-00006E030000}"/>
+    <cellStyle name="Normal 8 3 2" xfId="408" xr:uid="{00000000-0005-0000-0000-00006F030000}"/>
+    <cellStyle name="Normal 8 3 3" xfId="558" xr:uid="{00000000-0005-0000-0000-000070030000}"/>
+    <cellStyle name="Normal 8 4" xfId="406" xr:uid="{00000000-0005-0000-0000-000071030000}"/>
+    <cellStyle name="Normal 8 5" xfId="556" xr:uid="{00000000-0005-0000-0000-000072030000}"/>
+    <cellStyle name="Normal 9" xfId="149" xr:uid="{00000000-0005-0000-0000-000073030000}"/>
+    <cellStyle name="Normal 9 10" xfId="622" xr:uid="{00000000-0005-0000-0000-000074030000}"/>
+    <cellStyle name="Normal 9 10 2" xfId="887" xr:uid="{00000000-0005-0000-0000-000075030000}"/>
+    <cellStyle name="Normal 9 11" xfId="655" xr:uid="{00000000-0005-0000-0000-000076030000}"/>
+    <cellStyle name="Normal 9 11 2" xfId="917" xr:uid="{00000000-0005-0000-0000-000077030000}"/>
+    <cellStyle name="Normal 9 12" xfId="721" xr:uid="{00000000-0005-0000-0000-000078030000}"/>
+    <cellStyle name="Normal 9 2" xfId="167" xr:uid="{00000000-0005-0000-0000-000079030000}"/>
+    <cellStyle name="Normal 9 2 10" xfId="729" xr:uid="{00000000-0005-0000-0000-00007A030000}"/>
+    <cellStyle name="Normal 9 2 2" xfId="181" xr:uid="{00000000-0005-0000-0000-00007B030000}"/>
+    <cellStyle name="Normal 9 2 2 2" xfId="207" xr:uid="{00000000-0005-0000-0000-00007C030000}"/>
+    <cellStyle name="Normal 9 2 2 2 2" xfId="281" xr:uid="{00000000-0005-0000-0000-00007D030000}"/>
+    <cellStyle name="Normal 9 2 2 2 3" xfId="411" xr:uid="{00000000-0005-0000-0000-00007E030000}"/>
+    <cellStyle name="Normal 9 2 2 2 4" xfId="474" xr:uid="{00000000-0005-0000-0000-00007F030000}"/>
+    <cellStyle name="Normal 9 2 2 2 4 2" xfId="828" xr:uid="{00000000-0005-0000-0000-000080030000}"/>
+    <cellStyle name="Normal 9 2 2 2 5" xfId="562" xr:uid="{00000000-0005-0000-0000-000081030000}"/>
+    <cellStyle name="Normal 9 2 2 2 6" xfId="625" xr:uid="{00000000-0005-0000-0000-000082030000}"/>
+    <cellStyle name="Normal 9 2 2 2 6 2" xfId="890" xr:uid="{00000000-0005-0000-0000-000083030000}"/>
+    <cellStyle name="Normal 9 2 2 2 7" xfId="699" xr:uid="{00000000-0005-0000-0000-000084030000}"/>
+    <cellStyle name="Normal 9 2 2 2 7 2" xfId="961" xr:uid="{00000000-0005-0000-0000-000085030000}"/>
+    <cellStyle name="Normal 9 2 2 2 8" xfId="765" xr:uid="{00000000-0005-0000-0000-000086030000}"/>
+    <cellStyle name="Normal 9 2 2 3" xfId="280" xr:uid="{00000000-0005-0000-0000-000087030000}"/>
+    <cellStyle name="Normal 9 2 2 4" xfId="410" xr:uid="{00000000-0005-0000-0000-000088030000}"/>
+    <cellStyle name="Normal 9 2 2 5" xfId="437" xr:uid="{00000000-0005-0000-0000-000089030000}"/>
+    <cellStyle name="Normal 9 2 2 5 2" xfId="791" xr:uid="{00000000-0005-0000-0000-00008A030000}"/>
+    <cellStyle name="Normal 9 2 2 6" xfId="561" xr:uid="{00000000-0005-0000-0000-00008B030000}"/>
+    <cellStyle name="Normal 9 2 2 7" xfId="624" xr:uid="{00000000-0005-0000-0000-00008C030000}"/>
+    <cellStyle name="Normal 9 2 2 7 2" xfId="889" xr:uid="{00000000-0005-0000-0000-00008D030000}"/>
+    <cellStyle name="Normal 9 2 2 8" xfId="676" xr:uid="{00000000-0005-0000-0000-00008E030000}"/>
+    <cellStyle name="Normal 9 2 2 8 2" xfId="938" xr:uid="{00000000-0005-0000-0000-00008F030000}"/>
+    <cellStyle name="Normal 9 2 2 9" xfId="742" xr:uid="{00000000-0005-0000-0000-000090030000}"/>
+    <cellStyle name="Normal 9 2 3" xfId="196" xr:uid="{00000000-0005-0000-0000-000091030000}"/>
+    <cellStyle name="Normal 9 2 3 2" xfId="282" xr:uid="{00000000-0005-0000-0000-000092030000}"/>
+    <cellStyle name="Normal 9 2 3 3" xfId="412" xr:uid="{00000000-0005-0000-0000-000093030000}"/>
+    <cellStyle name="Normal 9 2 3 4" xfId="463" xr:uid="{00000000-0005-0000-0000-000094030000}"/>
+    <cellStyle name="Normal 9 2 3 4 2" xfId="817" xr:uid="{00000000-0005-0000-0000-000095030000}"/>
+    <cellStyle name="Normal 9 2 3 5" xfId="563" xr:uid="{00000000-0005-0000-0000-000096030000}"/>
+    <cellStyle name="Normal 9 2 3 6" xfId="626" xr:uid="{00000000-0005-0000-0000-000097030000}"/>
+    <cellStyle name="Normal 9 2 3 6 2" xfId="891" xr:uid="{00000000-0005-0000-0000-000098030000}"/>
+    <cellStyle name="Normal 9 2 3 7" xfId="688" xr:uid="{00000000-0005-0000-0000-000099030000}"/>
+    <cellStyle name="Normal 9 2 3 7 2" xfId="950" xr:uid="{00000000-0005-0000-0000-00009A030000}"/>
+    <cellStyle name="Normal 9 2 3 8" xfId="754" xr:uid="{00000000-0005-0000-0000-00009B030000}"/>
+    <cellStyle name="Normal 9 2 4" xfId="279" xr:uid="{00000000-0005-0000-0000-00009C030000}"/>
+    <cellStyle name="Normal 9 2 5" xfId="382" xr:uid="{00000000-0005-0000-0000-00009D030000}"/>
+    <cellStyle name="Normal 9 2 6" xfId="449" xr:uid="{00000000-0005-0000-0000-00009E030000}"/>
+    <cellStyle name="Normal 9 2 6 2" xfId="803" xr:uid="{00000000-0005-0000-0000-00009F030000}"/>
+    <cellStyle name="Normal 9 2 7" xfId="560" xr:uid="{00000000-0005-0000-0000-0000A0030000}"/>
+    <cellStyle name="Normal 9 2 8" xfId="623" xr:uid="{00000000-0005-0000-0000-0000A1030000}"/>
+    <cellStyle name="Normal 9 2 8 2" xfId="888" xr:uid="{00000000-0005-0000-0000-0000A2030000}"/>
+    <cellStyle name="Normal 9 2 9" xfId="663" xr:uid="{00000000-0005-0000-0000-0000A3030000}"/>
+    <cellStyle name="Normal 9 2 9 2" xfId="925" xr:uid="{00000000-0005-0000-0000-0000A4030000}"/>
+    <cellStyle name="Normal 9 3" xfId="172" xr:uid="{00000000-0005-0000-0000-0000A5030000}"/>
+    <cellStyle name="Normal 9 3 2" xfId="198" xr:uid="{00000000-0005-0000-0000-0000A6030000}"/>
+    <cellStyle name="Normal 9 3 2 2" xfId="284" xr:uid="{00000000-0005-0000-0000-0000A7030000}"/>
+    <cellStyle name="Normal 9 3 2 3" xfId="414" xr:uid="{00000000-0005-0000-0000-0000A8030000}"/>
+    <cellStyle name="Normal 9 3 2 4" xfId="465" xr:uid="{00000000-0005-0000-0000-0000A9030000}"/>
+    <cellStyle name="Normal 9 3 2 4 2" xfId="819" xr:uid="{00000000-0005-0000-0000-0000AA030000}"/>
+    <cellStyle name="Normal 9 3 2 5" xfId="565" xr:uid="{00000000-0005-0000-0000-0000AB030000}"/>
+    <cellStyle name="Normal 9 3 2 6" xfId="628" xr:uid="{00000000-0005-0000-0000-0000AC030000}"/>
+    <cellStyle name="Normal 9 3 2 6 2" xfId="893" xr:uid="{00000000-0005-0000-0000-0000AD030000}"/>
+    <cellStyle name="Normal 9 3 2 7" xfId="690" xr:uid="{00000000-0005-0000-0000-0000AE030000}"/>
+    <cellStyle name="Normal 9 3 2 7 2" xfId="952" xr:uid="{00000000-0005-0000-0000-0000AF030000}"/>
+    <cellStyle name="Normal 9 3 2 8" xfId="756" xr:uid="{00000000-0005-0000-0000-0000B0030000}"/>
+    <cellStyle name="Normal 9 3 3" xfId="283" xr:uid="{00000000-0005-0000-0000-0000B1030000}"/>
+    <cellStyle name="Normal 9 3 4" xfId="413" xr:uid="{00000000-0005-0000-0000-0000B2030000}"/>
+    <cellStyle name="Normal 9 3 5" xfId="425" xr:uid="{00000000-0005-0000-0000-0000B3030000}"/>
+    <cellStyle name="Normal 9 3 5 2" xfId="779" xr:uid="{00000000-0005-0000-0000-0000B4030000}"/>
+    <cellStyle name="Normal 9 3 6" xfId="564" xr:uid="{00000000-0005-0000-0000-0000B5030000}"/>
+    <cellStyle name="Normal 9 3 7" xfId="627" xr:uid="{00000000-0005-0000-0000-0000B6030000}"/>
+    <cellStyle name="Normal 9 3 7 2" xfId="892" xr:uid="{00000000-0005-0000-0000-0000B7030000}"/>
+    <cellStyle name="Normal 9 3 8" xfId="671" xr:uid="{00000000-0005-0000-0000-0000B8030000}"/>
+    <cellStyle name="Normal 9 3 8 2" xfId="933" xr:uid="{00000000-0005-0000-0000-0000B9030000}"/>
+    <cellStyle name="Normal 9 3 9" xfId="737" xr:uid="{00000000-0005-0000-0000-0000BA030000}"/>
+    <cellStyle name="Normal 9 4" xfId="187" xr:uid="{00000000-0005-0000-0000-0000BB030000}"/>
+    <cellStyle name="Normal 9 4 2" xfId="285" xr:uid="{00000000-0005-0000-0000-0000BC030000}"/>
+    <cellStyle name="Normal 9 4 3" xfId="415" xr:uid="{00000000-0005-0000-0000-0000BD030000}"/>
+    <cellStyle name="Normal 9 4 4" xfId="454" xr:uid="{00000000-0005-0000-0000-0000BE030000}"/>
+    <cellStyle name="Normal 9 4 4 2" xfId="808" xr:uid="{00000000-0005-0000-0000-0000BF030000}"/>
+    <cellStyle name="Normal 9 4 5" xfId="566" xr:uid="{00000000-0005-0000-0000-0000C0030000}"/>
+    <cellStyle name="Normal 9 4 6" xfId="629" xr:uid="{00000000-0005-0000-0000-0000C1030000}"/>
+    <cellStyle name="Normal 9 4 6 2" xfId="894" xr:uid="{00000000-0005-0000-0000-0000C2030000}"/>
+    <cellStyle name="Normal 9 4 7" xfId="679" xr:uid="{00000000-0005-0000-0000-0000C3030000}"/>
+    <cellStyle name="Normal 9 4 7 2" xfId="941" xr:uid="{00000000-0005-0000-0000-0000C4030000}"/>
+    <cellStyle name="Normal 9 4 8" xfId="745" xr:uid="{00000000-0005-0000-0000-0000C5030000}"/>
+    <cellStyle name="Normal 9 5" xfId="286" xr:uid="{00000000-0005-0000-0000-0000C6030000}"/>
+    <cellStyle name="Normal 9 5 2" xfId="416" xr:uid="{00000000-0005-0000-0000-0000C7030000}"/>
+    <cellStyle name="Normal 9 5 3" xfId="435" xr:uid="{00000000-0005-0000-0000-0000C8030000}"/>
+    <cellStyle name="Normal 9 5 3 2" xfId="789" xr:uid="{00000000-0005-0000-0000-0000C9030000}"/>
+    <cellStyle name="Normal 9 5 4" xfId="567" xr:uid="{00000000-0005-0000-0000-0000CA030000}"/>
+    <cellStyle name="Normal 9 5 5" xfId="630" xr:uid="{00000000-0005-0000-0000-0000CB030000}"/>
+    <cellStyle name="Normal 9 5 5 2" xfId="895" xr:uid="{00000000-0005-0000-0000-0000CC030000}"/>
+    <cellStyle name="Normal 9 5 6" xfId="668" xr:uid="{00000000-0005-0000-0000-0000CD030000}"/>
+    <cellStyle name="Normal 9 5 6 2" xfId="930" xr:uid="{00000000-0005-0000-0000-0000CE030000}"/>
+    <cellStyle name="Normal 9 5 7" xfId="774" xr:uid="{00000000-0005-0000-0000-0000CF030000}"/>
+    <cellStyle name="Normal 9 5 8" xfId="734" xr:uid="{00000000-0005-0000-0000-0000D0030000}"/>
+    <cellStyle name="Normal 9 6" xfId="278" xr:uid="{00000000-0005-0000-0000-0000D1030000}"/>
+    <cellStyle name="Normal 9 7" xfId="409" xr:uid="{00000000-0005-0000-0000-0000D2030000}"/>
+    <cellStyle name="Normal 9 8" xfId="426" xr:uid="{00000000-0005-0000-0000-0000D3030000}"/>
+    <cellStyle name="Normal 9 8 2" xfId="780" xr:uid="{00000000-0005-0000-0000-0000D4030000}"/>
+    <cellStyle name="Normal 9 9" xfId="559" xr:uid="{00000000-0005-0000-0000-0000D5030000}"/>
     <cellStyle name="Note" xfId="18" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Note 2" xfId="76"/>
-    <cellStyle name="Note 2 10" xfId="287"/>
-    <cellStyle name="Note 2 11" xfId="125"/>
-    <cellStyle name="Note 2 11 2" xfId="975"/>
-    <cellStyle name="Note 2 12" xfId="106"/>
-    <cellStyle name="Note 2 2" xfId="141"/>
-    <cellStyle name="Note 2 2 2" xfId="417"/>
-    <cellStyle name="Note 2 3" xfId="432"/>
-    <cellStyle name="Note 2 3 2" xfId="786"/>
-    <cellStyle name="Note 2 4" xfId="568"/>
-    <cellStyle name="Note 2 5" xfId="631"/>
-    <cellStyle name="Note 2 5 2" xfId="896"/>
-    <cellStyle name="Note 2 6" xfId="633"/>
-    <cellStyle name="Note 2 7" xfId="666"/>
-    <cellStyle name="Note 2 7 2" xfId="928"/>
-    <cellStyle name="Note 2 8" xfId="775"/>
-    <cellStyle name="Note 2 9" xfId="732"/>
+    <cellStyle name="Note 2" xfId="76" xr:uid="{00000000-0005-0000-0000-0000D7030000}"/>
+    <cellStyle name="Note 2 10" xfId="287" xr:uid="{00000000-0005-0000-0000-0000D8030000}"/>
+    <cellStyle name="Note 2 11" xfId="125" xr:uid="{00000000-0005-0000-0000-0000D9030000}"/>
+    <cellStyle name="Note 2 11 2" xfId="975" xr:uid="{00000000-0005-0000-0000-0000DA030000}"/>
+    <cellStyle name="Note 2 12" xfId="106" xr:uid="{00000000-0005-0000-0000-0000DB030000}"/>
+    <cellStyle name="Note 2 2" xfId="141" xr:uid="{00000000-0005-0000-0000-0000DC030000}"/>
+    <cellStyle name="Note 2 2 2" xfId="417" xr:uid="{00000000-0005-0000-0000-0000DD030000}"/>
+    <cellStyle name="Note 2 3" xfId="432" xr:uid="{00000000-0005-0000-0000-0000DE030000}"/>
+    <cellStyle name="Note 2 3 2" xfId="786" xr:uid="{00000000-0005-0000-0000-0000DF030000}"/>
+    <cellStyle name="Note 2 4" xfId="568" xr:uid="{00000000-0005-0000-0000-0000E0030000}"/>
+    <cellStyle name="Note 2 5" xfId="631" xr:uid="{00000000-0005-0000-0000-0000E1030000}"/>
+    <cellStyle name="Note 2 5 2" xfId="896" xr:uid="{00000000-0005-0000-0000-0000E2030000}"/>
+    <cellStyle name="Note 2 6" xfId="633" xr:uid="{00000000-0005-0000-0000-0000E3030000}"/>
+    <cellStyle name="Note 2 7" xfId="666" xr:uid="{00000000-0005-0000-0000-0000E4030000}"/>
+    <cellStyle name="Note 2 7 2" xfId="928" xr:uid="{00000000-0005-0000-0000-0000E5030000}"/>
+    <cellStyle name="Note 2 8" xfId="775" xr:uid="{00000000-0005-0000-0000-0000E6030000}"/>
+    <cellStyle name="Note 2 9" xfId="732" xr:uid="{00000000-0005-0000-0000-0000E7030000}"/>
     <cellStyle name="Output" xfId="13" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Output 2" xfId="73"/>
-    <cellStyle name="Output 2 2" xfId="418"/>
-    <cellStyle name="Output 2 2 2" xfId="995"/>
-    <cellStyle name="Output 3" xfId="1024"/>
-    <cellStyle name="Style 1" xfId="122"/>
-    <cellStyle name="Style 1 2" xfId="419"/>
-    <cellStyle name="Style 1 3" xfId="569"/>
+    <cellStyle name="Output 2" xfId="73" xr:uid="{00000000-0005-0000-0000-0000E9030000}"/>
+    <cellStyle name="Output 2 2" xfId="418" xr:uid="{00000000-0005-0000-0000-0000EA030000}"/>
+    <cellStyle name="Output 2 2 2" xfId="995" xr:uid="{00000000-0005-0000-0000-0000EB030000}"/>
+    <cellStyle name="Output 3" xfId="1024" xr:uid="{00000000-0005-0000-0000-0000EC030000}"/>
+    <cellStyle name="Style 1" xfId="122" xr:uid="{00000000-0005-0000-0000-0000ED030000}"/>
+    <cellStyle name="Style 1 2" xfId="419" xr:uid="{00000000-0005-0000-0000-0000EE030000}"/>
+    <cellStyle name="Style 1 3" xfId="569" xr:uid="{00000000-0005-0000-0000-0000EF030000}"/>
     <cellStyle name="Title" xfId="4" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Title 2" xfId="46"/>
-    <cellStyle name="Title 2 2" xfId="104"/>
-    <cellStyle name="Title 2 2 2" xfId="361"/>
-    <cellStyle name="Title 2 2 3" xfId="996"/>
-    <cellStyle name="Title 2 3" xfId="91"/>
-    <cellStyle name="Title 3" xfId="634"/>
-    <cellStyle name="Title 4" xfId="116"/>
+    <cellStyle name="Title 2" xfId="46" xr:uid="{00000000-0005-0000-0000-0000F1030000}"/>
+    <cellStyle name="Title 2 2" xfId="104" xr:uid="{00000000-0005-0000-0000-0000F2030000}"/>
+    <cellStyle name="Title 2 2 2" xfId="361" xr:uid="{00000000-0005-0000-0000-0000F3030000}"/>
+    <cellStyle name="Title 2 2 3" xfId="996" xr:uid="{00000000-0005-0000-0000-0000F4030000}"/>
+    <cellStyle name="Title 2 3" xfId="91" xr:uid="{00000000-0005-0000-0000-0000F5030000}"/>
+    <cellStyle name="Title 3" xfId="634" xr:uid="{00000000-0005-0000-0000-0000F6030000}"/>
+    <cellStyle name="Title 4" xfId="116" xr:uid="{00000000-0005-0000-0000-0000F7030000}"/>
     <cellStyle name="Total" xfId="20" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Total 2" xfId="87"/>
-    <cellStyle name="Total 2 2" xfId="420"/>
-    <cellStyle name="Total 2 2 2" xfId="997"/>
-    <cellStyle name="Total 3" xfId="1025"/>
+    <cellStyle name="Total 2" xfId="87" xr:uid="{00000000-0005-0000-0000-0000F9030000}"/>
+    <cellStyle name="Total 2 2" xfId="420" xr:uid="{00000000-0005-0000-0000-0000FA030000}"/>
+    <cellStyle name="Total 2 2 2" xfId="997" xr:uid="{00000000-0005-0000-0000-0000FB030000}"/>
+    <cellStyle name="Total 3" xfId="1025" xr:uid="{00000000-0005-0000-0000-0000FC030000}"/>
     <cellStyle name="Warning Text" xfId="17" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="Warning Text 2" xfId="83"/>
-    <cellStyle name="Warning Text 2 2" xfId="421"/>
-    <cellStyle name="Warning Text 2 2 2" xfId="998"/>
-    <cellStyle name="常规_Sheet1_18" xfId="211"/>
+    <cellStyle name="Warning Text 2" xfId="83" xr:uid="{00000000-0005-0000-0000-0000FE030000}"/>
+    <cellStyle name="Warning Text 2 2" xfId="421" xr:uid="{00000000-0005-0000-0000-0000FF030000}"/>
+    <cellStyle name="Warning Text 2 2 2" xfId="998" xr:uid="{00000000-0005-0000-0000-000000040000}"/>
+    <cellStyle name="常规_Sheet1_18" xfId="211" xr:uid="{00000000-0005-0000-0000-000001040000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4645,7 +4672,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4665,7 +4692,7 @@
       <c r="A1" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="B1" s="30"/>
+      <c r="B1" s="29"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
@@ -4675,7 +4702,7 @@
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="31"/>
+      <c r="B2" s="30"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="2" t="s">
@@ -4688,7 +4715,7 @@
       <c r="A3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B3" s="32"/>
+      <c r="B3" s="31"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -4697,7 +4724,7 @@
     </row>
     <row r="4" spans="1:8" ht="15.75">
       <c r="A4" s="9"/>
-      <c r="B4" s="33"/>
+      <c r="B4" s="32"/>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -4708,7 +4735,7 @@
       <c r="A5" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="34" t="s">
+      <c r="B5" s="33" t="s">
         <v>132</v>
       </c>
       <c r="C5" s="7" t="s">
@@ -4731,10 +4758,10 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75">
-      <c r="A6" s="50">
+      <c r="A6" s="43">
         <v>1</v>
       </c>
-      <c r="B6" s="35">
+      <c r="B6" s="34">
         <v>1620082</v>
       </c>
       <c r="C6" s="15" t="s">
@@ -4757,7 +4784,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75">
-      <c r="A7" s="49"/>
+      <c r="A7" s="42"/>
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
@@ -4771,10 +4798,10 @@
       <c r="H7" s="18"/>
     </row>
     <row r="8" spans="1:8" ht="15.75">
-      <c r="A8" s="50">
+      <c r="A8" s="43">
         <v>2</v>
       </c>
-      <c r="B8" s="36">
+      <c r="B8" s="35">
         <v>1620003</v>
       </c>
       <c r="C8" s="22" t="s">
@@ -4797,7 +4824,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75">
-      <c r="A9" s="50"/>
+      <c r="A9" s="43"/>
       <c r="B9" s="18"/>
       <c r="C9" s="22"/>
       <c r="D9" s="22"/>
@@ -4811,10 +4838,10 @@
       <c r="H9" s="22"/>
     </row>
     <row r="10" spans="1:8" ht="15.75">
-      <c r="A10" s="50">
+      <c r="A10" s="43">
         <v>2</v>
       </c>
-      <c r="B10" s="36">
+      <c r="B10" s="35">
         <v>1620005</v>
       </c>
       <c r="C10" s="22" t="s">
@@ -4837,7 +4864,7 @@
       </c>
     </row>
     <row r="11" spans="1:8" ht="15.75">
-      <c r="A11" s="50"/>
+      <c r="A11" s="43"/>
       <c r="B11" s="18"/>
       <c r="C11" s="22"/>
       <c r="D11" s="22"/>
@@ -4851,50 +4878,50 @@
       <c r="H11" s="22"/>
     </row>
     <row r="12" spans="1:8" ht="15.75">
-      <c r="A12" s="45">
+      <c r="A12" s="38">
         <v>4</v>
       </c>
-      <c r="B12" s="36">
+      <c r="B12" s="35">
         <v>1620032</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="C12" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="23">
         <v>402</v>
       </c>
-      <c r="E12" s="24" t="s">
+      <c r="E12" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="F12" s="24" t="s">
+      <c r="F12" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="G12" s="24" t="s">
+      <c r="G12" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="H12" s="24" t="s">
+      <c r="H12" s="23" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15.75">
-      <c r="A13" s="45"/>
+      <c r="A13" s="38"/>
       <c r="B13" s="18"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24" t="s">
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="F13" s="24" t="s">
+      <c r="F13" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="G13" s="24"/>
-      <c r="H13" s="24"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="23"/>
     </row>
     <row r="14" spans="1:8" ht="15.75">
-      <c r="A14" s="50">
+      <c r="A14" s="43">
         <v>4</v>
       </c>
-      <c r="B14" s="36">
+      <c r="B14" s="35">
         <v>1620024</v>
       </c>
       <c r="C14" s="11" t="s">
@@ -4917,7 +4944,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="15.75">
-      <c r="A15" s="50"/>
+      <c r="A15" s="43"/>
       <c r="B15" s="18"/>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -4931,10 +4958,10 @@
       <c r="H15" s="11"/>
     </row>
     <row r="16" spans="1:8" ht="15.75">
-      <c r="A16" s="50">
+      <c r="A16" s="43">
         <v>1</v>
       </c>
-      <c r="B16" s="36">
+      <c r="B16" s="35">
         <v>1620008</v>
       </c>
       <c r="C16" s="22" t="s">
@@ -4957,7 +4984,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" ht="15.75">
-      <c r="A17" s="50"/>
+      <c r="A17" s="43"/>
       <c r="B17" s="18"/>
       <c r="C17" s="22"/>
       <c r="D17" s="22"/>
@@ -4973,10 +5000,10 @@
       </c>
     </row>
     <row r="18" spans="1:8" ht="15.75">
-      <c r="A18" s="48">
+      <c r="A18" s="41">
         <v>1</v>
       </c>
-      <c r="B18" s="36">
+      <c r="B18" s="35">
         <v>1620009</v>
       </c>
       <c r="C18" s="12" t="s">
@@ -4999,7 +5026,7 @@
       </c>
     </row>
     <row r="19" spans="1:8" ht="15.75">
-      <c r="A19" s="48"/>
+      <c r="A19" s="41"/>
       <c r="B19" s="18"/>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -5016,7 +5043,7 @@
       <c r="A20" s="11">
         <v>1</v>
       </c>
-      <c r="B20" s="27">
+      <c r="B20" s="26">
         <v>1620084</v>
       </c>
       <c r="C20" s="15" t="s">
@@ -5034,12 +5061,12 @@
       <c r="G20" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="H20" s="25" t="s">
+      <c r="H20" s="24" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15.75">
-      <c r="A21" s="50"/>
+      <c r="A21" s="43"/>
       <c r="B21" s="18"/>
       <c r="C21" s="15"/>
       <c r="D21" s="15"/>
@@ -5056,7 +5083,7 @@
       <c r="A22" s="22">
         <v>1</v>
       </c>
-      <c r="B22" s="36">
+      <c r="B22" s="35">
         <v>1610002</v>
       </c>
       <c r="C22" s="22">
@@ -5079,7 +5106,7 @@
       </c>
     </row>
     <row r="23" spans="1:8" ht="15.75">
-      <c r="A23" s="50"/>
+      <c r="A23" s="43"/>
       <c r="B23" s="18"/>
       <c r="C23" s="15"/>
       <c r="D23" s="15"/>
@@ -5093,10 +5120,10 @@
       <c r="H23" s="15"/>
     </row>
     <row r="24" spans="1:8" ht="15.75">
-      <c r="A24" s="46">
+      <c r="A24" s="39">
         <v>1</v>
       </c>
-      <c r="B24" s="36">
+      <c r="B24" s="35">
         <v>1610003</v>
       </c>
       <c r="C24" s="22">
@@ -5119,7 +5146,7 @@
       </c>
     </row>
     <row r="25" spans="1:8" ht="15.75">
-      <c r="A25" s="50"/>
+      <c r="A25" s="43"/>
       <c r="B25" s="18"/>
       <c r="C25" s="15"/>
       <c r="D25" s="15"/>
@@ -5133,25 +5160,25 @@
       <c r="H25" s="15"/>
     </row>
     <row r="26" spans="1:8" ht="15.75">
-      <c r="A26" s="48">
+      <c r="A26" s="41">
         <v>3</v>
       </c>
-      <c r="B26" s="27">
+      <c r="B26" s="26">
         <v>1610080</v>
       </c>
-      <c r="C26" s="26">
+      <c r="C26" s="25">
         <v>330</v>
       </c>
-      <c r="D26" s="26">
+      <c r="D26" s="25">
         <v>402</v>
       </c>
-      <c r="E26" s="26" t="s">
+      <c r="E26" s="25" t="s">
         <v>23</v>
       </c>
       <c r="F26" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="G26" s="26" t="s">
+      <c r="G26" s="25" t="s">
         <v>146</v>
       </c>
       <c r="H26" s="15" t="s">
@@ -5159,11 +5186,11 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="15.75">
-      <c r="A27" s="48"/>
+      <c r="A27" s="41"/>
       <c r="B27" s="18"/>
       <c r="C27" s="12"/>
       <c r="D27" s="12"/>
-      <c r="E27" s="26" t="s">
+      <c r="E27" s="25" t="s">
         <v>111</v>
       </c>
       <c r="F27" s="12" t="s">
@@ -5173,10 +5200,10 @@
       <c r="H27" s="12"/>
     </row>
     <row r="28" spans="1:8" ht="15.75">
-      <c r="A28" s="46">
+      <c r="A28" s="39">
         <v>1</v>
       </c>
-      <c r="B28" s="27">
+      <c r="B28" s="26">
         <v>1610083</v>
       </c>
       <c r="C28" s="12" t="s">
@@ -5199,7 +5226,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" ht="15.75">
-      <c r="A29" s="50"/>
+      <c r="A29" s="43"/>
       <c r="B29" s="18"/>
       <c r="C29" s="15"/>
       <c r="D29" s="15"/>
@@ -5213,28 +5240,28 @@
       <c r="H29" s="15"/>
     </row>
     <row r="30" spans="1:8" ht="15.75">
-      <c r="A30" s="54">
+      <c r="A30" s="47">
         <v>1</v>
       </c>
-      <c r="B30" s="54">
+      <c r="B30" s="47">
         <v>1610007</v>
       </c>
-      <c r="C30" s="54" t="s">
+      <c r="C30" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="D30" s="54">
+      <c r="D30" s="47">
         <v>402</v>
       </c>
-      <c r="E30" s="54" t="s">
+      <c r="E30" s="47" t="s">
         <v>148</v>
       </c>
-      <c r="F30" s="54" t="s">
+      <c r="F30" s="47" t="s">
         <v>149</v>
       </c>
-      <c r="G30" s="52" t="s">
+      <c r="G30" s="45" t="s">
         <v>151</v>
       </c>
-      <c r="H30" s="54" t="s">
+      <c r="H30" s="47" t="s">
         <v>150</v>
       </c>
     </row>
@@ -5242,25 +5269,25 @@
       <c r="A31" s="11">
         <v>1</v>
       </c>
-      <c r="B31" s="27">
+      <c r="B31" s="26">
         <v>1046104</v>
       </c>
-      <c r="C31" s="28" t="s">
+      <c r="C31" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="D31" s="28" t="s">
+      <c r="D31" s="27" t="s">
         <v>20</v>
       </c>
       <c r="E31" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="F31" s="28" t="s">
+      <c r="F31" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="G31" s="28" t="s">
+      <c r="G31" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="H31" s="28" t="s">
+      <c r="H31" s="27" t="s">
         <v>116</v>
       </c>
     </row>
@@ -5268,87 +5295,87 @@
       <c r="A32" s="11">
         <v>1</v>
       </c>
-      <c r="B32" s="27">
+      <c r="B32" s="26">
         <v>1650012</v>
       </c>
-      <c r="C32" s="28" t="s">
+      <c r="C32" s="27" t="s">
         <v>103</v>
       </c>
       <c r="D32" s="18">
         <v>402</v>
       </c>
-      <c r="E32" s="28" t="s">
+      <c r="E32" s="27" t="s">
         <v>160</v>
       </c>
-      <c r="F32" s="28" t="s">
+      <c r="F32" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="G32" s="28" t="s">
+      <c r="G32" s="27" t="s">
         <v>179</v>
       </c>
-      <c r="H32" s="28" t="s">
+      <c r="H32" s="27" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="15.75">
-      <c r="A33" s="29"/>
+      <c r="A33" s="28"/>
       <c r="B33" s="18"/>
-      <c r="C33" s="29"/>
-      <c r="D33" s="29"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
       <c r="E33" s="21" t="s">
         <v>109</v>
       </c>
       <c r="F33" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="G33" s="29"/>
-      <c r="H33" s="29"/>
-    </row>
-    <row r="34" spans="1:8" s="51" customFormat="1" ht="15.75">
-      <c r="A34" s="47">
+      <c r="G33" s="28"/>
+      <c r="H33" s="28"/>
+    </row>
+    <row r="34" spans="1:8" s="44" customFormat="1" ht="15.75">
+      <c r="A34" s="40">
         <v>1</v>
       </c>
-      <c r="B34" s="47">
+      <c r="B34" s="40">
         <v>1650039</v>
       </c>
-      <c r="C34" s="47" t="s">
+      <c r="C34" s="40" t="s">
         <v>175</v>
       </c>
-      <c r="D34" s="47">
+      <c r="D34" s="40">
         <v>402</v>
       </c>
-      <c r="E34" s="28" t="s">
+      <c r="E34" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="F34" s="47" t="s">
+      <c r="F34" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="G34" s="47" t="s">
+      <c r="G34" s="40" t="s">
         <v>178</v>
       </c>
-      <c r="H34" s="28" t="s">
+      <c r="H34" s="27" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="15.75">
-      <c r="A35" s="37"/>
-      <c r="B35" s="37"/>
-      <c r="C35" s="37"/>
-      <c r="D35" s="37"/>
-      <c r="E35" s="37" t="s">
+      <c r="A35" s="36"/>
+      <c r="B35" s="36"/>
+      <c r="C35" s="36"/>
+      <c r="D35" s="36"/>
+      <c r="E35" s="36" t="s">
         <v>177</v>
       </c>
-      <c r="F35" s="37" t="s">
+      <c r="F35" s="36" t="s">
         <v>77</v>
       </c>
-      <c r="G35" s="37"/>
-      <c r="H35" s="37"/>
+      <c r="G35" s="36"/>
+      <c r="H35" s="36"/>
     </row>
     <row r="36" spans="1:8" ht="15.75">
-      <c r="A36" s="50">
+      <c r="A36" s="43">
         <v>1</v>
       </c>
-      <c r="B36" s="35">
+      <c r="B36" s="34">
         <v>1650011</v>
       </c>
       <c r="C36" s="15" t="s">
@@ -5360,7 +5387,7 @@
       <c r="E36" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="F36" s="28" t="s">
+      <c r="F36" s="27" t="s">
         <v>96</v>
       </c>
       <c r="G36" s="15" t="s">
@@ -5371,7 +5398,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" ht="15.75">
-      <c r="A37" s="49"/>
+      <c r="A37" s="42"/>
       <c r="B37" s="18"/>
       <c r="C37" s="18"/>
       <c r="D37" s="18"/>
@@ -5381,7 +5408,7 @@
       <c r="H37" s="18"/>
     </row>
     <row r="38" spans="1:8" ht="15.75">
-      <c r="A38" s="50">
+      <c r="A38" s="43">
         <v>1</v>
       </c>
       <c r="B38" s="12">
@@ -5393,10 +5420,10 @@
       <c r="D38" s="15">
         <v>805</v>
       </c>
-      <c r="E38" s="28" t="s">
+      <c r="E38" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="F38" s="28" t="s">
+      <c r="F38" s="27" t="s">
         <v>100</v>
       </c>
       <c r="G38" s="15" t="s">
@@ -5410,7 +5437,7 @@
       <c r="A39" s="11">
         <v>1</v>
       </c>
-      <c r="B39" s="27">
+      <c r="B39" s="26">
         <v>1690086</v>
       </c>
       <c r="C39" s="12" t="s">
@@ -5431,83 +5458,83 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="15.75">
-      <c r="A40" s="50">
+      <c r="A40" s="43">
         <v>1</v>
       </c>
-      <c r="B40" s="27">
+      <c r="B40" s="51">
         <v>1630001</v>
       </c>
-      <c r="C40" s="22" t="s">
+      <c r="C40" s="52" t="s">
         <v>117</v>
       </c>
-      <c r="D40" s="22" t="s">
+      <c r="D40" s="52" t="s">
         <v>118</v>
       </c>
-      <c r="E40" s="22" t="s">
+      <c r="E40" s="52" t="s">
         <v>117</v>
       </c>
-      <c r="F40" s="22" t="s">
+      <c r="F40" s="52" t="s">
         <v>119</v>
       </c>
-      <c r="G40" s="22" t="s">
+      <c r="G40" s="52" t="s">
         <v>121</v>
       </c>
-      <c r="H40" s="23" t="s">
+      <c r="H40" s="53" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="15.75">
-      <c r="A42" s="50">
+      <c r="A42" s="43">
         <v>1</v>
       </c>
-      <c r="B42" s="18">
+      <c r="B42" s="54">
         <v>1690085</v>
       </c>
-      <c r="C42" s="15" t="s">
+      <c r="C42" s="54" t="s">
         <v>145</v>
       </c>
-      <c r="D42" s="15" t="s">
+      <c r="D42" s="54" t="s">
         <v>144</v>
       </c>
-      <c r="E42" s="15" t="s">
+      <c r="E42" s="54" t="s">
         <v>143</v>
       </c>
-      <c r="F42" s="15" t="s">
+      <c r="F42" s="54" t="s">
         <v>142</v>
       </c>
-      <c r="G42" s="15" t="s">
+      <c r="G42" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="H42" s="15" t="s">
+      <c r="H42" s="54" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="51"/>
+      <c r="A43" s="44"/>
     </row>
     <row r="44" spans="1:8" ht="15.75">
-      <c r="A44" s="50">
+      <c r="A44" s="43">
         <v>1</v>
       </c>
-      <c r="B44" s="36">
+      <c r="B44" s="55">
         <v>1680001</v>
       </c>
-      <c r="C44" s="22" t="s">
+      <c r="C44" s="52" t="s">
         <v>59</v>
       </c>
-      <c r="D44" s="22" t="s">
+      <c r="D44" s="52" t="s">
         <v>60</v>
       </c>
-      <c r="E44" s="22" t="s">
+      <c r="E44" s="52" t="s">
         <v>61</v>
       </c>
-      <c r="F44" s="22" t="s">
+      <c r="F44" s="52" t="s">
         <v>62</v>
       </c>
-      <c r="G44" s="22" t="s">
+      <c r="G44" s="52" t="s">
         <v>63</v>
       </c>
-      <c r="H44" s="22" t="s">
+      <c r="H44" s="52" t="s">
         <v>64</v>
       </c>
     </row>
@@ -5526,7 +5553,7 @@
       <c r="H45" s="22"/>
     </row>
     <row r="46" spans="1:8" ht="15.75">
-      <c r="A46" s="48"/>
+      <c r="A46" s="41"/>
       <c r="B46" s="18"/>
       <c r="C46" s="22"/>
       <c r="D46" s="22"/>
@@ -5540,7 +5567,7 @@
       <c r="H46" s="22"/>
     </row>
     <row r="47" spans="1:8" ht="15.75">
-      <c r="A47" s="50"/>
+      <c r="A47" s="43"/>
       <c r="B47" s="18"/>
       <c r="C47" s="22"/>
       <c r="D47" s="22"/>
@@ -5554,7 +5581,7 @@
       <c r="H47" s="22"/>
     </row>
     <row r="48" spans="1:8" ht="15.75">
-      <c r="A48" s="48"/>
+      <c r="A48" s="41"/>
       <c r="B48" s="18"/>
       <c r="C48" s="22"/>
       <c r="D48" s="22"/>
@@ -5568,7 +5595,7 @@
       <c r="H48" s="22"/>
     </row>
     <row r="49" spans="1:8" ht="15.75">
-      <c r="A49" s="50"/>
+      <c r="A49" s="43"/>
       <c r="B49" s="18"/>
       <c r="C49" s="22"/>
       <c r="D49" s="22"/>
@@ -5582,7 +5609,7 @@
       <c r="H49" s="22"/>
     </row>
     <row r="50" spans="1:8" ht="15.75">
-      <c r="A50" s="50"/>
+      <c r="A50" s="43"/>
       <c r="B50" s="18"/>
       <c r="C50" s="15"/>
       <c r="D50" s="15"/>
@@ -5592,194 +5619,203 @@
       <c r="H50" s="15"/>
     </row>
     <row r="51" spans="1:8" ht="15.75">
-      <c r="A51" s="50">
+      <c r="A51" s="43">
         <v>1</v>
       </c>
-      <c r="B51" s="36">
+      <c r="B51" s="56">
         <v>1123585</v>
       </c>
-      <c r="C51" s="22" t="s">
+      <c r="C51" s="57" t="s">
         <v>134</v>
       </c>
-      <c r="D51" s="22" t="s">
+      <c r="D51" s="57" t="s">
         <v>74</v>
       </c>
-      <c r="E51" s="22" t="s">
+      <c r="E51" s="57" t="s">
         <v>134</v>
       </c>
-      <c r="F51" s="22" t="s">
+      <c r="F51" s="57" t="s">
         <v>75</v>
       </c>
-      <c r="G51" s="22" t="s">
+      <c r="G51" s="57" t="s">
         <v>76</v>
       </c>
-      <c r="H51" s="22" t="s">
+      <c r="H51" s="57" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="15.75">
-      <c r="A52" s="50"/>
-      <c r="B52" s="18"/>
-      <c r="C52" s="15"/>
-      <c r="D52" s="15"/>
-      <c r="E52" s="15"/>
-      <c r="F52" s="15"/>
-      <c r="G52" s="15"/>
-      <c r="H52" s="15"/>
+      <c r="A52" s="43"/>
+      <c r="B52" s="28"/>
+      <c r="C52" s="58"/>
+      <c r="D52" s="58"/>
+      <c r="E52" s="58"/>
+      <c r="F52" s="58"/>
+      <c r="G52" s="58"/>
+      <c r="H52" s="58"/>
     </row>
     <row r="53" spans="1:8" s="13" customFormat="1" ht="15.75">
-      <c r="A53" s="48">
+      <c r="A53" s="41">
         <v>1</v>
       </c>
-      <c r="B53" s="27">
+      <c r="B53" s="59">
         <v>1690061</v>
       </c>
-      <c r="C53" s="15" t="s">
+      <c r="C53" s="58" t="s">
         <v>84</v>
       </c>
-      <c r="D53" s="11" t="s">
+      <c r="D53" s="60" t="s">
         <v>85</v>
       </c>
-      <c r="E53" s="15" t="s">
+      <c r="E53" s="58" t="s">
         <v>84</v>
       </c>
-      <c r="F53" s="11" t="s">
+      <c r="F53" s="60" t="s">
         <v>86</v>
       </c>
-      <c r="G53" s="15" t="s">
+      <c r="G53" s="58" t="s">
         <v>87</v>
       </c>
-      <c r="H53" s="11" t="s">
+      <c r="H53" s="60" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="54" spans="1:8" s="13" customFormat="1" ht="15.75">
-      <c r="A54" s="48"/>
-      <c r="B54" s="27"/>
-      <c r="C54" s="15"/>
-      <c r="D54" s="11"/>
-      <c r="E54" s="15"/>
-      <c r="F54" s="11"/>
-      <c r="G54" s="15"/>
-      <c r="H54" s="11"/>
+      <c r="A54" s="41"/>
+      <c r="B54" s="59"/>
+      <c r="C54" s="58"/>
+      <c r="D54" s="60"/>
+      <c r="E54" s="58"/>
+      <c r="F54" s="60"/>
+      <c r="G54" s="58"/>
+      <c r="H54" s="60"/>
     </row>
     <row r="55" spans="1:8" ht="15.75">
-      <c r="A55" s="47">
+      <c r="A55" s="40">
         <v>1</v>
       </c>
-      <c r="B55" s="40">
+      <c r="B55" s="58">
         <v>1187123</v>
       </c>
-      <c r="C55" s="38">
+      <c r="C55" s="61">
         <v>1187123</v>
       </c>
-      <c r="D55" s="38" t="s">
+      <c r="D55" s="61" t="s">
         <v>161</v>
       </c>
-      <c r="E55" s="38" t="s">
+      <c r="E55" s="61" t="s">
         <v>162</v>
       </c>
-      <c r="F55" s="38" t="s">
+      <c r="F55" s="61" t="s">
         <v>137</v>
       </c>
-      <c r="G55" s="39" t="s">
+      <c r="G55" s="62" t="s">
         <v>131</v>
       </c>
-      <c r="H55" s="37" t="s">
+      <c r="H55" s="63" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="15.75">
-      <c r="A56" s="50"/>
-      <c r="B56" s="18"/>
-      <c r="C56" s="15"/>
-      <c r="D56" s="15"/>
-      <c r="E56" s="15"/>
-      <c r="F56" s="15"/>
-      <c r="G56" s="15"/>
-      <c r="H56" s="15"/>
+      <c r="A56" s="43"/>
+      <c r="B56" s="28"/>
+      <c r="C56" s="58"/>
+      <c r="D56" s="58"/>
+      <c r="E56" s="58"/>
+      <c r="F56" s="58"/>
+      <c r="G56" s="58"/>
+      <c r="H56" s="58"/>
     </row>
     <row r="57" spans="1:8" ht="15.75">
-      <c r="A57" s="49">
+      <c r="A57" s="42">
         <v>1</v>
       </c>
-      <c r="B57" s="42">
+      <c r="B57" s="58">
         <v>1187113</v>
       </c>
-      <c r="C57" s="41">
+      <c r="C57" s="61">
         <v>1187113</v>
       </c>
-      <c r="D57" s="41" t="s">
+      <c r="D57" s="61" t="s">
         <v>161</v>
       </c>
-      <c r="E57" s="41" t="s">
+      <c r="E57" s="61" t="s">
         <v>162</v>
       </c>
-      <c r="F57" s="41" t="s">
+      <c r="F57" s="61" t="s">
         <v>137</v>
       </c>
-      <c r="G57" s="41" t="s">
+      <c r="G57" s="61" t="s">
         <v>152</v>
       </c>
-      <c r="H57" s="43" t="s">
+      <c r="H57" s="64" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="15.75">
-      <c r="A58" s="50"/>
-      <c r="B58" s="18"/>
-      <c r="C58" s="15"/>
-      <c r="D58" s="15"/>
-      <c r="E58" s="15"/>
-      <c r="F58" s="15"/>
-      <c r="G58" s="15"/>
-      <c r="H58" s="15"/>
+      <c r="A58" s="43"/>
+      <c r="B58" s="28"/>
+      <c r="C58" s="58"/>
+      <c r="D58" s="58"/>
+      <c r="E58" s="58"/>
+      <c r="F58" s="58"/>
+      <c r="G58" s="58"/>
+      <c r="H58" s="58"/>
     </row>
     <row r="59" spans="1:8" ht="15.75">
-      <c r="A59" s="47">
+      <c r="A59" s="40">
         <v>1</v>
       </c>
-      <c r="B59" s="47">
+      <c r="B59" s="61">
         <v>1376008</v>
       </c>
-      <c r="C59" s="47">
+      <c r="C59" s="61">
         <v>1376008</v>
       </c>
-      <c r="D59" s="47"/>
-      <c r="E59" s="47" t="s">
+      <c r="D59" s="61"/>
+      <c r="E59" s="61" t="s">
         <v>166</v>
       </c>
-      <c r="F59" s="47" t="s">
+      <c r="F59" s="61" t="s">
         <v>167</v>
       </c>
-      <c r="G59" s="47"/>
-      <c r="H59" s="47" t="s">
+      <c r="G59" s="61"/>
+      <c r="H59" s="61" t="s">
         <v>168</v>
       </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="B60" s="65"/>
+      <c r="C60" s="65"/>
+      <c r="D60" s="65"/>
+      <c r="E60" s="65"/>
+      <c r="F60" s="65"/>
+      <c r="G60" s="65"/>
+      <c r="H60" s="65"/>
     </row>
     <row r="61" spans="1:8" ht="15.75">
       <c r="A61" s="11">
         <v>1</v>
       </c>
-      <c r="B61" s="35">
+      <c r="B61" s="59">
         <v>1153320</v>
       </c>
-      <c r="C61" s="12" t="s">
+      <c r="C61" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="D61" s="12" t="s">
+      <c r="D61" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="E61" s="15">
+      <c r="E61" s="58">
         <v>1153320</v>
       </c>
-      <c r="F61" s="12">
+      <c r="F61" s="28">
         <v>1153320</v>
       </c>
-      <c r="G61" s="12" t="s">
+      <c r="G61" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="H61" s="12" t="s">
+      <c r="H61" s="28" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5828,10 +5864,10 @@
       </c>
     </row>
     <row r="65" spans="1:8" ht="15.75">
-      <c r="A65" s="50">
+      <c r="A65" s="43">
         <v>2</v>
       </c>
-      <c r="B65" s="35">
+      <c r="B65" s="34">
         <v>1690072</v>
       </c>
       <c r="C65" s="12" t="s">
@@ -5852,59 +5888,59 @@
       </c>
     </row>
     <row r="66" spans="1:8" ht="15.75">
-      <c r="A66" s="46">
+      <c r="A66" s="39">
         <v>1</v>
       </c>
-      <c r="B66" s="36">
+      <c r="B66" s="35">
         <v>1610109</v>
       </c>
-      <c r="C66" s="53" t="s">
+      <c r="C66" s="46" t="s">
         <v>170</v>
       </c>
-      <c r="D66" s="53">
+      <c r="D66" s="46">
         <v>402</v>
       </c>
-      <c r="E66" s="56" t="s">
+      <c r="E66" s="49" t="s">
         <v>171</v>
       </c>
-      <c r="F66" s="53" t="s">
+      <c r="F66" s="46" t="s">
         <v>172</v>
       </c>
-      <c r="G66" s="53" t="s">
+      <c r="G66" s="46" t="s">
         <v>169</v>
       </c>
-      <c r="H66" s="53" t="s">
+      <c r="H66" s="46" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="17.25">
-      <c r="A67" s="46">
+      <c r="A67" s="39">
         <v>2</v>
       </c>
-      <c r="B67" s="50">
+      <c r="B67" s="43">
         <v>1610001</v>
       </c>
-      <c r="C67" s="53">
+      <c r="C67" s="46">
         <v>0</v>
       </c>
-      <c r="D67" s="53">
+      <c r="D67" s="46">
         <v>402</v>
       </c>
-      <c r="E67" s="44" t="s">
+      <c r="E67" s="37" t="s">
         <v>182</v>
       </c>
-      <c r="F67" s="53" t="s">
+      <c r="F67" s="46" t="s">
         <v>149</v>
       </c>
-      <c r="G67" s="53" t="s">
+      <c r="G67" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="H67" s="57" t="s">
+      <c r="H67" s="50" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="15.75">
-      <c r="A68" s="55" t="s">
+      <c r="A68" s="48" t="s">
         <v>153</v>
       </c>
     </row>
@@ -5914,7 +5950,7 @@
       </c>
     </row>
     <row r="71" spans="1:8" ht="15.75">
-      <c r="A71" s="55" t="s">
+      <c r="A71" s="48" t="s">
         <v>156</v>
       </c>
     </row>
